--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/2구역 전투 테이블 V1.3.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/2구역 전투 테이블 V1.3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200016\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0E3DD9-B9AD-45FB-8100-BA912ED867D1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6135E0A7-F29C-4263-AD6B-13BA913DDCC2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14300" yWindow="0" windowWidth="14610" windowHeight="15590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="290">
   <si>
     <t>2구역 메인/서브 이벤트 전투 테이블</t>
   </si>
@@ -1096,6 +1096,14 @@
   </si>
   <si>
     <t>율리아 수치 조정</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>V1.4</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>드론 공격력 조정</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1331,12 +1339,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1374,6 +1376,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2290,7 +2298,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="9.5" customWidth="1"/>
@@ -2360,6 +2368,20 @@
         <v>287</v>
       </c>
       <c r="D6" s="13" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="B7" s="11">
+        <v>46297</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>286</v>
       </c>
     </row>
@@ -2424,2653 +2446,2653 @@
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.45">
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-      <c r="O2" s="19"/>
-      <c r="P2" s="19"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
     </row>
     <row r="4" spans="1:50" x14ac:dyDescent="0.45">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="J4" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="21" t="s">
+      <c r="K4" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="21" t="s">
+      <c r="L4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="21" t="s">
+      <c r="M4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="22" t="s">
+      <c r="N4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O4" s="22" t="s">
+      <c r="O4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="22" t="s">
+      <c r="P4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="22" t="s">
+      <c r="Q4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="R4" s="22" t="s">
+      <c r="R4" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="S4" s="22" t="s">
+      <c r="S4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="T4" s="22" t="s">
+      <c r="T4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="22" t="s">
+      <c r="U4" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="22" t="s">
+      <c r="V4" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="W4" s="21" t="s">
+      <c r="W4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="X4" s="21" t="s">
+      <c r="X4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="Y4" s="22" t="s">
+      <c r="Y4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="Z4" s="22" t="s">
+      <c r="Z4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="AA4" s="22" t="s">
+      <c r="AA4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="AB4" s="22" t="s">
+      <c r="AB4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="AC4" s="22" t="s">
+      <c r="AC4" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="AD4" s="22" t="s">
+      <c r="AD4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="AE4" s="22" t="s">
+      <c r="AE4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="AF4" s="22" t="s">
+      <c r="AF4" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="AG4" s="22" t="s">
+      <c r="AG4" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="AH4" s="21" t="s">
+      <c r="AH4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="AI4" s="21" t="s">
+      <c r="AI4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="AJ4" s="22" t="s">
+      <c r="AJ4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="AK4" s="22" t="s">
+      <c r="AK4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="AL4" s="22" t="s">
+      <c r="AL4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="AM4" s="22" t="s">
+      <c r="AM4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="AN4" s="22" t="s">
+      <c r="AN4" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="AO4" s="22" t="s">
+      <c r="AO4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="AP4" s="22" t="s">
+      <c r="AP4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="AQ4" s="22" t="s">
+      <c r="AQ4" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="AR4" s="22" t="s">
+      <c r="AR4" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="AS4" s="22" t="s">
+      <c r="AS4" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="AT4" s="22" t="s">
+      <c r="AT4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="AU4" s="22" t="s">
+      <c r="AU4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="AV4" s="22" t="s">
+      <c r="AV4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="AW4" s="22" t="s">
+      <c r="AW4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="AX4" s="22" t="s">
+      <c r="AX4" s="20" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:50" ht="34" x14ac:dyDescent="0.45">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="21" t="s">
+      <c r="K5" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="L5" s="21" t="s">
+      <c r="L5" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="M5" s="21" t="s">
+      <c r="M5" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="N5" s="21" t="s">
+      <c r="N5" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="O5" s="21" t="s">
+      <c r="O5" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="P5" s="21" t="s">
+      <c r="P5" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="Q5" s="21" t="s">
+      <c r="Q5" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="R5" s="21" t="s">
+      <c r="R5" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="S5" s="21" t="s">
+      <c r="S5" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="T5" s="21" t="s">
+      <c r="T5" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="U5" s="21" t="s">
+      <c r="U5" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="V5" s="21" t="s">
+      <c r="V5" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="W5" s="21" t="s">
+      <c r="W5" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="X5" s="21" t="s">
+      <c r="X5" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="Y5" s="21" t="s">
+      <c r="Y5" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="Z5" s="21" t="s">
+      <c r="Z5" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="AA5" s="21" t="s">
+      <c r="AA5" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="AB5" s="21" t="s">
+      <c r="AB5" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="AC5" s="21" t="s">
+      <c r="AC5" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="AD5" s="21" t="s">
+      <c r="AD5" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="AE5" s="21" t="s">
+      <c r="AE5" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="AF5" s="21" t="s">
+      <c r="AF5" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="AG5" s="21" t="s">
+      <c r="AG5" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="AH5" s="23" t="s">
+      <c r="AH5" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="AI5" s="23" t="s">
+      <c r="AI5" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="AJ5" s="21" t="s">
+      <c r="AJ5" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="AK5" s="21" t="s">
+      <c r="AK5" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AL5" s="21" t="s">
+      <c r="AL5" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="AM5" s="21" t="s">
+      <c r="AM5" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="AN5" s="21" t="s">
+      <c r="AN5" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="AO5" s="23" t="s">
+      <c r="AO5" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="AP5" s="23" t="s">
+      <c r="AP5" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="AQ5" s="21" t="s">
+      <c r="AQ5" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="AR5" s="21" t="s">
+      <c r="AR5" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="AS5" s="21" t="s">
+      <c r="AS5" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="AT5" s="21" t="s">
+      <c r="AT5" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="AU5" s="21" t="s">
+      <c r="AU5" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="AV5" s="21" t="s">
+      <c r="AV5" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="AW5" s="21" t="s">
+      <c r="AW5" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="AX5" s="21" t="s">
+      <c r="AX5" s="19" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:50" ht="170" x14ac:dyDescent="0.45">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="19">
         <v>5</v>
       </c>
-      <c r="F6" s="21">
-        <v>10</v>
-      </c>
-      <c r="G6" s="21">
+      <c r="F6" s="32">
+        <v>4</v>
+      </c>
+      <c r="G6" s="19">
         <v>5</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="22">
         <v>0.10000000149011599</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="22">
         <v>0.10000000149011599</v>
       </c>
-      <c r="J6" s="24">
+      <c r="J6" s="22">
         <v>0.10000000149011599</v>
       </c>
-      <c r="K6" s="21">
+      <c r="K6" s="19">
         <v>2</v>
       </c>
-      <c r="L6" s="21" t="s">
+      <c r="L6" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="M6" s="23" t="s">
+      <c r="M6" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="N6" s="21">
-        <v>0</v>
-      </c>
-      <c r="O6" s="21">
+      <c r="N6" s="19">
+        <v>0</v>
+      </c>
+      <c r="O6" s="19">
         <v>2</v>
       </c>
-      <c r="P6" s="21">
+      <c r="P6" s="19">
         <v>1</v>
       </c>
-      <c r="Q6" s="21">
-        <v>0</v>
-      </c>
-      <c r="R6" s="21"/>
-      <c r="S6" s="21"/>
-      <c r="T6" s="21"/>
-      <c r="U6" s="24">
+      <c r="Q6" s="19">
+        <v>0</v>
+      </c>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="22">
         <v>1</v>
       </c>
-      <c r="V6" s="24">
-        <v>0</v>
-      </c>
-      <c r="W6" s="21"/>
-      <c r="X6" s="23"/>
-      <c r="Y6" s="21"/>
-      <c r="Z6" s="21"/>
-      <c r="AA6" s="21"/>
-      <c r="AB6" s="21"/>
-      <c r="AC6" s="21"/>
-      <c r="AD6" s="21"/>
-      <c r="AE6" s="21"/>
-      <c r="AF6" s="24"/>
-      <c r="AG6" s="24"/>
-      <c r="AH6" s="23" t="s">
+      <c r="V6" s="22">
+        <v>0</v>
+      </c>
+      <c r="W6" s="19"/>
+      <c r="X6" s="21"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="19"/>
+      <c r="AA6" s="19"/>
+      <c r="AB6" s="19"/>
+      <c r="AC6" s="19"/>
+      <c r="AD6" s="19"/>
+      <c r="AE6" s="19"/>
+      <c r="AF6" s="22"/>
+      <c r="AG6" s="22"/>
+      <c r="AH6" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="AI6" s="21">
+      <c r="AI6" s="19">
         <v>15</v>
       </c>
-      <c r="AJ6" s="21">
+      <c r="AJ6" s="19">
         <v>5</v>
       </c>
-      <c r="AK6" s="21">
+      <c r="AK6" s="19">
         <v>1</v>
       </c>
-      <c r="AL6" s="21">
+      <c r="AL6" s="19">
         <v>4</v>
       </c>
-      <c r="AM6" s="21">
+      <c r="AM6" s="19">
         <v>1</v>
       </c>
-      <c r="AN6" s="21"/>
-      <c r="AO6" s="21"/>
-      <c r="AP6" s="21"/>
-      <c r="AQ6" s="21"/>
-      <c r="AR6" s="21"/>
-      <c r="AS6" s="21"/>
-      <c r="AT6" s="21">
+      <c r="AN6" s="19"/>
+      <c r="AO6" s="19"/>
+      <c r="AP6" s="19"/>
+      <c r="AQ6" s="19"/>
+      <c r="AR6" s="19"/>
+      <c r="AS6" s="19"/>
+      <c r="AT6" s="19">
         <v>15</v>
       </c>
-      <c r="AU6" s="21">
+      <c r="AU6" s="19">
         <v>5</v>
       </c>
-      <c r="AV6" s="21">
+      <c r="AV6" s="19">
         <v>1</v>
       </c>
-      <c r="AW6" s="21">
+      <c r="AW6" s="19">
         <v>4</v>
       </c>
-      <c r="AX6" s="21">
+      <c r="AX6" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:50" ht="289" x14ac:dyDescent="0.45">
-      <c r="A7" s="21"/>
-      <c r="B7" s="21" t="s">
+      <c r="A7" s="19"/>
+      <c r="B7" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="19">
         <v>8</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="19">
         <v>6</v>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="19">
         <v>6</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="22">
         <v>0.10000000149011599</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="22">
         <v>0.10000000149011599</v>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="22">
         <v>0.25</v>
       </c>
-      <c r="K7" s="21">
+      <c r="K7" s="19">
         <v>3</v>
       </c>
-      <c r="L7" s="21" t="s">
+      <c r="L7" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="M7" s="23" t="s">
+      <c r="M7" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="N7" s="21">
-        <v>0</v>
-      </c>
-      <c r="O7" s="21">
+      <c r="N7" s="19">
+        <v>0</v>
+      </c>
+      <c r="O7" s="19">
         <v>1</v>
       </c>
-      <c r="P7" s="21">
+      <c r="P7" s="19">
         <v>1</v>
       </c>
-      <c r="Q7" s="21">
-        <v>0</v>
-      </c>
-      <c r="R7" s="21"/>
-      <c r="S7" s="21">
-        <v>0</v>
-      </c>
-      <c r="T7" s="21">
-        <v>0</v>
-      </c>
-      <c r="U7" s="24">
+      <c r="Q7" s="19">
+        <v>0</v>
+      </c>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19">
+        <v>0</v>
+      </c>
+      <c r="T7" s="19">
+        <v>0</v>
+      </c>
+      <c r="U7" s="22">
         <v>1</v>
       </c>
-      <c r="V7" s="24">
-        <v>0</v>
-      </c>
-      <c r="W7" s="21" t="s">
+      <c r="V7" s="22">
+        <v>0</v>
+      </c>
+      <c r="W7" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="X7" s="21" t="s">
+      <c r="X7" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="Y7" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="21">
+      <c r="Y7" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="19">
         <v>1</v>
       </c>
-      <c r="AA7" s="21">
+      <c r="AA7" s="19">
         <v>1</v>
       </c>
-      <c r="AB7" s="21">
+      <c r="AB7" s="19">
         <v>1</v>
       </c>
-      <c r="AC7" s="21" t="s">
+      <c r="AC7" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="AD7" s="21">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="21"/>
-      <c r="AF7" s="24">
+      <c r="AD7" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="19"/>
+      <c r="AF7" s="22">
         <v>0.6</v>
       </c>
-      <c r="AG7" s="24">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="23" t="s">
+      <c r="AG7" s="22">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="AI7" s="21">
+      <c r="AI7" s="19">
         <v>30</v>
       </c>
-      <c r="AJ7" s="21">
+      <c r="AJ7" s="19">
         <v>10</v>
       </c>
-      <c r="AK7" s="21">
+      <c r="AK7" s="19">
         <v>3</v>
       </c>
-      <c r="AL7" s="21">
+      <c r="AL7" s="19">
         <v>4</v>
       </c>
-      <c r="AM7" s="21">
+      <c r="AM7" s="19">
         <v>1</v>
       </c>
-      <c r="AN7" s="21"/>
-      <c r="AO7" s="21"/>
-      <c r="AP7" s="21"/>
-      <c r="AQ7" s="21"/>
-      <c r="AR7" s="21"/>
-      <c r="AS7" s="21"/>
-      <c r="AT7" s="21">
+      <c r="AN7" s="19"/>
+      <c r="AO7" s="19"/>
+      <c r="AP7" s="19"/>
+      <c r="AQ7" s="19"/>
+      <c r="AR7" s="19"/>
+      <c r="AS7" s="19"/>
+      <c r="AT7" s="19">
         <v>30</v>
       </c>
-      <c r="AU7" s="21">
+      <c r="AU7" s="19">
         <v>10</v>
       </c>
-      <c r="AV7" s="21">
+      <c r="AV7" s="19">
         <v>3</v>
       </c>
-      <c r="AW7" s="21">
+      <c r="AW7" s="19">
         <v>4</v>
       </c>
-      <c r="AX7" s="21">
+      <c r="AX7" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:50" ht="204" x14ac:dyDescent="0.45">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="19">
         <v>6</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="19">
         <v>6</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="19">
         <v>8</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="22">
         <v>0.10000000149011599</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="22">
         <v>0.25</v>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="22">
         <v>0.10000000149011599</v>
       </c>
-      <c r="K8" s="21">
-        <v>0</v>
-      </c>
-      <c r="L8" s="21" t="s">
+      <c r="K8" s="19">
+        <v>0</v>
+      </c>
+      <c r="L8" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M8" s="23" t="s">
+      <c r="M8" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="N8" s="21">
-        <v>0</v>
-      </c>
-      <c r="O8" s="21">
-        <v>0</v>
-      </c>
-      <c r="P8" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="21">
-        <v>0</v>
-      </c>
-      <c r="R8" s="21"/>
-      <c r="S8" s="21">
-        <v>0</v>
-      </c>
-      <c r="T8" s="21">
-        <v>0</v>
-      </c>
-      <c r="U8" s="24">
+      <c r="N8" s="19">
+        <v>0</v>
+      </c>
+      <c r="O8" s="19">
+        <v>0</v>
+      </c>
+      <c r="P8" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="19">
+        <v>0</v>
+      </c>
+      <c r="R8" s="19"/>
+      <c r="S8" s="19">
+        <v>0</v>
+      </c>
+      <c r="T8" s="19">
+        <v>0</v>
+      </c>
+      <c r="U8" s="22">
         <v>0.80000001192092896</v>
       </c>
-      <c r="V8" s="24">
-        <v>0</v>
-      </c>
-      <c r="W8" s="21" t="s">
+      <c r="V8" s="22">
+        <v>0</v>
+      </c>
+      <c r="W8" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="X8" s="23" t="s">
+      <c r="X8" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="Y8" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="21">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="21">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="21"/>
-      <c r="AD8" s="21">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="21">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="24">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="24">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="23" t="s">
+      <c r="Y8" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="19"/>
+      <c r="AD8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="22">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="22">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="AI8" s="21">
+      <c r="AI8" s="19">
         <v>30</v>
       </c>
-      <c r="AJ8" s="21">
+      <c r="AJ8" s="19">
         <v>10</v>
       </c>
-      <c r="AK8" s="21">
+      <c r="AK8" s="19">
         <v>2</v>
       </c>
-      <c r="AL8" s="21">
+      <c r="AL8" s="19">
         <v>3</v>
       </c>
-      <c r="AM8" s="21">
+      <c r="AM8" s="19">
         <v>3</v>
       </c>
-      <c r="AN8" s="21"/>
-      <c r="AO8" s="21"/>
-      <c r="AP8" s="21"/>
-      <c r="AQ8" s="21"/>
-      <c r="AR8" s="21"/>
-      <c r="AS8" s="21"/>
-      <c r="AT8" s="21">
+      <c r="AN8" s="19"/>
+      <c r="AO8" s="19"/>
+      <c r="AP8" s="19"/>
+      <c r="AQ8" s="19"/>
+      <c r="AR8" s="19"/>
+      <c r="AS8" s="19"/>
+      <c r="AT8" s="19">
         <v>30</v>
       </c>
-      <c r="AU8" s="21">
+      <c r="AU8" s="19">
         <v>10</v>
       </c>
-      <c r="AV8" s="21">
+      <c r="AV8" s="19">
         <v>2</v>
       </c>
-      <c r="AW8" s="21">
+      <c r="AW8" s="19">
         <v>3</v>
       </c>
-      <c r="AX8" s="21">
+      <c r="AX8" s="19">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:50" ht="153" x14ac:dyDescent="0.45">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21" t="s">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="19">
         <v>6</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="19">
         <v>12</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="19">
         <v>6</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="22">
         <v>0.20000000298023199</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="22">
         <v>0.15000000596046401</v>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="22">
         <v>0.15000000596046401</v>
       </c>
-      <c r="K9" s="21">
+      <c r="K9" s="19">
         <v>2</v>
       </c>
-      <c r="L9" s="21" t="s">
+      <c r="L9" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="M9" s="23" t="s">
+      <c r="M9" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="N9" s="21">
-        <v>0</v>
-      </c>
-      <c r="O9" s="21">
+      <c r="N9" s="19">
+        <v>0</v>
+      </c>
+      <c r="O9" s="19">
         <v>1</v>
       </c>
-      <c r="P9" s="21">
+      <c r="P9" s="19">
         <v>1</v>
       </c>
-      <c r="Q9" s="21">
+      <c r="Q9" s="19">
         <v>1</v>
       </c>
-      <c r="R9" s="21" t="s">
+      <c r="R9" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="S9" s="21">
-        <v>0</v>
-      </c>
-      <c r="T9" s="21">
-        <v>0</v>
-      </c>
-      <c r="U9" s="24">
+      <c r="S9" s="19">
+        <v>0</v>
+      </c>
+      <c r="T9" s="19">
+        <v>0</v>
+      </c>
+      <c r="U9" s="22">
         <v>1.20000004768372</v>
       </c>
-      <c r="V9" s="24">
+      <c r="V9" s="22">
         <v>1</v>
       </c>
-      <c r="W9" s="21"/>
-      <c r="X9" s="21"/>
-      <c r="Y9" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="21"/>
-      <c r="AD9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="24">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="24">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="23" t="s">
+      <c r="W9" s="19"/>
+      <c r="X9" s="19"/>
+      <c r="Y9" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="19"/>
+      <c r="AD9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="22">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="22">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="AI9" s="21">
+      <c r="AI9" s="19">
         <v>60</v>
       </c>
-      <c r="AJ9" s="21">
+      <c r="AJ9" s="19">
         <v>20</v>
       </c>
-      <c r="AK9" s="21">
+      <c r="AK9" s="19">
         <v>3</v>
       </c>
-      <c r="AL9" s="21">
+      <c r="AL9" s="19">
         <v>4</v>
       </c>
-      <c r="AM9" s="21">
+      <c r="AM9" s="19">
         <v>3</v>
       </c>
-      <c r="AN9" s="21"/>
-      <c r="AO9" s="21"/>
-      <c r="AP9" s="21"/>
-      <c r="AQ9" s="21"/>
-      <c r="AR9" s="21"/>
-      <c r="AS9" s="21"/>
-      <c r="AT9" s="21">
+      <c r="AN9" s="19"/>
+      <c r="AO9" s="19"/>
+      <c r="AP9" s="19"/>
+      <c r="AQ9" s="19"/>
+      <c r="AR9" s="19"/>
+      <c r="AS9" s="19"/>
+      <c r="AT9" s="19">
         <v>60</v>
       </c>
-      <c r="AU9" s="21">
+      <c r="AU9" s="19">
         <v>20</v>
       </c>
-      <c r="AV9" s="21">
+      <c r="AV9" s="19">
         <v>3</v>
       </c>
-      <c r="AW9" s="21">
+      <c r="AW9" s="19">
         <v>4</v>
       </c>
-      <c r="AX9" s="21">
+      <c r="AX9" s="19">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:50" ht="306" x14ac:dyDescent="0.45">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21" t="s">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="19">
         <v>100</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="19">
         <v>6</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="19">
         <v>6</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="22">
         <v>0.25</v>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="22">
         <v>0.20000000298023199</v>
       </c>
-      <c r="J10" s="24">
+      <c r="J10" s="22">
         <v>0.20000000298023199</v>
       </c>
-      <c r="K10" s="21">
+      <c r="K10" s="19">
         <v>1</v>
       </c>
-      <c r="L10" s="21" t="s">
+      <c r="L10" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="M10" s="23" t="s">
+      <c r="M10" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="N10" s="21">
-        <v>0</v>
-      </c>
-      <c r="O10" s="21">
+      <c r="N10" s="19">
+        <v>0</v>
+      </c>
+      <c r="O10" s="19">
         <v>1</v>
       </c>
-      <c r="P10" s="21">
+      <c r="P10" s="19">
         <v>1</v>
       </c>
-      <c r="Q10" s="21">
-        <v>0</v>
-      </c>
-      <c r="R10" s="21"/>
-      <c r="S10" s="21">
-        <v>0</v>
-      </c>
-      <c r="T10" s="21">
-        <v>0</v>
-      </c>
-      <c r="U10" s="24">
+      <c r="Q10" s="19">
+        <v>0</v>
+      </c>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19">
+        <v>0</v>
+      </c>
+      <c r="T10" s="19">
+        <v>0</v>
+      </c>
+      <c r="U10" s="22">
         <v>1</v>
       </c>
-      <c r="V10" s="24">
-        <v>0</v>
-      </c>
-      <c r="W10" s="21" t="s">
+      <c r="V10" s="22">
+        <v>0</v>
+      </c>
+      <c r="W10" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="X10" s="23" t="s">
+      <c r="X10" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="Y10" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="21">
+      <c r="Y10" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="19">
         <v>1</v>
       </c>
-      <c r="AC10" s="21" t="s">
+      <c r="AC10" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="AD10" s="21">
+      <c r="AD10" s="19">
         <v>1</v>
       </c>
-      <c r="AE10" s="21">
+      <c r="AE10" s="19">
         <v>1</v>
       </c>
-      <c r="AF10" s="24">
+      <c r="AF10" s="22">
         <v>1</v>
       </c>
-      <c r="AG10" s="24">
+      <c r="AG10" s="22">
         <v>0.8</v>
       </c>
-      <c r="AH10" s="23" t="s">
+      <c r="AH10" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="AI10" s="21">
+      <c r="AI10" s="19">
         <v>80</v>
       </c>
-      <c r="AJ10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="21">
+      <c r="AJ10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="19">
         <v>10</v>
       </c>
-      <c r="AL10" s="21">
+      <c r="AL10" s="19">
         <v>5</v>
       </c>
-      <c r="AM10" s="21">
+      <c r="AM10" s="19">
         <v>3</v>
       </c>
-      <c r="AN10" s="21"/>
-      <c r="AO10" s="21"/>
-      <c r="AP10" s="21"/>
-      <c r="AQ10" s="21"/>
-      <c r="AR10" s="21"/>
-      <c r="AS10" s="21"/>
-      <c r="AT10" s="21">
+      <c r="AN10" s="19"/>
+      <c r="AO10" s="19"/>
+      <c r="AP10" s="19"/>
+      <c r="AQ10" s="19"/>
+      <c r="AR10" s="19"/>
+      <c r="AS10" s="19"/>
+      <c r="AT10" s="19">
         <v>80</v>
       </c>
-      <c r="AU10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AV10" s="21">
+      <c r="AU10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="19">
         <v>7</v>
       </c>
-      <c r="AW10" s="21">
+      <c r="AW10" s="19">
         <v>5</v>
       </c>
-      <c r="AX10" s="21">
+      <c r="AX10" s="19">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:50" ht="239.5" x14ac:dyDescent="0.45">
-      <c r="A11" s="21"/>
-      <c r="B11" s="21" t="s">
+      <c r="A11" s="19"/>
+      <c r="B11" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="19">
         <v>8</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="19">
         <v>6</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="19">
         <v>6</v>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="23">
         <v>0.1</v>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="23">
         <v>0.1</v>
       </c>
-      <c r="J11" s="25">
+      <c r="J11" s="23">
         <v>0.1</v>
       </c>
-      <c r="K11" s="21">
+      <c r="K11" s="19">
         <v>3</v>
       </c>
-      <c r="L11" s="21" t="s">
+      <c r="L11" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="M11" s="23" t="s">
+      <c r="M11" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="N11" s="21">
-        <v>0</v>
-      </c>
-      <c r="O11" s="21">
+      <c r="N11" s="19">
+        <v>0</v>
+      </c>
+      <c r="O11" s="19">
         <v>1</v>
       </c>
-      <c r="P11" s="21">
+      <c r="P11" s="19">
         <v>1</v>
       </c>
-      <c r="Q11" s="21">
-        <v>0</v>
-      </c>
-      <c r="R11" s="21"/>
-      <c r="S11" s="21"/>
-      <c r="T11" s="21"/>
-      <c r="U11" s="25">
+      <c r="Q11" s="19">
+        <v>0</v>
+      </c>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="23">
         <v>1</v>
       </c>
-      <c r="V11" s="25"/>
-      <c r="W11" s="21" t="s">
+      <c r="V11" s="23"/>
+      <c r="W11" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="X11" s="23" t="s">
+      <c r="X11" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="Y11" s="21"/>
-      <c r="Z11" s="21"/>
-      <c r="AA11" s="21"/>
-      <c r="AB11" s="21"/>
-      <c r="AC11" s="21"/>
-      <c r="AD11" s="21"/>
-      <c r="AE11" s="21"/>
-      <c r="AF11" s="25"/>
-      <c r="AG11" s="25"/>
-      <c r="AH11" s="21"/>
-      <c r="AI11" s="23"/>
-      <c r="AJ11" s="21"/>
-      <c r="AK11" s="21"/>
-      <c r="AL11" s="21"/>
-      <c r="AM11" s="21"/>
-      <c r="AN11" s="21"/>
-      <c r="AO11" s="21"/>
-      <c r="AP11" s="21"/>
-      <c r="AQ11" s="25"/>
-      <c r="AR11" s="25"/>
-      <c r="AS11" s="23" t="s">
+      <c r="Y11" s="19"/>
+      <c r="Z11" s="19"/>
+      <c r="AA11" s="19"/>
+      <c r="AB11" s="19"/>
+      <c r="AC11" s="19"/>
+      <c r="AD11" s="19"/>
+      <c r="AE11" s="19"/>
+      <c r="AF11" s="23"/>
+      <c r="AG11" s="23"/>
+      <c r="AH11" s="19"/>
+      <c r="AI11" s="21"/>
+      <c r="AJ11" s="19"/>
+      <c r="AK11" s="19"/>
+      <c r="AL11" s="19"/>
+      <c r="AM11" s="19"/>
+      <c r="AN11" s="19"/>
+      <c r="AO11" s="19"/>
+      <c r="AP11" s="19"/>
+      <c r="AQ11" s="23"/>
+      <c r="AR11" s="23"/>
+      <c r="AS11" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="AT11" s="21">
+      <c r="AT11" s="19">
         <v>50</v>
       </c>
-      <c r="AU11" s="21">
+      <c r="AU11" s="19">
         <v>50</v>
       </c>
-      <c r="AV11" s="21">
+      <c r="AV11" s="19">
         <v>8</v>
       </c>
-      <c r="AW11" s="21">
+      <c r="AW11" s="19">
         <v>4</v>
       </c>
-      <c r="AX11" s="21">
+      <c r="AX11" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:50" ht="255" x14ac:dyDescent="0.45">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21" t="s">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="19">
         <v>6</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="19">
         <v>6</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="19">
         <v>8</v>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="23">
         <v>0.1</v>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="23">
         <v>0.1</v>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="23">
         <v>0.1</v>
       </c>
-      <c r="K12" s="21">
-        <v>0</v>
-      </c>
-      <c r="L12" s="21" t="s">
+      <c r="K12" s="19">
+        <v>0</v>
+      </c>
+      <c r="L12" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="M12" s="23" t="s">
+      <c r="M12" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="N12" s="21">
-        <v>0</v>
-      </c>
-      <c r="O12" s="21">
-        <v>0</v>
-      </c>
-      <c r="P12" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="21">
-        <v>0</v>
-      </c>
-      <c r="R12" s="21"/>
-      <c r="S12" s="21"/>
-      <c r="T12" s="21"/>
-      <c r="U12" s="25">
+      <c r="N12" s="19">
+        <v>0</v>
+      </c>
+      <c r="O12" s="19">
+        <v>0</v>
+      </c>
+      <c r="P12" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="19">
+        <v>0</v>
+      </c>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="23">
         <v>0.8</v>
       </c>
-      <c r="V12" s="25"/>
-      <c r="W12" s="21" t="s">
+      <c r="V12" s="23"/>
+      <c r="W12" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="X12" s="23" t="s">
+      <c r="X12" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="Y12" s="21"/>
-      <c r="Z12" s="21"/>
-      <c r="AA12" s="21"/>
-      <c r="AB12" s="21"/>
-      <c r="AC12" s="21"/>
-      <c r="AD12" s="21"/>
-      <c r="AE12" s="21"/>
-      <c r="AF12" s="25"/>
-      <c r="AG12" s="25"/>
-      <c r="AH12" s="21" t="s">
+      <c r="Y12" s="19"/>
+      <c r="Z12" s="19"/>
+      <c r="AA12" s="19"/>
+      <c r="AB12" s="19"/>
+      <c r="AC12" s="19"/>
+      <c r="AD12" s="19"/>
+      <c r="AE12" s="19"/>
+      <c r="AF12" s="23"/>
+      <c r="AG12" s="23"/>
+      <c r="AH12" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="AI12" s="23" t="s">
+      <c r="AI12" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="AJ12" s="21"/>
-      <c r="AK12" s="21"/>
-      <c r="AL12" s="21"/>
-      <c r="AM12" s="21"/>
-      <c r="AN12" s="21"/>
-      <c r="AO12" s="21"/>
-      <c r="AP12" s="21"/>
-      <c r="AQ12" s="25"/>
-      <c r="AR12" s="25"/>
-      <c r="AS12" s="23" t="s">
+      <c r="AJ12" s="19"/>
+      <c r="AK12" s="19"/>
+      <c r="AL12" s="19"/>
+      <c r="AM12" s="19"/>
+      <c r="AN12" s="19"/>
+      <c r="AO12" s="19"/>
+      <c r="AP12" s="19"/>
+      <c r="AQ12" s="23"/>
+      <c r="AR12" s="23"/>
+      <c r="AS12" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="AT12" s="21">
+      <c r="AT12" s="19">
         <v>50</v>
       </c>
-      <c r="AU12" s="21">
+      <c r="AU12" s="19">
         <v>50</v>
       </c>
-      <c r="AV12" s="21">
+      <c r="AV12" s="19">
         <v>6</v>
       </c>
-      <c r="AW12" s="21">
+      <c r="AW12" s="19">
         <v>3</v>
       </c>
-      <c r="AX12" s="21">
+      <c r="AX12" s="19">
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:50" ht="85" x14ac:dyDescent="0.45">
-      <c r="A13" s="21"/>
-      <c r="B13" s="21" t="s">
+      <c r="A13" s="19"/>
+      <c r="B13" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="19">
         <v>50</v>
       </c>
-      <c r="F13" s="21">
-        <v>0</v>
-      </c>
-      <c r="G13" s="21">
-        <v>0</v>
-      </c>
-      <c r="H13" s="25">
-        <v>0</v>
-      </c>
-      <c r="I13" s="25">
-        <v>0</v>
-      </c>
-      <c r="J13" s="25">
-        <v>0</v>
-      </c>
-      <c r="K13" s="21">
+      <c r="F13" s="19">
+        <v>0</v>
+      </c>
+      <c r="G13" s="19">
+        <v>0</v>
+      </c>
+      <c r="H13" s="23">
+        <v>0</v>
+      </c>
+      <c r="I13" s="23">
+        <v>0</v>
+      </c>
+      <c r="J13" s="23">
+        <v>0</v>
+      </c>
+      <c r="K13" s="19">
         <v>3</v>
       </c>
-      <c r="L13" s="21" t="s">
+      <c r="L13" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="M13" s="21" t="s">
+      <c r="M13" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="N13" s="21"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="21"/>
-      <c r="W13" s="21" t="s">
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="X13" s="21" t="s">
+      <c r="X13" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
-      <c r="AA13" s="21"/>
-      <c r="AB13" s="21"/>
-      <c r="AC13" s="21"/>
-      <c r="AD13" s="21"/>
-      <c r="AE13" s="21"/>
-      <c r="AF13" s="21"/>
-      <c r="AG13" s="21"/>
-      <c r="AH13" s="21"/>
-      <c r="AI13" s="21"/>
-      <c r="AJ13" s="21"/>
-      <c r="AK13" s="21"/>
-      <c r="AL13" s="21"/>
-      <c r="AM13" s="21"/>
-      <c r="AN13" s="21"/>
-      <c r="AO13" s="21"/>
-      <c r="AP13" s="21"/>
-      <c r="AQ13" s="21"/>
-      <c r="AR13" s="21"/>
-      <c r="AS13" s="23" t="s">
+      <c r="Y13" s="19"/>
+      <c r="Z13" s="19"/>
+      <c r="AA13" s="19"/>
+      <c r="AB13" s="19"/>
+      <c r="AC13" s="19"/>
+      <c r="AD13" s="19"/>
+      <c r="AE13" s="19"/>
+      <c r="AF13" s="19"/>
+      <c r="AG13" s="19"/>
+      <c r="AH13" s="19"/>
+      <c r="AI13" s="19"/>
+      <c r="AJ13" s="19"/>
+      <c r="AK13" s="19"/>
+      <c r="AL13" s="19"/>
+      <c r="AM13" s="19"/>
+      <c r="AN13" s="19"/>
+      <c r="AO13" s="19"/>
+      <c r="AP13" s="19"/>
+      <c r="AQ13" s="19"/>
+      <c r="AR13" s="19"/>
+      <c r="AS13" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="AT13" s="21">
-        <v>0</v>
-      </c>
-      <c r="AU13" s="21"/>
-      <c r="AV13" s="21"/>
-      <c r="AW13" s="21"/>
-      <c r="AX13" s="21"/>
+      <c r="AT13" s="19">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="19"/>
+      <c r="AV13" s="19"/>
+      <c r="AW13" s="19"/>
+      <c r="AX13" s="19"/>
     </row>
     <row r="14" spans="1:50" ht="85" x14ac:dyDescent="0.45">
-      <c r="A14" s="21"/>
-      <c r="B14" s="21" t="s">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="D14" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="19">
         <v>50</v>
       </c>
-      <c r="F14" s="21">
-        <v>0</v>
-      </c>
-      <c r="G14" s="21">
-        <v>0</v>
-      </c>
-      <c r="H14" s="25">
-        <v>0</v>
-      </c>
-      <c r="I14" s="25">
-        <v>0</v>
-      </c>
-      <c r="J14" s="25">
-        <v>0</v>
-      </c>
-      <c r="K14" s="21">
+      <c r="F14" s="19">
+        <v>0</v>
+      </c>
+      <c r="G14" s="19">
+        <v>0</v>
+      </c>
+      <c r="H14" s="23">
+        <v>0</v>
+      </c>
+      <c r="I14" s="23">
+        <v>0</v>
+      </c>
+      <c r="J14" s="23">
+        <v>0</v>
+      </c>
+      <c r="K14" s="19">
         <v>2</v>
       </c>
-      <c r="L14" s="21" t="s">
+      <c r="L14" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="M14" s="21" t="s">
+      <c r="M14" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="N14" s="21"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="21"/>
-      <c r="R14" s="21"/>
-      <c r="S14" s="21"/>
-      <c r="T14" s="21"/>
-      <c r="U14" s="21"/>
-      <c r="V14" s="21"/>
-      <c r="W14" s="21" t="s">
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="X14" s="21" t="s">
+      <c r="X14" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="Y14" s="21"/>
-      <c r="Z14" s="21"/>
-      <c r="AA14" s="21"/>
-      <c r="AB14" s="21"/>
-      <c r="AC14" s="21"/>
-      <c r="AD14" s="21"/>
-      <c r="AE14" s="21"/>
-      <c r="AF14" s="21"/>
-      <c r="AG14" s="21"/>
-      <c r="AH14" s="21"/>
-      <c r="AI14" s="21"/>
-      <c r="AJ14" s="21"/>
-      <c r="AK14" s="21"/>
-      <c r="AL14" s="21"/>
-      <c r="AM14" s="21"/>
-      <c r="AN14" s="21"/>
-      <c r="AO14" s="21"/>
-      <c r="AP14" s="21"/>
-      <c r="AQ14" s="21"/>
-      <c r="AR14" s="21"/>
-      <c r="AS14" s="23" t="s">
+      <c r="Y14" s="19"/>
+      <c r="Z14" s="19"/>
+      <c r="AA14" s="19"/>
+      <c r="AB14" s="19"/>
+      <c r="AC14" s="19"/>
+      <c r="AD14" s="19"/>
+      <c r="AE14" s="19"/>
+      <c r="AF14" s="19"/>
+      <c r="AG14" s="19"/>
+      <c r="AH14" s="19"/>
+      <c r="AI14" s="19"/>
+      <c r="AJ14" s="19"/>
+      <c r="AK14" s="19"/>
+      <c r="AL14" s="19"/>
+      <c r="AM14" s="19"/>
+      <c r="AN14" s="19"/>
+      <c r="AO14" s="19"/>
+      <c r="AP14" s="19"/>
+      <c r="AQ14" s="19"/>
+      <c r="AR14" s="19"/>
+      <c r="AS14" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="AT14" s="21">
-        <v>0</v>
-      </c>
-      <c r="AU14" s="21"/>
-      <c r="AV14" s="21"/>
-      <c r="AW14" s="21"/>
-      <c r="AX14" s="21"/>
+      <c r="AT14" s="19">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="19"/>
+      <c r="AV14" s="19"/>
+      <c r="AW14" s="19"/>
+      <c r="AX14" s="19"/>
     </row>
     <row r="15" spans="1:50" ht="85" x14ac:dyDescent="0.45">
-      <c r="A15" s="21"/>
-      <c r="B15" s="21" t="s">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="19">
         <v>50</v>
       </c>
-      <c r="F15" s="21">
-        <v>0</v>
-      </c>
-      <c r="G15" s="21">
-        <v>0</v>
-      </c>
-      <c r="H15" s="25">
-        <v>0</v>
-      </c>
-      <c r="I15" s="25">
-        <v>0</v>
-      </c>
-      <c r="J15" s="25">
-        <v>0</v>
-      </c>
-      <c r="K15" s="21">
+      <c r="F15" s="19">
+        <v>0</v>
+      </c>
+      <c r="G15" s="19">
+        <v>0</v>
+      </c>
+      <c r="H15" s="23">
+        <v>0</v>
+      </c>
+      <c r="I15" s="23">
+        <v>0</v>
+      </c>
+      <c r="J15" s="23">
+        <v>0</v>
+      </c>
+      <c r="K15" s="19">
         <v>1</v>
       </c>
-      <c r="L15" s="21" t="s">
+      <c r="L15" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="M15" s="21" t="s">
+      <c r="M15" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="N15" s="21"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="21"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="21"/>
-      <c r="V15" s="21"/>
-      <c r="W15" s="21" t="s">
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="19"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="19"/>
+      <c r="U15" s="19"/>
+      <c r="V15" s="19"/>
+      <c r="W15" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="X15" s="21" t="s">
+      <c r="X15" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="Y15" s="21"/>
-      <c r="Z15" s="21"/>
-      <c r="AA15" s="21"/>
-      <c r="AB15" s="21"/>
-      <c r="AC15" s="21"/>
-      <c r="AD15" s="21"/>
-      <c r="AE15" s="21"/>
-      <c r="AF15" s="21"/>
-      <c r="AG15" s="21"/>
-      <c r="AH15" s="21"/>
-      <c r="AI15" s="21"/>
-      <c r="AJ15" s="21"/>
-      <c r="AK15" s="21"/>
-      <c r="AL15" s="21"/>
-      <c r="AM15" s="21"/>
-      <c r="AN15" s="21"/>
-      <c r="AO15" s="21"/>
-      <c r="AP15" s="21"/>
-      <c r="AQ15" s="21"/>
-      <c r="AR15" s="21"/>
-      <c r="AS15" s="23" t="s">
+      <c r="Y15" s="19"/>
+      <c r="Z15" s="19"/>
+      <c r="AA15" s="19"/>
+      <c r="AB15" s="19"/>
+      <c r="AC15" s="19"/>
+      <c r="AD15" s="19"/>
+      <c r="AE15" s="19"/>
+      <c r="AF15" s="19"/>
+      <c r="AG15" s="19"/>
+      <c r="AH15" s="19"/>
+      <c r="AI15" s="19"/>
+      <c r="AJ15" s="19"/>
+      <c r="AK15" s="19"/>
+      <c r="AL15" s="19"/>
+      <c r="AM15" s="19"/>
+      <c r="AN15" s="19"/>
+      <c r="AO15" s="19"/>
+      <c r="AP15" s="19"/>
+      <c r="AQ15" s="19"/>
+      <c r="AR15" s="19"/>
+      <c r="AS15" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="AT15" s="21">
-        <v>0</v>
-      </c>
-      <c r="AU15" s="21"/>
-      <c r="AV15" s="21"/>
-      <c r="AW15" s="21"/>
-      <c r="AX15" s="21"/>
+      <c r="AT15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AU15" s="19"/>
+      <c r="AV15" s="19"/>
+      <c r="AW15" s="19"/>
+      <c r="AX15" s="19"/>
     </row>
     <row r="16" spans="1:50" ht="85" x14ac:dyDescent="0.45">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21" t="s">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="19">
         <v>50</v>
       </c>
-      <c r="F16" s="21">
-        <v>0</v>
-      </c>
-      <c r="G16" s="21">
-        <v>0</v>
-      </c>
-      <c r="H16" s="25">
-        <v>0</v>
-      </c>
-      <c r="I16" s="25">
-        <v>0</v>
-      </c>
-      <c r="J16" s="25">
-        <v>0</v>
-      </c>
-      <c r="K16" s="21">
+      <c r="F16" s="19">
+        <v>0</v>
+      </c>
+      <c r="G16" s="19">
+        <v>0</v>
+      </c>
+      <c r="H16" s="23">
+        <v>0</v>
+      </c>
+      <c r="I16" s="23">
+        <v>0</v>
+      </c>
+      <c r="J16" s="23">
+        <v>0</v>
+      </c>
+      <c r="K16" s="19">
         <v>3</v>
       </c>
-      <c r="L16" s="21" t="s">
+      <c r="L16" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="M16" s="21" t="s">
+      <c r="M16" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="N16" s="21"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="21"/>
-      <c r="Q16" s="21"/>
-      <c r="R16" s="21"/>
-      <c r="S16" s="21"/>
-      <c r="T16" s="21"/>
-      <c r="U16" s="21"/>
-      <c r="V16" s="21"/>
-      <c r="W16" s="21" t="s">
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="19"/>
+      <c r="U16" s="19"/>
+      <c r="V16" s="19"/>
+      <c r="W16" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="X16" s="21" t="s">
+      <c r="X16" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="Y16" s="21"/>
-      <c r="Z16" s="21"/>
-      <c r="AA16" s="21"/>
-      <c r="AB16" s="21"/>
-      <c r="AC16" s="21"/>
-      <c r="AD16" s="21"/>
-      <c r="AE16" s="21"/>
-      <c r="AF16" s="21"/>
-      <c r="AG16" s="21"/>
-      <c r="AH16" s="21"/>
-      <c r="AI16" s="21"/>
-      <c r="AJ16" s="21"/>
-      <c r="AK16" s="21"/>
-      <c r="AL16" s="21"/>
-      <c r="AM16" s="21"/>
-      <c r="AN16" s="21"/>
-      <c r="AO16" s="21"/>
-      <c r="AP16" s="21"/>
-      <c r="AQ16" s="21"/>
-      <c r="AR16" s="21"/>
-      <c r="AS16" s="23" t="s">
+      <c r="Y16" s="19"/>
+      <c r="Z16" s="19"/>
+      <c r="AA16" s="19"/>
+      <c r="AB16" s="19"/>
+      <c r="AC16" s="19"/>
+      <c r="AD16" s="19"/>
+      <c r="AE16" s="19"/>
+      <c r="AF16" s="19"/>
+      <c r="AG16" s="19"/>
+      <c r="AH16" s="19"/>
+      <c r="AI16" s="19"/>
+      <c r="AJ16" s="19"/>
+      <c r="AK16" s="19"/>
+      <c r="AL16" s="19"/>
+      <c r="AM16" s="19"/>
+      <c r="AN16" s="19"/>
+      <c r="AO16" s="19"/>
+      <c r="AP16" s="19"/>
+      <c r="AQ16" s="19"/>
+      <c r="AR16" s="19"/>
+      <c r="AS16" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="AT16" s="21">
-        <v>0</v>
-      </c>
-      <c r="AU16" s="21"/>
-      <c r="AV16" s="21"/>
-      <c r="AW16" s="21"/>
-      <c r="AX16" s="21"/>
+      <c r="AT16" s="19">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="19"/>
+      <c r="AV16" s="19"/>
+      <c r="AW16" s="19"/>
+      <c r="AX16" s="19"/>
     </row>
     <row r="17" spans="1:50" ht="85" x14ac:dyDescent="0.45">
-      <c r="A17" s="21"/>
-      <c r="B17" s="21" t="s">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="19">
         <v>50</v>
       </c>
-      <c r="F17" s="21">
-        <v>0</v>
-      </c>
-      <c r="G17" s="21">
-        <v>0</v>
-      </c>
-      <c r="H17" s="25">
-        <v>0</v>
-      </c>
-      <c r="I17" s="25">
-        <v>0</v>
-      </c>
-      <c r="J17" s="25">
-        <v>0</v>
-      </c>
-      <c r="K17" s="21">
+      <c r="F17" s="19">
+        <v>0</v>
+      </c>
+      <c r="G17" s="19">
+        <v>0</v>
+      </c>
+      <c r="H17" s="23">
+        <v>0</v>
+      </c>
+      <c r="I17" s="23">
+        <v>0</v>
+      </c>
+      <c r="J17" s="23">
+        <v>0</v>
+      </c>
+      <c r="K17" s="19">
         <v>2</v>
       </c>
-      <c r="L17" s="21" t="s">
+      <c r="L17" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="M17" s="21" t="s">
+      <c r="M17" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="N17" s="21"/>
-      <c r="O17" s="21"/>
-      <c r="P17" s="21"/>
-      <c r="Q17" s="21"/>
-      <c r="R17" s="21"/>
-      <c r="S17" s="21"/>
-      <c r="T17" s="21"/>
-      <c r="U17" s="21"/>
-      <c r="V17" s="21"/>
-      <c r="W17" s="21" t="s">
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="19"/>
+      <c r="S17" s="19"/>
+      <c r="T17" s="19"/>
+      <c r="U17" s="19"/>
+      <c r="V17" s="19"/>
+      <c r="W17" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="X17" s="21" t="s">
+      <c r="X17" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="Y17" s="21"/>
-      <c r="Z17" s="21"/>
-      <c r="AA17" s="21"/>
-      <c r="AB17" s="21"/>
-      <c r="AC17" s="21"/>
-      <c r="AD17" s="21"/>
-      <c r="AE17" s="21"/>
-      <c r="AF17" s="21"/>
-      <c r="AG17" s="21"/>
-      <c r="AH17" s="21"/>
-      <c r="AI17" s="21"/>
-      <c r="AJ17" s="21"/>
-      <c r="AK17" s="21"/>
-      <c r="AL17" s="21"/>
-      <c r="AM17" s="21"/>
-      <c r="AN17" s="21"/>
-      <c r="AO17" s="21"/>
-      <c r="AP17" s="21"/>
-      <c r="AQ17" s="21"/>
-      <c r="AR17" s="21"/>
-      <c r="AS17" s="23" t="s">
+      <c r="Y17" s="19"/>
+      <c r="Z17" s="19"/>
+      <c r="AA17" s="19"/>
+      <c r="AB17" s="19"/>
+      <c r="AC17" s="19"/>
+      <c r="AD17" s="19"/>
+      <c r="AE17" s="19"/>
+      <c r="AF17" s="19"/>
+      <c r="AG17" s="19"/>
+      <c r="AH17" s="19"/>
+      <c r="AI17" s="19"/>
+      <c r="AJ17" s="19"/>
+      <c r="AK17" s="19"/>
+      <c r="AL17" s="19"/>
+      <c r="AM17" s="19"/>
+      <c r="AN17" s="19"/>
+      <c r="AO17" s="19"/>
+      <c r="AP17" s="19"/>
+      <c r="AQ17" s="19"/>
+      <c r="AR17" s="19"/>
+      <c r="AS17" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="AT17" s="21">
-        <v>0</v>
-      </c>
-      <c r="AU17" s="21"/>
-      <c r="AV17" s="21"/>
-      <c r="AW17" s="21"/>
-      <c r="AX17" s="21"/>
+      <c r="AT17" s="19">
+        <v>0</v>
+      </c>
+      <c r="AU17" s="19"/>
+      <c r="AV17" s="19"/>
+      <c r="AW17" s="19"/>
+      <c r="AX17" s="19"/>
     </row>
     <row r="18" spans="1:50" ht="85" x14ac:dyDescent="0.45">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21" t="s">
+      <c r="A18" s="19"/>
+      <c r="B18" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="19">
         <v>50</v>
       </c>
-      <c r="F18" s="21">
-        <v>0</v>
-      </c>
-      <c r="G18" s="21">
-        <v>0</v>
-      </c>
-      <c r="H18" s="25">
-        <v>0</v>
-      </c>
-      <c r="I18" s="25">
-        <v>0</v>
-      </c>
-      <c r="J18" s="25">
-        <v>0</v>
-      </c>
-      <c r="K18" s="21">
+      <c r="F18" s="19">
+        <v>0</v>
+      </c>
+      <c r="G18" s="19">
+        <v>0</v>
+      </c>
+      <c r="H18" s="23">
+        <v>0</v>
+      </c>
+      <c r="I18" s="23">
+        <v>0</v>
+      </c>
+      <c r="J18" s="23">
+        <v>0</v>
+      </c>
+      <c r="K18" s="19">
         <v>1</v>
       </c>
-      <c r="L18" s="21" t="s">
+      <c r="L18" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="M18" s="21" t="s">
+      <c r="M18" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="N18" s="21"/>
-      <c r="O18" s="21"/>
-      <c r="P18" s="21"/>
-      <c r="Q18" s="21"/>
-      <c r="R18" s="21"/>
-      <c r="S18" s="21"/>
-      <c r="T18" s="21"/>
-      <c r="U18" s="21"/>
-      <c r="V18" s="21"/>
-      <c r="W18" s="21" t="s">
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="19"/>
+      <c r="U18" s="19"/>
+      <c r="V18" s="19"/>
+      <c r="W18" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="X18" s="21" t="s">
+      <c r="X18" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="Y18" s="21"/>
-      <c r="Z18" s="21"/>
-      <c r="AA18" s="21"/>
-      <c r="AB18" s="21"/>
-      <c r="AC18" s="21"/>
-      <c r="AD18" s="21"/>
-      <c r="AE18" s="21"/>
-      <c r="AF18" s="21"/>
-      <c r="AG18" s="21"/>
-      <c r="AH18" s="21"/>
-      <c r="AI18" s="21"/>
-      <c r="AJ18" s="21"/>
-      <c r="AK18" s="21"/>
-      <c r="AL18" s="21"/>
-      <c r="AM18" s="21"/>
-      <c r="AN18" s="21"/>
-      <c r="AO18" s="21"/>
-      <c r="AP18" s="21"/>
-      <c r="AQ18" s="21"/>
-      <c r="AR18" s="21"/>
-      <c r="AS18" s="23" t="s">
+      <c r="Y18" s="19"/>
+      <c r="Z18" s="19"/>
+      <c r="AA18" s="19"/>
+      <c r="AB18" s="19"/>
+      <c r="AC18" s="19"/>
+      <c r="AD18" s="19"/>
+      <c r="AE18" s="19"/>
+      <c r="AF18" s="19"/>
+      <c r="AG18" s="19"/>
+      <c r="AH18" s="19"/>
+      <c r="AI18" s="19"/>
+      <c r="AJ18" s="19"/>
+      <c r="AK18" s="19"/>
+      <c r="AL18" s="19"/>
+      <c r="AM18" s="19"/>
+      <c r="AN18" s="19"/>
+      <c r="AO18" s="19"/>
+      <c r="AP18" s="19"/>
+      <c r="AQ18" s="19"/>
+      <c r="AR18" s="19"/>
+      <c r="AS18" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="AT18" s="21">
-        <v>0</v>
-      </c>
-      <c r="AU18" s="21"/>
-      <c r="AV18" s="21"/>
-      <c r="AW18" s="21"/>
-      <c r="AX18" s="21"/>
+      <c r="AT18" s="19">
+        <v>0</v>
+      </c>
+      <c r="AU18" s="19"/>
+      <c r="AV18" s="19"/>
+      <c r="AW18" s="19"/>
+      <c r="AX18" s="19"/>
     </row>
     <row r="19" spans="1:50" ht="85" x14ac:dyDescent="0.45">
-      <c r="A19" s="21"/>
-      <c r="B19" s="21" t="s">
+      <c r="A19" s="19"/>
+      <c r="B19" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="D19" s="21" t="s">
+      <c r="D19" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="19">
         <v>50</v>
       </c>
-      <c r="F19" s="21">
-        <v>0</v>
-      </c>
-      <c r="G19" s="21">
-        <v>0</v>
-      </c>
-      <c r="H19" s="25">
-        <v>0</v>
-      </c>
-      <c r="I19" s="25">
-        <v>0</v>
-      </c>
-      <c r="J19" s="25">
-        <v>0</v>
-      </c>
-      <c r="K19" s="21">
+      <c r="F19" s="19">
+        <v>0</v>
+      </c>
+      <c r="G19" s="19">
+        <v>0</v>
+      </c>
+      <c r="H19" s="23">
+        <v>0</v>
+      </c>
+      <c r="I19" s="23">
+        <v>0</v>
+      </c>
+      <c r="J19" s="23">
+        <v>0</v>
+      </c>
+      <c r="K19" s="19">
         <v>3</v>
       </c>
-      <c r="L19" s="21" t="s">
+      <c r="L19" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="M19" s="21" t="s">
+      <c r="M19" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="N19" s="21"/>
-      <c r="O19" s="21"/>
-      <c r="P19" s="21"/>
-      <c r="Q19" s="21"/>
-      <c r="R19" s="21"/>
-      <c r="S19" s="21"/>
-      <c r="T19" s="21"/>
-      <c r="U19" s="21"/>
-      <c r="V19" s="21"/>
-      <c r="W19" s="21" t="s">
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="19"/>
+      <c r="T19" s="19"/>
+      <c r="U19" s="19"/>
+      <c r="V19" s="19"/>
+      <c r="W19" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="X19" s="21" t="s">
+      <c r="X19" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="Y19" s="21"/>
-      <c r="Z19" s="21"/>
-      <c r="AA19" s="21"/>
-      <c r="AB19" s="21"/>
-      <c r="AC19" s="21"/>
-      <c r="AD19" s="21"/>
-      <c r="AE19" s="21"/>
-      <c r="AF19" s="21"/>
-      <c r="AG19" s="21"/>
-      <c r="AH19" s="21"/>
-      <c r="AI19" s="21"/>
-      <c r="AJ19" s="21"/>
-      <c r="AK19" s="21"/>
-      <c r="AL19" s="21"/>
-      <c r="AM19" s="21"/>
-      <c r="AN19" s="21"/>
-      <c r="AO19" s="21"/>
-      <c r="AP19" s="21"/>
-      <c r="AQ19" s="21"/>
-      <c r="AR19" s="21"/>
-      <c r="AS19" s="23" t="s">
+      <c r="Y19" s="19"/>
+      <c r="Z19" s="19"/>
+      <c r="AA19" s="19"/>
+      <c r="AB19" s="19"/>
+      <c r="AC19" s="19"/>
+      <c r="AD19" s="19"/>
+      <c r="AE19" s="19"/>
+      <c r="AF19" s="19"/>
+      <c r="AG19" s="19"/>
+      <c r="AH19" s="19"/>
+      <c r="AI19" s="19"/>
+      <c r="AJ19" s="19"/>
+      <c r="AK19" s="19"/>
+      <c r="AL19" s="19"/>
+      <c r="AM19" s="19"/>
+      <c r="AN19" s="19"/>
+      <c r="AO19" s="19"/>
+      <c r="AP19" s="19"/>
+      <c r="AQ19" s="19"/>
+      <c r="AR19" s="19"/>
+      <c r="AS19" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="AT19" s="21">
-        <v>0</v>
-      </c>
-      <c r="AU19" s="21"/>
-      <c r="AV19" s="21"/>
-      <c r="AW19" s="21"/>
-      <c r="AX19" s="21"/>
+      <c r="AT19" s="19">
+        <v>0</v>
+      </c>
+      <c r="AU19" s="19"/>
+      <c r="AV19" s="19"/>
+      <c r="AW19" s="19"/>
+      <c r="AX19" s="19"/>
     </row>
     <row r="20" spans="1:50" ht="85" x14ac:dyDescent="0.45">
-      <c r="A20" s="21"/>
-      <c r="B20" s="21" t="s">
+      <c r="A20" s="19"/>
+      <c r="B20" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="19">
         <v>50</v>
       </c>
-      <c r="F20" s="21">
-        <v>0</v>
-      </c>
-      <c r="G20" s="21">
-        <v>0</v>
-      </c>
-      <c r="H20" s="25">
-        <v>0</v>
-      </c>
-      <c r="I20" s="25">
-        <v>0</v>
-      </c>
-      <c r="J20" s="25">
-        <v>0</v>
-      </c>
-      <c r="K20" s="21">
+      <c r="F20" s="19">
+        <v>0</v>
+      </c>
+      <c r="G20" s="19">
+        <v>0</v>
+      </c>
+      <c r="H20" s="23">
+        <v>0</v>
+      </c>
+      <c r="I20" s="23">
+        <v>0</v>
+      </c>
+      <c r="J20" s="23">
+        <v>0</v>
+      </c>
+      <c r="K20" s="19">
         <v>2</v>
       </c>
-      <c r="L20" s="21" t="s">
+      <c r="L20" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="M20" s="21" t="s">
+      <c r="M20" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="N20" s="21"/>
-      <c r="O20" s="21"/>
-      <c r="P20" s="21"/>
-      <c r="Q20" s="21"/>
-      <c r="R20" s="21"/>
-      <c r="S20" s="21"/>
-      <c r="T20" s="21"/>
-      <c r="U20" s="21"/>
-      <c r="V20" s="21"/>
-      <c r="W20" s="21" t="s">
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19"/>
+      <c r="R20" s="19"/>
+      <c r="S20" s="19"/>
+      <c r="T20" s="19"/>
+      <c r="U20" s="19"/>
+      <c r="V20" s="19"/>
+      <c r="W20" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="X20" s="21" t="s">
+      <c r="X20" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="Y20" s="21"/>
-      <c r="Z20" s="21"/>
-      <c r="AA20" s="21"/>
-      <c r="AB20" s="21"/>
-      <c r="AC20" s="21"/>
-      <c r="AD20" s="21"/>
-      <c r="AE20" s="21"/>
-      <c r="AF20" s="21"/>
-      <c r="AG20" s="21"/>
-      <c r="AH20" s="21"/>
-      <c r="AI20" s="21"/>
-      <c r="AJ20" s="21"/>
-      <c r="AK20" s="21"/>
-      <c r="AL20" s="21"/>
-      <c r="AM20" s="21"/>
-      <c r="AN20" s="21"/>
-      <c r="AO20" s="21"/>
-      <c r="AP20" s="21"/>
-      <c r="AQ20" s="21"/>
-      <c r="AR20" s="21"/>
-      <c r="AS20" s="23" t="s">
+      <c r="Y20" s="19"/>
+      <c r="Z20" s="19"/>
+      <c r="AA20" s="19"/>
+      <c r="AB20" s="19"/>
+      <c r="AC20" s="19"/>
+      <c r="AD20" s="19"/>
+      <c r="AE20" s="19"/>
+      <c r="AF20" s="19"/>
+      <c r="AG20" s="19"/>
+      <c r="AH20" s="19"/>
+      <c r="AI20" s="19"/>
+      <c r="AJ20" s="19"/>
+      <c r="AK20" s="19"/>
+      <c r="AL20" s="19"/>
+      <c r="AM20" s="19"/>
+      <c r="AN20" s="19"/>
+      <c r="AO20" s="19"/>
+      <c r="AP20" s="19"/>
+      <c r="AQ20" s="19"/>
+      <c r="AR20" s="19"/>
+      <c r="AS20" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="AT20" s="21">
-        <v>0</v>
-      </c>
-      <c r="AU20" s="21"/>
-      <c r="AV20" s="21"/>
-      <c r="AW20" s="21"/>
-      <c r="AX20" s="21"/>
+      <c r="AT20" s="19">
+        <v>0</v>
+      </c>
+      <c r="AU20" s="19"/>
+      <c r="AV20" s="19"/>
+      <c r="AW20" s="19"/>
+      <c r="AX20" s="19"/>
     </row>
     <row r="21" spans="1:50" ht="85" x14ac:dyDescent="0.45">
-      <c r="A21" s="21"/>
-      <c r="B21" s="21" t="s">
+      <c r="A21" s="19"/>
+      <c r="B21" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="21" t="s">
+      <c r="D21" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="19">
         <v>50</v>
       </c>
-      <c r="F21" s="21">
-        <v>0</v>
-      </c>
-      <c r="G21" s="21">
-        <v>0</v>
-      </c>
-      <c r="H21" s="25">
-        <v>0</v>
-      </c>
-      <c r="I21" s="25">
-        <v>0</v>
-      </c>
-      <c r="J21" s="25">
-        <v>0</v>
-      </c>
-      <c r="K21" s="21">
+      <c r="F21" s="19">
+        <v>0</v>
+      </c>
+      <c r="G21" s="19">
+        <v>0</v>
+      </c>
+      <c r="H21" s="23">
+        <v>0</v>
+      </c>
+      <c r="I21" s="23">
+        <v>0</v>
+      </c>
+      <c r="J21" s="23">
+        <v>0</v>
+      </c>
+      <c r="K21" s="19">
         <v>1</v>
       </c>
-      <c r="L21" s="21" t="s">
+      <c r="L21" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="M21" s="21" t="s">
+      <c r="M21" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="N21" s="21"/>
-      <c r="O21" s="21"/>
-      <c r="P21" s="21"/>
-      <c r="Q21" s="21"/>
-      <c r="R21" s="21"/>
-      <c r="S21" s="21"/>
-      <c r="T21" s="21"/>
-      <c r="U21" s="21"/>
-      <c r="V21" s="21"/>
-      <c r="W21" s="21" t="s">
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="19"/>
+      <c r="R21" s="19"/>
+      <c r="S21" s="19"/>
+      <c r="T21" s="19"/>
+      <c r="U21" s="19"/>
+      <c r="V21" s="19"/>
+      <c r="W21" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="X21" s="21" t="s">
+      <c r="X21" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="Y21" s="21"/>
-      <c r="Z21" s="21"/>
-      <c r="AA21" s="21"/>
-      <c r="AB21" s="21"/>
-      <c r="AC21" s="21"/>
-      <c r="AD21" s="21"/>
-      <c r="AE21" s="21"/>
-      <c r="AF21" s="21"/>
-      <c r="AG21" s="21"/>
-      <c r="AH21" s="21"/>
-      <c r="AI21" s="21"/>
-      <c r="AJ21" s="21"/>
-      <c r="AK21" s="21"/>
-      <c r="AL21" s="21"/>
-      <c r="AM21" s="21"/>
-      <c r="AN21" s="21"/>
-      <c r="AO21" s="21"/>
-      <c r="AP21" s="21"/>
-      <c r="AQ21" s="21"/>
-      <c r="AR21" s="21"/>
-      <c r="AS21" s="23" t="s">
+      <c r="Y21" s="19"/>
+      <c r="Z21" s="19"/>
+      <c r="AA21" s="19"/>
+      <c r="AB21" s="19"/>
+      <c r="AC21" s="19"/>
+      <c r="AD21" s="19"/>
+      <c r="AE21" s="19"/>
+      <c r="AF21" s="19"/>
+      <c r="AG21" s="19"/>
+      <c r="AH21" s="19"/>
+      <c r="AI21" s="19"/>
+      <c r="AJ21" s="19"/>
+      <c r="AK21" s="19"/>
+      <c r="AL21" s="19"/>
+      <c r="AM21" s="19"/>
+      <c r="AN21" s="19"/>
+      <c r="AO21" s="19"/>
+      <c r="AP21" s="19"/>
+      <c r="AQ21" s="19"/>
+      <c r="AR21" s="19"/>
+      <c r="AS21" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="AT21" s="21">
-        <v>0</v>
-      </c>
-      <c r="AU21" s="21"/>
-      <c r="AV21" s="21"/>
-      <c r="AW21" s="21"/>
-      <c r="AX21" s="21"/>
+      <c r="AT21" s="19">
+        <v>0</v>
+      </c>
+      <c r="AU21" s="19"/>
+      <c r="AV21" s="19"/>
+      <c r="AW21" s="19"/>
+      <c r="AX21" s="19"/>
     </row>
     <row r="22" spans="1:50" ht="204" x14ac:dyDescent="0.45">
-      <c r="A22" s="21"/>
-      <c r="B22" s="21" t="s">
+      <c r="A22" s="19"/>
+      <c r="B22" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="D22" s="21" t="s">
+      <c r="D22" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="32">
         <v>200</v>
       </c>
-      <c r="F22" s="34">
+      <c r="F22" s="32">
         <v>18</v>
       </c>
-      <c r="G22" s="34">
+      <c r="G22" s="32">
         <v>25</v>
       </c>
-      <c r="H22" s="26">
+      <c r="H22" s="24">
         <v>0.25</v>
       </c>
-      <c r="I22" s="26">
+      <c r="I22" s="24">
         <v>0.1</v>
       </c>
-      <c r="J22" s="26">
+      <c r="J22" s="24">
         <v>0.2</v>
       </c>
-      <c r="K22" s="21">
-        <v>0</v>
-      </c>
-      <c r="L22" s="21" t="s">
+      <c r="K22" s="19">
+        <v>0</v>
+      </c>
+      <c r="L22" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="M22" s="21" t="s">
+      <c r="M22" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="N22" s="21">
-        <v>0</v>
-      </c>
-      <c r="O22" s="21">
+      <c r="N22" s="19">
+        <v>0</v>
+      </c>
+      <c r="O22" s="19">
         <v>1</v>
       </c>
-      <c r="P22" s="21">
+      <c r="P22" s="19">
         <v>1</v>
       </c>
-      <c r="Q22" s="21">
+      <c r="Q22" s="19">
         <v>1</v>
       </c>
-      <c r="R22" s="21">
+      <c r="R22" s="19">
         <v>9</v>
       </c>
-      <c r="S22" s="21">
-        <v>0</v>
-      </c>
-      <c r="T22" s="21"/>
-      <c r="U22" s="24">
+      <c r="S22" s="19">
+        <v>0</v>
+      </c>
+      <c r="T22" s="19"/>
+      <c r="U22" s="22">
         <v>1.20000004768372</v>
       </c>
-      <c r="V22" s="24">
+      <c r="V22" s="22">
         <v>1.2</v>
       </c>
-      <c r="W22" s="21" t="s">
+      <c r="W22" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="X22" s="21" t="s">
+      <c r="X22" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="Y22" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="21">
+      <c r="Y22" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="19">
         <v>1</v>
       </c>
-      <c r="AA22" s="21">
+      <c r="AA22" s="19">
         <v>1</v>
       </c>
-      <c r="AB22" s="21">
+      <c r="AB22" s="19">
         <v>1</v>
       </c>
-      <c r="AC22" s="21">
+      <c r="AC22" s="19">
         <v>2</v>
       </c>
-      <c r="AD22" s="21">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="21" t="s">
+      <c r="AD22" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="AF22" s="24">
+      <c r="AF22" s="22">
         <v>1.8</v>
       </c>
-      <c r="AG22" s="24">
+      <c r="AG22" s="22">
         <v>1.8</v>
       </c>
-      <c r="AH22" s="21" t="s">
+      <c r="AH22" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="AI22" s="23" t="s">
+      <c r="AI22" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="AJ22" s="21"/>
-      <c r="AK22" s="21"/>
-      <c r="AL22" s="21"/>
-      <c r="AM22" s="21"/>
-      <c r="AN22" s="21"/>
-      <c r="AO22" s="21"/>
-      <c r="AP22" s="21"/>
-      <c r="AQ22" s="27">
+      <c r="AJ22" s="19"/>
+      <c r="AK22" s="19"/>
+      <c r="AL22" s="19"/>
+      <c r="AM22" s="19"/>
+      <c r="AN22" s="19"/>
+      <c r="AO22" s="19"/>
+      <c r="AP22" s="19"/>
+      <c r="AQ22" s="25">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AR22" s="27">
+      <c r="AR22" s="25">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AS22" s="23" t="s">
+      <c r="AS22" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="AT22" s="21"/>
-      <c r="AU22" s="21"/>
-      <c r="AV22" s="21"/>
-      <c r="AW22" s="21"/>
-      <c r="AX22" s="21"/>
+      <c r="AT22" s="19"/>
+      <c r="AU22" s="19"/>
+      <c r="AV22" s="19"/>
+      <c r="AW22" s="19"/>
+      <c r="AX22" s="19"/>
     </row>
     <row r="23" spans="1:50" ht="357" x14ac:dyDescent="0.45">
-      <c r="A23" s="21"/>
-      <c r="B23" s="21" t="s">
+      <c r="A23" s="19"/>
+      <c r="B23" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="D23" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="E23" s="34">
+      <c r="E23" s="32">
         <v>80</v>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="19">
         <v>15</v>
       </c>
-      <c r="G23" s="21">
+      <c r="G23" s="19">
         <v>20</v>
       </c>
-      <c r="H23" s="26">
+      <c r="H23" s="24">
         <v>0.2</v>
       </c>
-      <c r="I23" s="26">
-        <v>0</v>
-      </c>
-      <c r="J23" s="26">
-        <v>0</v>
-      </c>
-      <c r="K23" s="21">
+      <c r="I23" s="24">
+        <v>0</v>
+      </c>
+      <c r="J23" s="24">
+        <v>0</v>
+      </c>
+      <c r="K23" s="19">
         <v>3</v>
       </c>
-      <c r="L23" s="21" t="s">
+      <c r="L23" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="M23" s="21" t="s">
+      <c r="M23" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="N23" s="21"/>
-      <c r="O23" s="21"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="21"/>
-      <c r="R23" s="21"/>
-      <c r="S23" s="21"/>
-      <c r="T23" s="21"/>
-      <c r="U23" s="24"/>
-      <c r="V23" s="24"/>
-      <c r="W23" s="21" t="s">
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
+      <c r="R23" s="19"/>
+      <c r="S23" s="19"/>
+      <c r="T23" s="19"/>
+      <c r="U23" s="22"/>
+      <c r="V23" s="22"/>
+      <c r="W23" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="X23" s="21" t="s">
+      <c r="X23" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="Y23" s="21"/>
-      <c r="Z23" s="21"/>
-      <c r="AA23" s="21"/>
-      <c r="AB23" s="21"/>
-      <c r="AC23" s="21"/>
-      <c r="AD23" s="21"/>
-      <c r="AE23" s="21"/>
-      <c r="AF23" s="24"/>
-      <c r="AG23" s="24"/>
-      <c r="AH23" s="21" t="s">
+      <c r="Y23" s="19"/>
+      <c r="Z23" s="19"/>
+      <c r="AA23" s="19"/>
+      <c r="AB23" s="19"/>
+      <c r="AC23" s="19"/>
+      <c r="AD23" s="19"/>
+      <c r="AE23" s="19"/>
+      <c r="AF23" s="22"/>
+      <c r="AG23" s="22"/>
+      <c r="AH23" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="AI23" s="21" t="s">
+      <c r="AI23" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="AJ23" s="21">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="21">
+      <c r="AJ23" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="19">
         <v>1</v>
       </c>
-      <c r="AL23" s="21">
+      <c r="AL23" s="19">
         <v>1</v>
       </c>
-      <c r="AM23" s="21">
+      <c r="AM23" s="19">
         <v>1</v>
       </c>
-      <c r="AN23" s="21">
+      <c r="AN23" s="19">
         <v>9</v>
       </c>
-      <c r="AO23" s="21">
-        <v>0</v>
-      </c>
-      <c r="AP23" s="21"/>
-      <c r="AQ23" s="24">
+      <c r="AO23" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP23" s="19"/>
+      <c r="AQ23" s="22">
         <v>1.20000004768372</v>
       </c>
-      <c r="AR23" s="24">
+      <c r="AR23" s="22">
         <v>1.2</v>
       </c>
-      <c r="AS23" s="23" t="s">
+      <c r="AS23" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="AT23" s="21"/>
-      <c r="AU23" s="21"/>
-      <c r="AV23" s="21"/>
-      <c r="AW23" s="21"/>
-      <c r="AX23" s="21"/>
+      <c r="AT23" s="19"/>
+      <c r="AU23" s="19"/>
+      <c r="AV23" s="19"/>
+      <c r="AW23" s="19"/>
+      <c r="AX23" s="19"/>
     </row>
     <row r="24" spans="1:50" ht="374" x14ac:dyDescent="0.45">
-      <c r="A24" s="21"/>
-      <c r="B24" s="21" t="s">
+      <c r="A24" s="19"/>
+      <c r="B24" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="D24" s="21" t="s">
+      <c r="D24" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="32">
         <v>80</v>
       </c>
-      <c r="F24" s="21">
+      <c r="F24" s="19">
         <v>15</v>
       </c>
-      <c r="G24" s="21">
+      <c r="G24" s="19">
         <v>20</v>
       </c>
-      <c r="H24" s="26">
+      <c r="H24" s="24">
         <v>0.2</v>
       </c>
-      <c r="I24" s="26">
-        <v>0</v>
-      </c>
-      <c r="J24" s="26">
-        <v>0</v>
-      </c>
-      <c r="K24" s="21">
+      <c r="I24" s="24">
+        <v>0</v>
+      </c>
+      <c r="J24" s="24">
+        <v>0</v>
+      </c>
+      <c r="K24" s="19">
         <v>2</v>
       </c>
-      <c r="L24" s="21" t="s">
+      <c r="L24" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="M24" s="21" t="s">
+      <c r="M24" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="N24" s="21"/>
-      <c r="O24" s="21"/>
-      <c r="P24" s="21"/>
-      <c r="Q24" s="21"/>
-      <c r="R24" s="21"/>
-      <c r="S24" s="21"/>
-      <c r="T24" s="21"/>
-      <c r="U24" s="24"/>
-      <c r="V24" s="24"/>
-      <c r="W24" s="21" t="s">
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="19"/>
+      <c r="S24" s="19"/>
+      <c r="T24" s="19"/>
+      <c r="U24" s="22"/>
+      <c r="V24" s="22"/>
+      <c r="W24" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="X24" s="21" t="s">
+      <c r="X24" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="Y24" s="21"/>
-      <c r="Z24" s="21"/>
-      <c r="AA24" s="21"/>
-      <c r="AB24" s="21"/>
-      <c r="AC24" s="21"/>
-      <c r="AD24" s="21"/>
-      <c r="AE24" s="21"/>
-      <c r="AF24" s="24"/>
-      <c r="AG24" s="24"/>
-      <c r="AH24" s="21" t="s">
+      <c r="Y24" s="19"/>
+      <c r="Z24" s="19"/>
+      <c r="AA24" s="19"/>
+      <c r="AB24" s="19"/>
+      <c r="AC24" s="19"/>
+      <c r="AD24" s="19"/>
+      <c r="AE24" s="19"/>
+      <c r="AF24" s="22"/>
+      <c r="AG24" s="22"/>
+      <c r="AH24" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="AI24" s="21" t="s">
+      <c r="AI24" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="AJ24" s="21">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="21">
+      <c r="AJ24" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="19">
         <v>1</v>
       </c>
-      <c r="AL24" s="21">
+      <c r="AL24" s="19">
         <v>1</v>
       </c>
-      <c r="AM24" s="21">
+      <c r="AM24" s="19">
         <v>1</v>
       </c>
-      <c r="AN24" s="21">
+      <c r="AN24" s="19">
         <v>2</v>
       </c>
-      <c r="AO24" s="21">
-        <v>0</v>
-      </c>
-      <c r="AP24" s="21" t="s">
+      <c r="AO24" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP24" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="AQ24" s="24">
+      <c r="AQ24" s="22">
         <v>1.8</v>
       </c>
-      <c r="AR24" s="24">
+      <c r="AR24" s="22">
         <v>1.8</v>
       </c>
-      <c r="AS24" s="23" t="s">
+      <c r="AS24" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="AT24" s="21"/>
-      <c r="AU24" s="21"/>
-      <c r="AV24" s="21"/>
-      <c r="AW24" s="21"/>
-      <c r="AX24" s="21"/>
+      <c r="AT24" s="19"/>
+      <c r="AU24" s="19"/>
+      <c r="AV24" s="19"/>
+      <c r="AW24" s="19"/>
+      <c r="AX24" s="19"/>
     </row>
     <row r="25" spans="1:50" ht="170" x14ac:dyDescent="0.45">
-      <c r="A25" s="21"/>
-      <c r="B25" s="21" t="s">
+      <c r="A25" s="19"/>
+      <c r="B25" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C25" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="D25" s="21" t="s">
+      <c r="D25" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="E25" s="34">
+      <c r="E25" s="32">
         <v>200</v>
       </c>
-      <c r="F25" s="21">
+      <c r="F25" s="19">
         <v>15</v>
       </c>
-      <c r="G25" s="34">
+      <c r="G25" s="32">
         <v>25</v>
       </c>
-      <c r="H25" s="26">
+      <c r="H25" s="24">
         <v>0.25</v>
       </c>
-      <c r="I25" s="26">
+      <c r="I25" s="24">
         <v>0.1</v>
       </c>
-      <c r="J25" s="26">
+      <c r="J25" s="24">
         <v>0.2</v>
       </c>
-      <c r="K25" s="21">
-        <v>0</v>
-      </c>
-      <c r="L25" s="21" t="s">
+      <c r="K25" s="19">
+        <v>0</v>
+      </c>
+      <c r="L25" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="M25" s="21" t="s">
+      <c r="M25" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="N25" s="21"/>
-      <c r="O25" s="21"/>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="21"/>
-      <c r="R25" s="21"/>
-      <c r="S25" s="21"/>
-      <c r="T25" s="21"/>
-      <c r="U25" s="24">
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="22">
         <v>2.2999999999999998</v>
       </c>
-      <c r="V25" s="24">
+      <c r="V25" s="22">
         <v>2.2999999999999998</v>
       </c>
-      <c r="W25" s="21"/>
-      <c r="X25" s="21"/>
-      <c r="Y25" s="21"/>
-      <c r="Z25" s="21"/>
-      <c r="AA25" s="21"/>
-      <c r="AB25" s="21"/>
-      <c r="AC25" s="21"/>
-      <c r="AD25" s="21"/>
-      <c r="AE25" s="21"/>
-      <c r="AF25" s="24"/>
-      <c r="AG25" s="24"/>
-      <c r="AH25" s="21"/>
-      <c r="AI25" s="23"/>
-      <c r="AJ25" s="21"/>
-      <c r="AK25" s="21"/>
-      <c r="AL25" s="21"/>
-      <c r="AM25" s="21"/>
-      <c r="AN25" s="21"/>
-      <c r="AO25" s="21"/>
-      <c r="AP25" s="21"/>
-      <c r="AQ25" s="27"/>
-      <c r="AR25" s="27"/>
-      <c r="AS25" s="23" t="s">
+      <c r="W25" s="19"/>
+      <c r="X25" s="19"/>
+      <c r="Y25" s="19"/>
+      <c r="Z25" s="19"/>
+      <c r="AA25" s="19"/>
+      <c r="AB25" s="19"/>
+      <c r="AC25" s="19"/>
+      <c r="AD25" s="19"/>
+      <c r="AE25" s="19"/>
+      <c r="AF25" s="22"/>
+      <c r="AG25" s="22"/>
+      <c r="AH25" s="19"/>
+      <c r="AI25" s="21"/>
+      <c r="AJ25" s="19"/>
+      <c r="AK25" s="19"/>
+      <c r="AL25" s="19"/>
+      <c r="AM25" s="19"/>
+      <c r="AN25" s="19"/>
+      <c r="AO25" s="19"/>
+      <c r="AP25" s="19"/>
+      <c r="AQ25" s="25"/>
+      <c r="AR25" s="25"/>
+      <c r="AS25" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="AT25" s="21"/>
-      <c r="AU25" s="21"/>
-      <c r="AV25" s="21"/>
-      <c r="AW25" s="21"/>
-      <c r="AX25" s="21"/>
+      <c r="AT25" s="19"/>
+      <c r="AU25" s="19"/>
+      <c r="AV25" s="19"/>
+      <c r="AW25" s="19"/>
+      <c r="AX25" s="19"/>
     </row>
     <row r="26" spans="1:50" ht="170" x14ac:dyDescent="0.45">
-      <c r="A26" s="21"/>
-      <c r="B26" s="28" t="s">
+      <c r="A26" s="19"/>
+      <c r="B26" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="D26" s="28" t="s">
+      <c r="D26" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="E26" s="28">
+      <c r="E26" s="26">
         <v>30</v>
       </c>
-      <c r="F26" s="35">
+      <c r="F26" s="33">
         <v>18</v>
       </c>
-      <c r="G26" s="28">
+      <c r="G26" s="26">
         <v>10</v>
       </c>
-      <c r="H26" s="29">
-        <v>0</v>
-      </c>
-      <c r="I26" s="29">
-        <v>0</v>
-      </c>
-      <c r="J26" s="29">
-        <v>0</v>
-      </c>
-      <c r="K26" s="21">
+      <c r="H26" s="27">
+        <v>0</v>
+      </c>
+      <c r="I26" s="27">
+        <v>0</v>
+      </c>
+      <c r="J26" s="27">
+        <v>0</v>
+      </c>
+      <c r="K26" s="19">
         <v>1</v>
       </c>
-      <c r="L26" s="28" t="s">
+      <c r="L26" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="M26" s="28" t="s">
+      <c r="M26" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="N26" s="28">
-        <v>0</v>
-      </c>
-      <c r="O26" s="28">
+      <c r="N26" s="26">
+        <v>0</v>
+      </c>
+      <c r="O26" s="26">
         <v>1</v>
       </c>
-      <c r="P26" s="28">
+      <c r="P26" s="26">
         <v>1</v>
       </c>
-      <c r="Q26" s="28">
+      <c r="Q26" s="26">
         <v>1</v>
       </c>
-      <c r="R26" s="28">
+      <c r="R26" s="26">
         <v>2</v>
       </c>
-      <c r="S26" s="28">
-        <v>0</v>
-      </c>
-      <c r="T26" s="30" t="s">
+      <c r="S26" s="26">
+        <v>0</v>
+      </c>
+      <c r="T26" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="U26" s="31">
+      <c r="U26" s="29">
         <v>2.2999999999999998</v>
       </c>
-      <c r="V26" s="31">
+      <c r="V26" s="29">
         <v>2.2999999999999998</v>
       </c>
-      <c r="W26" s="28"/>
-      <c r="X26" s="28"/>
-      <c r="Y26" s="28"/>
-      <c r="Z26" s="28"/>
-      <c r="AA26" s="28"/>
-      <c r="AB26" s="28"/>
-      <c r="AC26" s="28"/>
-      <c r="AD26" s="28"/>
-      <c r="AE26" s="28"/>
-      <c r="AF26" s="31"/>
-      <c r="AG26" s="31"/>
-      <c r="AH26" s="28"/>
-      <c r="AI26" s="32"/>
-      <c r="AJ26" s="30"/>
-      <c r="AK26" s="30"/>
-      <c r="AL26" s="30"/>
-      <c r="AM26" s="30"/>
-      <c r="AN26" s="30"/>
-      <c r="AO26" s="30"/>
-      <c r="AP26" s="30"/>
-      <c r="AQ26" s="33"/>
-      <c r="AR26" s="33"/>
-      <c r="AS26" s="32" t="s">
+      <c r="W26" s="26"/>
+      <c r="X26" s="26"/>
+      <c r="Y26" s="26"/>
+      <c r="Z26" s="26"/>
+      <c r="AA26" s="26"/>
+      <c r="AB26" s="26"/>
+      <c r="AC26" s="26"/>
+      <c r="AD26" s="26"/>
+      <c r="AE26" s="26"/>
+      <c r="AF26" s="29"/>
+      <c r="AG26" s="29"/>
+      <c r="AH26" s="26"/>
+      <c r="AI26" s="30"/>
+      <c r="AJ26" s="28"/>
+      <c r="AK26" s="28"/>
+      <c r="AL26" s="28"/>
+      <c r="AM26" s="28"/>
+      <c r="AN26" s="28"/>
+      <c r="AO26" s="28"/>
+      <c r="AP26" s="28"/>
+      <c r="AQ26" s="31"/>
+      <c r="AR26" s="31"/>
+      <c r="AS26" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="AT26" s="30"/>
-      <c r="AU26" s="30"/>
-      <c r="AV26" s="30"/>
-      <c r="AW26" s="30"/>
-      <c r="AX26" s="30"/>
+      <c r="AT26" s="28"/>
+      <c r="AU26" s="28"/>
+      <c r="AV26" s="28"/>
+      <c r="AW26" s="28"/>
+      <c r="AX26" s="28"/>
     </row>
     <row r="27" spans="1:50" ht="102" x14ac:dyDescent="0.45">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="C27" s="21" t="s">
+      <c r="C27" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="D27" s="21" t="s">
+      <c r="D27" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="E27" s="21" t="s">
+      <c r="E27" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="F27" s="21" t="s">
+      <c r="F27" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="G27" s="21" t="s">
+      <c r="G27" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="H27" s="21" t="s">
+      <c r="H27" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="I27" s="21" t="s">
+      <c r="I27" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="J27" s="21" t="s">
+      <c r="J27" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="K27" s="21" t="s">
+      <c r="K27" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="L27" s="21" t="s">
+      <c r="L27" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="M27" s="21" t="s">
+      <c r="M27" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="N27" s="23" t="s">
+      <c r="N27" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="O27" s="21" t="s">
+      <c r="O27" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="P27" s="21" t="s">
+      <c r="P27" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="Q27" s="21" t="s">
+      <c r="Q27" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="R27" s="21" t="s">
+      <c r="R27" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="S27" s="21" t="s">
+      <c r="S27" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="T27" s="21" t="s">
+      <c r="T27" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="U27" s="21" t="s">
+      <c r="U27" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="V27" s="21" t="s">
+      <c r="V27" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="W27" s="21" t="s">
+      <c r="W27" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="X27" s="21" t="s">
+      <c r="X27" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="Y27" s="21" t="s">
+      <c r="Y27" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="Z27" s="21" t="s">
+      <c r="Z27" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="AA27" s="21" t="s">
+      <c r="AA27" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="AB27" s="21" t="s">
+      <c r="AB27" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="AC27" s="21" t="s">
+      <c r="AC27" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="AD27" s="21" t="s">
+      <c r="AD27" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="AE27" s="21" t="s">
+      <c r="AE27" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="AF27" s="21" t="s">
+      <c r="AF27" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="AG27" s="21" t="s">
+      <c r="AG27" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="AH27" s="21" t="s">
+      <c r="AH27" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="AI27" s="23" t="s">
+      <c r="AI27" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="AJ27" s="23" t="s">
+      <c r="AJ27" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="AK27" s="23" t="s">
+      <c r="AK27" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="AL27" s="23" t="s">
+      <c r="AL27" s="21" t="s">
         <v>211</v>
       </c>
-      <c r="AM27" s="23" t="s">
+      <c r="AM27" s="21" t="s">
         <v>212</v>
       </c>
-      <c r="AN27" s="23" t="s">
+      <c r="AN27" s="21" t="s">
         <v>213</v>
       </c>
-      <c r="AO27" s="23" t="s">
+      <c r="AO27" s="21" t="s">
         <v>214</v>
       </c>
-      <c r="AP27" s="23" t="s">
+      <c r="AP27" s="21" t="s">
         <v>215</v>
       </c>
-      <c r="AQ27" s="21" t="s">
+      <c r="AQ27" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="AR27" s="21" t="s">
+      <c r="AR27" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="AS27" s="21" t="s">
+      <c r="AS27" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="AT27" s="21" t="s">
+      <c r="AT27" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="AU27" s="21" t="s">
+      <c r="AU27" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="AV27" s="21" t="s">
+      <c r="AV27" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="AW27" s="21" t="s">
+      <c r="AW27" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="AX27" s="21" t="s">
+      <c r="AX27" s="19" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:50" x14ac:dyDescent="0.45">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
-      <c r="O28" s="21"/>
-      <c r="P28" s="21"/>
-      <c r="Q28" s="21"/>
-      <c r="R28" s="21"/>
-      <c r="S28" s="21"/>
-      <c r="T28" s="21"/>
-      <c r="U28" s="21"/>
-      <c r="V28" s="21"/>
-      <c r="W28" s="21"/>
-      <c r="X28" s="21"/>
-      <c r="Y28" s="21"/>
-      <c r="Z28" s="21"/>
-      <c r="AA28" s="21"/>
-      <c r="AB28" s="21"/>
-      <c r="AC28" s="21"/>
-      <c r="AD28" s="21"/>
-      <c r="AE28" s="21"/>
-      <c r="AF28" s="21"/>
-      <c r="AG28" s="21"/>
-      <c r="AH28" s="21"/>
-      <c r="AI28" s="21"/>
-      <c r="AJ28" s="21"/>
-      <c r="AK28" s="21"/>
-      <c r="AL28" s="21"/>
-      <c r="AM28" s="21"/>
-      <c r="AN28" s="21"/>
-      <c r="AO28" s="21"/>
-      <c r="AP28" s="21"/>
-      <c r="AQ28" s="21"/>
-      <c r="AR28" s="21"/>
-      <c r="AS28" s="21"/>
-      <c r="AT28" s="21"/>
-      <c r="AU28" s="21"/>
-      <c r="AV28" s="21"/>
-      <c r="AW28" s="21"/>
-      <c r="AX28" s="21"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="19"/>
+      <c r="Y28" s="19"/>
+      <c r="Z28" s="19"/>
+      <c r="AA28" s="19"/>
+      <c r="AB28" s="19"/>
+      <c r="AC28" s="19"/>
+      <c r="AD28" s="19"/>
+      <c r="AE28" s="19"/>
+      <c r="AF28" s="19"/>
+      <c r="AG28" s="19"/>
+      <c r="AH28" s="19"/>
+      <c r="AI28" s="19"/>
+      <c r="AJ28" s="19"/>
+      <c r="AK28" s="19"/>
+      <c r="AL28" s="19"/>
+      <c r="AM28" s="19"/>
+      <c r="AN28" s="19"/>
+      <c r="AO28" s="19"/>
+      <c r="AP28" s="19"/>
+      <c r="AQ28" s="19"/>
+      <c r="AR28" s="19"/>
+      <c r="AS28" s="19"/>
+      <c r="AT28" s="19"/>
+      <c r="AU28" s="19"/>
+      <c r="AV28" s="19"/>
+      <c r="AW28" s="19"/>
+      <c r="AX28" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5109,11 +5131,11 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="35" t="s">
         <v>223</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4" s="12" t="s">

--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/2구역 전투 테이블 V1.3.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/2구역 전투 테이블 V1.3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200016\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\개인\게임인재원 7기\Hero Influence\기획서\Hero Influence_강현재\밸런스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6135E0A7-F29C-4263-AD6B-13BA913DDCC2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14546355-506E-48ED-9D28-345DDBDFBD24}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14300" yWindow="0" windowWidth="14610" windowHeight="15590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="295">
   <si>
     <t>2구역 메인/서브 이벤트 전투 테이블</t>
   </si>
@@ -1104,6 +1104,26 @@
   </si>
   <si>
     <t>드론 공격력 조정</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>V1.5</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 부대 추가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FV20001</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>V1.6</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>보스 스테이터스 밸런스</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1191,7 +1211,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1211,11 +1231,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -1285,40 +1300,14 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="6" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="5" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="5" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="5" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="5" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1327,16 +1316,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="5" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="5" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="5" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="5" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
@@ -1372,16 +1355,42 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="5" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="6" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="5" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="5" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="5" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2298,7 +2307,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="9.5" customWidth="1"/>
@@ -2319,7 +2328,7 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="2">
         <v>46293</v>
       </c>
       <c r="C3" t="s">
@@ -2333,10 +2342,10 @@
       <c r="A4" t="s">
         <v>254</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="2">
         <v>46295</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="1" t="s">
         <v>255</v>
       </c>
       <c r="D4" t="s">
@@ -2344,44 +2353,72 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="2">
         <v>46295</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="3" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="2">
         <v>46297</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="3" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="2">
         <v>46297</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B8" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B9" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>286</v>
       </c>
     </row>
@@ -2446,2653 +2483,2653 @@
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.45">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="34"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
     </row>
     <row r="4" spans="1:50" x14ac:dyDescent="0.45">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="19" t="s">
+      <c r="I4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="19" t="s">
+      <c r="J4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="19" t="s">
+      <c r="L4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="19" t="s">
+      <c r="M4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="20" t="s">
+      <c r="N4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="O4" s="20" t="s">
+      <c r="O4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="20" t="s">
+      <c r="P4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="20" t="s">
+      <c r="Q4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="R4" s="20" t="s">
+      <c r="R4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="S4" s="20" t="s">
+      <c r="S4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="T4" s="20" t="s">
+      <c r="T4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="U4" s="20" t="s">
+      <c r="U4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="20" t="s">
+      <c r="V4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="W4" s="19" t="s">
+      <c r="W4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="X4" s="19" t="s">
+      <c r="X4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="Y4" s="20" t="s">
+      <c r="Y4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="Z4" s="20" t="s">
+      <c r="Z4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AA4" s="20" t="s">
+      <c r="AA4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AB4" s="20" t="s">
+      <c r="AB4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AC4" s="20" t="s">
+      <c r="AC4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="AD4" s="20" t="s">
+      <c r="AD4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AE4" s="20" t="s">
+      <c r="AE4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AF4" s="20" t="s">
+      <c r="AF4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="AG4" s="20" t="s">
+      <c r="AG4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="AH4" s="19" t="s">
+      <c r="AH4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="AI4" s="19" t="s">
+      <c r="AI4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="AJ4" s="20" t="s">
+      <c r="AJ4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AK4" s="20" t="s">
+      <c r="AK4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AL4" s="20" t="s">
+      <c r="AL4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AM4" s="20" t="s">
+      <c r="AM4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AN4" s="20" t="s">
+      <c r="AN4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="AO4" s="20" t="s">
+      <c r="AO4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AP4" s="20" t="s">
+      <c r="AP4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AQ4" s="20" t="s">
+      <c r="AQ4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="AR4" s="20" t="s">
+      <c r="AR4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="AS4" s="20" t="s">
+      <c r="AS4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="AT4" s="20" t="s">
+      <c r="AT4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AU4" s="20" t="s">
+      <c r="AU4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AV4" s="20" t="s">
+      <c r="AV4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AW4" s="20" t="s">
+      <c r="AW4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AX4" s="20" t="s">
+      <c r="AX4" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:50" ht="34" x14ac:dyDescent="0.45">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="K5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="L5" s="19" t="s">
+      <c r="L5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="M5" s="19" t="s">
+      <c r="M5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="N5" s="19" t="s">
+      <c r="N5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="O5" s="19" t="s">
+      <c r="O5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="P5" s="19" t="s">
+      <c r="P5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="Q5" s="19" t="s">
+      <c r="Q5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="R5" s="19" t="s">
+      <c r="R5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="S5" s="19" t="s">
+      <c r="S5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="T5" s="19" t="s">
+      <c r="T5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="U5" s="19" t="s">
+      <c r="U5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="V5" s="19" t="s">
+      <c r="V5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="W5" s="19" t="s">
+      <c r="W5" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="X5" s="19" t="s">
+      <c r="X5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="Y5" s="19" t="s">
+      <c r="Y5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="Z5" s="19" t="s">
+      <c r="Z5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="AA5" s="19" t="s">
+      <c r="AA5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="AB5" s="19" t="s">
+      <c r="AB5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="AC5" s="19" t="s">
+      <c r="AC5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AD5" s="19" t="s">
+      <c r="AD5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AE5" s="19" t="s">
+      <c r="AE5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="AF5" s="19" t="s">
+      <c r="AF5" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="AG5" s="19" t="s">
+      <c r="AG5" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="AH5" s="21" t="s">
+      <c r="AH5" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="AI5" s="21" t="s">
+      <c r="AI5" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="AJ5" s="19" t="s">
+      <c r="AJ5" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="AK5" s="19" t="s">
+      <c r="AK5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="AL5" s="19" t="s">
+      <c r="AL5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="AM5" s="19" t="s">
+      <c r="AM5" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="AN5" s="19" t="s">
+      <c r="AN5" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="AO5" s="21" t="s">
+      <c r="AO5" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="AP5" s="21" t="s">
+      <c r="AP5" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="AQ5" s="19" t="s">
+      <c r="AQ5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="AR5" s="19" t="s">
+      <c r="AR5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="AS5" s="19" t="s">
+      <c r="AS5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="AT5" s="19" t="s">
+      <c r="AT5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="AU5" s="19" t="s">
+      <c r="AU5" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="AV5" s="19" t="s">
+      <c r="AV5" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="AW5" s="19" t="s">
+      <c r="AW5" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="AX5" s="19" t="s">
+      <c r="AX5" s="7" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:50" ht="170" x14ac:dyDescent="0.45">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="7">
         <v>5</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="7">
         <v>4</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="7">
         <v>5</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="10">
         <v>0.10000000149011599</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="10">
         <v>0.10000000149011599</v>
       </c>
-      <c r="J6" s="22">
+      <c r="J6" s="10">
         <v>0.10000000149011599</v>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="7">
         <v>2</v>
       </c>
-      <c r="L6" s="19" t="s">
+      <c r="L6" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="M6" s="21" t="s">
+      <c r="M6" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="N6" s="19">
-        <v>0</v>
-      </c>
-      <c r="O6" s="19">
+      <c r="N6" s="7">
+        <v>0</v>
+      </c>
+      <c r="O6" s="7">
         <v>2</v>
       </c>
-      <c r="P6" s="19">
+      <c r="P6" s="7">
         <v>1</v>
       </c>
-      <c r="Q6" s="19">
-        <v>0</v>
-      </c>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
-      <c r="T6" s="19"/>
-      <c r="U6" s="22">
+      <c r="Q6" s="7">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="10">
         <v>1</v>
       </c>
-      <c r="V6" s="22">
-        <v>0</v>
-      </c>
-      <c r="W6" s="19"/>
-      <c r="X6" s="21"/>
-      <c r="Y6" s="19"/>
-      <c r="Z6" s="19"/>
-      <c r="AA6" s="19"/>
-      <c r="AB6" s="19"/>
-      <c r="AC6" s="19"/>
-      <c r="AD6" s="19"/>
-      <c r="AE6" s="19"/>
-      <c r="AF6" s="22"/>
-      <c r="AG6" s="22"/>
-      <c r="AH6" s="21" t="s">
+      <c r="V6" s="10">
+        <v>0</v>
+      </c>
+      <c r="W6" s="7"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7"/>
+      <c r="AA6" s="7"/>
+      <c r="AB6" s="7"/>
+      <c r="AC6" s="7"/>
+      <c r="AD6" s="7"/>
+      <c r="AE6" s="7"/>
+      <c r="AF6" s="10"/>
+      <c r="AG6" s="10"/>
+      <c r="AH6" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="AI6" s="19">
+      <c r="AI6" s="7">
         <v>15</v>
       </c>
-      <c r="AJ6" s="19">
+      <c r="AJ6" s="7">
         <v>5</v>
       </c>
-      <c r="AK6" s="19">
+      <c r="AK6" s="7">
         <v>1</v>
       </c>
-      <c r="AL6" s="19">
+      <c r="AL6" s="7">
         <v>4</v>
       </c>
-      <c r="AM6" s="19">
+      <c r="AM6" s="7">
         <v>1</v>
       </c>
-      <c r="AN6" s="19"/>
-      <c r="AO6" s="19"/>
-      <c r="AP6" s="19"/>
-      <c r="AQ6" s="19"/>
-      <c r="AR6" s="19"/>
-      <c r="AS6" s="19"/>
-      <c r="AT6" s="19">
+      <c r="AN6" s="7"/>
+      <c r="AO6" s="7"/>
+      <c r="AP6" s="7"/>
+      <c r="AQ6" s="7"/>
+      <c r="AR6" s="7"/>
+      <c r="AS6" s="7"/>
+      <c r="AT6" s="7">
         <v>15</v>
       </c>
-      <c r="AU6" s="19">
+      <c r="AU6" s="7">
         <v>5</v>
       </c>
-      <c r="AV6" s="19">
+      <c r="AV6" s="7">
         <v>1</v>
       </c>
-      <c r="AW6" s="19">
+      <c r="AW6" s="7">
         <v>4</v>
       </c>
-      <c r="AX6" s="19">
+      <c r="AX6" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:50" ht="289" x14ac:dyDescent="0.45">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19" t="s">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="7">
         <v>8</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="7">
         <v>6</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="7">
         <v>6</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="10">
         <v>0.10000000149011599</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="10">
         <v>0.10000000149011599</v>
       </c>
-      <c r="J7" s="22">
+      <c r="J7" s="10">
         <v>0.25</v>
       </c>
-      <c r="K7" s="19">
+      <c r="K7" s="7">
         <v>3</v>
       </c>
-      <c r="L7" s="19" t="s">
+      <c r="L7" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="M7" s="21" t="s">
+      <c r="M7" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="N7" s="19">
-        <v>0</v>
-      </c>
-      <c r="O7" s="19">
+      <c r="N7" s="7">
+        <v>0</v>
+      </c>
+      <c r="O7" s="7">
         <v>1</v>
       </c>
-      <c r="P7" s="19">
+      <c r="P7" s="7">
         <v>1</v>
       </c>
-      <c r="Q7" s="19">
-        <v>0</v>
-      </c>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19">
-        <v>0</v>
-      </c>
-      <c r="T7" s="19">
-        <v>0</v>
-      </c>
-      <c r="U7" s="22">
+      <c r="Q7" s="7">
+        <v>0</v>
+      </c>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7">
+        <v>0</v>
+      </c>
+      <c r="T7" s="7">
+        <v>0</v>
+      </c>
+      <c r="U7" s="10">
         <v>1</v>
       </c>
-      <c r="V7" s="22">
-        <v>0</v>
-      </c>
-      <c r="W7" s="19" t="s">
+      <c r="V7" s="10">
+        <v>0</v>
+      </c>
+      <c r="W7" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="X7" s="19" t="s">
+      <c r="X7" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="Y7" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="19">
+      <c r="Y7" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="7">
         <v>1</v>
       </c>
-      <c r="AA7" s="19">
+      <c r="AA7" s="7">
         <v>1</v>
       </c>
-      <c r="AB7" s="19">
+      <c r="AB7" s="7">
         <v>1</v>
       </c>
-      <c r="AC7" s="19" t="s">
+      <c r="AC7" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="AD7" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="19"/>
-      <c r="AF7" s="22">
+      <c r="AD7" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="7"/>
+      <c r="AF7" s="10">
         <v>0.6</v>
       </c>
-      <c r="AG7" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="21" t="s">
+      <c r="AG7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="AI7" s="19">
+      <c r="AI7" s="7">
         <v>30</v>
       </c>
-      <c r="AJ7" s="19">
+      <c r="AJ7" s="7">
         <v>10</v>
       </c>
-      <c r="AK7" s="19">
+      <c r="AK7" s="7">
         <v>3</v>
       </c>
-      <c r="AL7" s="19">
+      <c r="AL7" s="7">
         <v>4</v>
       </c>
-      <c r="AM7" s="19">
+      <c r="AM7" s="7">
         <v>1</v>
       </c>
-      <c r="AN7" s="19"/>
-      <c r="AO7" s="19"/>
-      <c r="AP7" s="19"/>
-      <c r="AQ7" s="19"/>
-      <c r="AR7" s="19"/>
-      <c r="AS7" s="19"/>
-      <c r="AT7" s="19">
+      <c r="AN7" s="7"/>
+      <c r="AO7" s="7"/>
+      <c r="AP7" s="7"/>
+      <c r="AQ7" s="7"/>
+      <c r="AR7" s="7"/>
+      <c r="AS7" s="7"/>
+      <c r="AT7" s="7">
         <v>30</v>
       </c>
-      <c r="AU7" s="19">
+      <c r="AU7" s="7">
         <v>10</v>
       </c>
-      <c r="AV7" s="19">
+      <c r="AV7" s="7">
         <v>3</v>
       </c>
-      <c r="AW7" s="19">
+      <c r="AW7" s="7">
         <v>4</v>
       </c>
-      <c r="AX7" s="19">
+      <c r="AX7" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:50" ht="204" x14ac:dyDescent="0.45">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19" t="s">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="7">
         <v>6</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="7">
         <v>6</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="7">
         <v>8</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="10">
         <v>0.10000000149011599</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="10">
         <v>0.25</v>
       </c>
-      <c r="J8" s="22">
+      <c r="J8" s="10">
         <v>0.10000000149011599</v>
       </c>
-      <c r="K8" s="19">
-        <v>0</v>
-      </c>
-      <c r="L8" s="19" t="s">
+      <c r="K8" s="7">
+        <v>0</v>
+      </c>
+      <c r="L8" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="M8" s="21" t="s">
+      <c r="M8" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="N8" s="19">
-        <v>0</v>
-      </c>
-      <c r="O8" s="19">
-        <v>0</v>
-      </c>
-      <c r="P8" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="19">
-        <v>0</v>
-      </c>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19">
-        <v>0</v>
-      </c>
-      <c r="T8" s="19">
-        <v>0</v>
-      </c>
-      <c r="U8" s="22">
+      <c r="N8" s="7">
+        <v>0</v>
+      </c>
+      <c r="O8" s="7">
+        <v>0</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7">
+        <v>0</v>
+      </c>
+      <c r="T8" s="7">
+        <v>0</v>
+      </c>
+      <c r="U8" s="10">
         <v>0.80000001192092896</v>
       </c>
-      <c r="V8" s="22">
-        <v>0</v>
-      </c>
-      <c r="W8" s="19" t="s">
+      <c r="V8" s="10">
+        <v>0</v>
+      </c>
+      <c r="W8" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="X8" s="21" t="s">
+      <c r="X8" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="Y8" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="19"/>
-      <c r="AD8" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="22">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="21" t="s">
+      <c r="Y8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="7"/>
+      <c r="AD8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="AI8" s="19">
+      <c r="AI8" s="7">
         <v>30</v>
       </c>
-      <c r="AJ8" s="19">
+      <c r="AJ8" s="7">
         <v>10</v>
       </c>
-      <c r="AK8" s="19">
+      <c r="AK8" s="7">
         <v>2</v>
       </c>
-      <c r="AL8" s="19">
+      <c r="AL8" s="7">
         <v>3</v>
       </c>
-      <c r="AM8" s="19">
+      <c r="AM8" s="7">
         <v>3</v>
       </c>
-      <c r="AN8" s="19"/>
-      <c r="AO8" s="19"/>
-      <c r="AP8" s="19"/>
-      <c r="AQ8" s="19"/>
-      <c r="AR8" s="19"/>
-      <c r="AS8" s="19"/>
-      <c r="AT8" s="19">
+      <c r="AN8" s="7"/>
+      <c r="AO8" s="7"/>
+      <c r="AP8" s="7"/>
+      <c r="AQ8" s="7"/>
+      <c r="AR8" s="7"/>
+      <c r="AS8" s="7"/>
+      <c r="AT8" s="7">
         <v>30</v>
       </c>
-      <c r="AU8" s="19">
+      <c r="AU8" s="7">
         <v>10</v>
       </c>
-      <c r="AV8" s="19">
+      <c r="AV8" s="7">
         <v>2</v>
       </c>
-      <c r="AW8" s="19">
+      <c r="AW8" s="7">
         <v>3</v>
       </c>
-      <c r="AX8" s="19">
+      <c r="AX8" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:50" ht="153" x14ac:dyDescent="0.45">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19" t="s">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="7">
         <v>6</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="7">
         <v>12</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="7">
         <v>6</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="10">
         <v>0.20000000298023199</v>
       </c>
-      <c r="I9" s="22">
+      <c r="I9" s="10">
         <v>0.15000000596046401</v>
       </c>
-      <c r="J9" s="22">
+      <c r="J9" s="10">
         <v>0.15000000596046401</v>
       </c>
-      <c r="K9" s="19">
+      <c r="K9" s="7">
         <v>2</v>
       </c>
-      <c r="L9" s="19" t="s">
+      <c r="L9" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="M9" s="21" t="s">
+      <c r="M9" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="N9" s="19">
-        <v>0</v>
-      </c>
-      <c r="O9" s="19">
+      <c r="N9" s="7">
+        <v>0</v>
+      </c>
+      <c r="O9" s="7">
         <v>1</v>
       </c>
-      <c r="P9" s="19">
+      <c r="P9" s="7">
         <v>1</v>
       </c>
-      <c r="Q9" s="19">
+      <c r="Q9" s="7">
         <v>1</v>
       </c>
-      <c r="R9" s="19" t="s">
+      <c r="R9" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="S9" s="19">
-        <v>0</v>
-      </c>
-      <c r="T9" s="19">
-        <v>0</v>
-      </c>
-      <c r="U9" s="22">
+      <c r="S9" s="7">
+        <v>0</v>
+      </c>
+      <c r="T9" s="7">
+        <v>0</v>
+      </c>
+      <c r="U9" s="10">
         <v>1.20000004768372</v>
       </c>
-      <c r="V9" s="22">
+      <c r="V9" s="10">
         <v>1</v>
       </c>
-      <c r="W9" s="19"/>
-      <c r="X9" s="19"/>
-      <c r="Y9" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="19"/>
-      <c r="AD9" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="22">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="21" t="s">
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="7"/>
+      <c r="AD9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="AI9" s="19">
+      <c r="AI9" s="7">
         <v>60</v>
       </c>
-      <c r="AJ9" s="19">
+      <c r="AJ9" s="7">
         <v>20</v>
       </c>
-      <c r="AK9" s="19">
+      <c r="AK9" s="7">
         <v>3</v>
       </c>
-      <c r="AL9" s="19">
+      <c r="AL9" s="7">
         <v>4</v>
       </c>
-      <c r="AM9" s="19">
+      <c r="AM9" s="7">
         <v>3</v>
       </c>
-      <c r="AN9" s="19"/>
-      <c r="AO9" s="19"/>
-      <c r="AP9" s="19"/>
-      <c r="AQ9" s="19"/>
-      <c r="AR9" s="19"/>
-      <c r="AS9" s="19"/>
-      <c r="AT9" s="19">
+      <c r="AN9" s="7"/>
+      <c r="AO9" s="7"/>
+      <c r="AP9" s="7"/>
+      <c r="AQ9" s="7"/>
+      <c r="AR9" s="7"/>
+      <c r="AS9" s="7"/>
+      <c r="AT9" s="7">
         <v>60</v>
       </c>
-      <c r="AU9" s="19">
+      <c r="AU9" s="7">
         <v>20</v>
       </c>
-      <c r="AV9" s="19">
+      <c r="AV9" s="7">
         <v>3</v>
       </c>
-      <c r="AW9" s="19">
+      <c r="AW9" s="7">
         <v>4</v>
       </c>
-      <c r="AX9" s="19">
+      <c r="AX9" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:50" ht="306" x14ac:dyDescent="0.45">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19" t="s">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="7">
         <v>100</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="7">
         <v>6</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="7">
         <v>6</v>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="10">
         <v>0.25</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="10">
         <v>0.20000000298023199</v>
       </c>
-      <c r="J10" s="22">
+      <c r="J10" s="10">
         <v>0.20000000298023199</v>
       </c>
-      <c r="K10" s="19">
+      <c r="K10" s="7">
         <v>1</v>
       </c>
-      <c r="L10" s="19" t="s">
+      <c r="L10" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="M10" s="21" t="s">
+      <c r="M10" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="N10" s="19">
-        <v>0</v>
-      </c>
-      <c r="O10" s="19">
+      <c r="N10" s="7">
+        <v>0</v>
+      </c>
+      <c r="O10" s="7">
         <v>1</v>
       </c>
-      <c r="P10" s="19">
+      <c r="P10" s="7">
         <v>1</v>
       </c>
-      <c r="Q10" s="19">
-        <v>0</v>
-      </c>
-      <c r="R10" s="19"/>
-      <c r="S10" s="19">
-        <v>0</v>
-      </c>
-      <c r="T10" s="19">
-        <v>0</v>
-      </c>
-      <c r="U10" s="22">
+      <c r="Q10" s="7">
+        <v>0</v>
+      </c>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7">
+        <v>0</v>
+      </c>
+      <c r="T10" s="7">
+        <v>0</v>
+      </c>
+      <c r="U10" s="10">
         <v>1</v>
       </c>
-      <c r="V10" s="22">
-        <v>0</v>
-      </c>
-      <c r="W10" s="19" t="s">
+      <c r="V10" s="10">
+        <v>0</v>
+      </c>
+      <c r="W10" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="X10" s="21" t="s">
+      <c r="X10" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="Y10" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="19">
+      <c r="Y10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="7">
         <v>1</v>
       </c>
-      <c r="AC10" s="19" t="s">
+      <c r="AC10" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="AD10" s="19">
+      <c r="AD10" s="7">
         <v>1</v>
       </c>
-      <c r="AE10" s="19">
+      <c r="AE10" s="7">
         <v>1</v>
       </c>
-      <c r="AF10" s="22">
+      <c r="AF10" s="10">
         <v>1</v>
       </c>
-      <c r="AG10" s="22">
+      <c r="AG10" s="10">
         <v>0.8</v>
       </c>
-      <c r="AH10" s="21" t="s">
+      <c r="AH10" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="AI10" s="19">
+      <c r="AI10" s="7">
         <v>80</v>
       </c>
-      <c r="AJ10" s="19">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="19">
+      <c r="AJ10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="7">
         <v>10</v>
       </c>
-      <c r="AL10" s="19">
+      <c r="AL10" s="7">
         <v>5</v>
       </c>
-      <c r="AM10" s="19">
+      <c r="AM10" s="7">
         <v>3</v>
       </c>
-      <c r="AN10" s="19"/>
-      <c r="AO10" s="19"/>
-      <c r="AP10" s="19"/>
-      <c r="AQ10" s="19"/>
-      <c r="AR10" s="19"/>
-      <c r="AS10" s="19"/>
-      <c r="AT10" s="19">
+      <c r="AN10" s="7"/>
+      <c r="AO10" s="7"/>
+      <c r="AP10" s="7"/>
+      <c r="AQ10" s="7"/>
+      <c r="AR10" s="7"/>
+      <c r="AS10" s="7"/>
+      <c r="AT10" s="7">
         <v>80</v>
       </c>
-      <c r="AU10" s="19">
-        <v>0</v>
-      </c>
-      <c r="AV10" s="19">
+      <c r="AU10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="7">
         <v>7</v>
       </c>
-      <c r="AW10" s="19">
+      <c r="AW10" s="7">
         <v>5</v>
       </c>
-      <c r="AX10" s="19">
+      <c r="AX10" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:50" ht="239.5" x14ac:dyDescent="0.45">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19" t="s">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="7">
         <v>8</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="7">
         <v>6</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="7">
         <v>6</v>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="11">
         <v>0.1</v>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="11">
         <v>0.1</v>
       </c>
-      <c r="J11" s="23">
+      <c r="J11" s="11">
         <v>0.1</v>
       </c>
-      <c r="K11" s="19">
+      <c r="K11" s="7">
         <v>3</v>
       </c>
-      <c r="L11" s="19" t="s">
+      <c r="L11" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="M11" s="21" t="s">
+      <c r="M11" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="N11" s="19">
-        <v>0</v>
-      </c>
-      <c r="O11" s="19">
+      <c r="N11" s="7">
+        <v>0</v>
+      </c>
+      <c r="O11" s="7">
         <v>1</v>
       </c>
-      <c r="P11" s="19">
+      <c r="P11" s="7">
         <v>1</v>
       </c>
-      <c r="Q11" s="19">
-        <v>0</v>
-      </c>
-      <c r="R11" s="19"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="19"/>
-      <c r="U11" s="23">
+      <c r="Q11" s="7">
+        <v>0</v>
+      </c>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="11">
         <v>1</v>
       </c>
-      <c r="V11" s="23"/>
-      <c r="W11" s="19" t="s">
+      <c r="V11" s="11"/>
+      <c r="W11" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="X11" s="21" t="s">
+      <c r="X11" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="Y11" s="19"/>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="19"/>
-      <c r="AB11" s="19"/>
-      <c r="AC11" s="19"/>
-      <c r="AD11" s="19"/>
-      <c r="AE11" s="19"/>
-      <c r="AF11" s="23"/>
-      <c r="AG11" s="23"/>
-      <c r="AH11" s="19"/>
-      <c r="AI11" s="21"/>
-      <c r="AJ11" s="19"/>
-      <c r="AK11" s="19"/>
-      <c r="AL11" s="19"/>
-      <c r="AM11" s="19"/>
-      <c r="AN11" s="19"/>
-      <c r="AO11" s="19"/>
-      <c r="AP11" s="19"/>
-      <c r="AQ11" s="23"/>
-      <c r="AR11" s="23"/>
-      <c r="AS11" s="21" t="s">
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7"/>
+      <c r="AA11" s="7"/>
+      <c r="AB11" s="7"/>
+      <c r="AC11" s="7"/>
+      <c r="AD11" s="7"/>
+      <c r="AE11" s="7"/>
+      <c r="AF11" s="11"/>
+      <c r="AG11" s="11"/>
+      <c r="AH11" s="7"/>
+      <c r="AI11" s="9"/>
+      <c r="AJ11" s="7"/>
+      <c r="AK11" s="7"/>
+      <c r="AL11" s="7"/>
+      <c r="AM11" s="7"/>
+      <c r="AN11" s="7"/>
+      <c r="AO11" s="7"/>
+      <c r="AP11" s="7"/>
+      <c r="AQ11" s="11"/>
+      <c r="AR11" s="11"/>
+      <c r="AS11" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="AT11" s="19">
+      <c r="AT11" s="7">
         <v>50</v>
       </c>
-      <c r="AU11" s="19">
+      <c r="AU11" s="7">
         <v>50</v>
       </c>
-      <c r="AV11" s="19">
+      <c r="AV11" s="7">
         <v>8</v>
       </c>
-      <c r="AW11" s="19">
+      <c r="AW11" s="7">
         <v>4</v>
       </c>
-      <c r="AX11" s="19">
+      <c r="AX11" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:50" ht="255" x14ac:dyDescent="0.45">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19" t="s">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="7">
         <v>6</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="7">
         <v>6</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="7">
         <v>8</v>
       </c>
-      <c r="H12" s="23">
+      <c r="H12" s="11">
         <v>0.1</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="11">
         <v>0.1</v>
       </c>
-      <c r="J12" s="23">
+      <c r="J12" s="11">
         <v>0.1</v>
       </c>
-      <c r="K12" s="19">
-        <v>0</v>
-      </c>
-      <c r="L12" s="19" t="s">
+      <c r="K12" s="7">
+        <v>0</v>
+      </c>
+      <c r="L12" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="M12" s="21" t="s">
+      <c r="M12" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="N12" s="19">
-        <v>0</v>
-      </c>
-      <c r="O12" s="19">
-        <v>0</v>
-      </c>
-      <c r="P12" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="19">
-        <v>0</v>
-      </c>
-      <c r="R12" s="19"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="19"/>
-      <c r="U12" s="23">
+      <c r="N12" s="7">
+        <v>0</v>
+      </c>
+      <c r="O12" s="7">
+        <v>0</v>
+      </c>
+      <c r="P12" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>0</v>
+      </c>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="11">
         <v>0.8</v>
       </c>
-      <c r="V12" s="23"/>
-      <c r="W12" s="19" t="s">
+      <c r="V12" s="11"/>
+      <c r="W12" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="X12" s="21" t="s">
+      <c r="X12" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="Y12" s="19"/>
-      <c r="Z12" s="19"/>
-      <c r="AA12" s="19"/>
-      <c r="AB12" s="19"/>
-      <c r="AC12" s="19"/>
-      <c r="AD12" s="19"/>
-      <c r="AE12" s="19"/>
-      <c r="AF12" s="23"/>
-      <c r="AG12" s="23"/>
-      <c r="AH12" s="19" t="s">
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7"/>
+      <c r="AA12" s="7"/>
+      <c r="AB12" s="7"/>
+      <c r="AC12" s="7"/>
+      <c r="AD12" s="7"/>
+      <c r="AE12" s="7"/>
+      <c r="AF12" s="11"/>
+      <c r="AG12" s="11"/>
+      <c r="AH12" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="AI12" s="21" t="s">
+      <c r="AI12" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="AJ12" s="19"/>
-      <c r="AK12" s="19"/>
-      <c r="AL12" s="19"/>
-      <c r="AM12" s="19"/>
-      <c r="AN12" s="19"/>
-      <c r="AO12" s="19"/>
-      <c r="AP12" s="19"/>
-      <c r="AQ12" s="23"/>
-      <c r="AR12" s="23"/>
-      <c r="AS12" s="21" t="s">
+      <c r="AJ12" s="7"/>
+      <c r="AK12" s="7"/>
+      <c r="AL12" s="7"/>
+      <c r="AM12" s="7"/>
+      <c r="AN12" s="7"/>
+      <c r="AO12" s="7"/>
+      <c r="AP12" s="7"/>
+      <c r="AQ12" s="11"/>
+      <c r="AR12" s="11"/>
+      <c r="AS12" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="AT12" s="19">
+      <c r="AT12" s="7">
         <v>50</v>
       </c>
-      <c r="AU12" s="19">
+      <c r="AU12" s="7">
         <v>50</v>
       </c>
-      <c r="AV12" s="19">
+      <c r="AV12" s="7">
         <v>6</v>
       </c>
-      <c r="AW12" s="19">
+      <c r="AW12" s="7">
         <v>3</v>
       </c>
-      <c r="AX12" s="19">
+      <c r="AX12" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:50" ht="85" x14ac:dyDescent="0.45">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19" t="s">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="7">
         <v>50</v>
       </c>
-      <c r="F13" s="19">
-        <v>0</v>
-      </c>
-      <c r="G13" s="19">
-        <v>0</v>
-      </c>
-      <c r="H13" s="23">
-        <v>0</v>
-      </c>
-      <c r="I13" s="23">
-        <v>0</v>
-      </c>
-      <c r="J13" s="23">
-        <v>0</v>
-      </c>
-      <c r="K13" s="19">
+      <c r="F13" s="7">
+        <v>0</v>
+      </c>
+      <c r="G13" s="7">
+        <v>0</v>
+      </c>
+      <c r="H13" s="11">
+        <v>0</v>
+      </c>
+      <c r="I13" s="11">
+        <v>0</v>
+      </c>
+      <c r="J13" s="11">
+        <v>0</v>
+      </c>
+      <c r="K13" s="7">
         <v>3</v>
       </c>
-      <c r="L13" s="19" t="s">
+      <c r="L13" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="M13" s="19" t="s">
+      <c r="M13" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="19"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="19"/>
-      <c r="U13" s="19"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="19" t="s">
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="X13" s="19" t="s">
+      <c r="X13" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="Y13" s="19"/>
-      <c r="Z13" s="19"/>
-      <c r="AA13" s="19"/>
-      <c r="AB13" s="19"/>
-      <c r="AC13" s="19"/>
-      <c r="AD13" s="19"/>
-      <c r="AE13" s="19"/>
-      <c r="AF13" s="19"/>
-      <c r="AG13" s="19"/>
-      <c r="AH13" s="19"/>
-      <c r="AI13" s="19"/>
-      <c r="AJ13" s="19"/>
-      <c r="AK13" s="19"/>
-      <c r="AL13" s="19"/>
-      <c r="AM13" s="19"/>
-      <c r="AN13" s="19"/>
-      <c r="AO13" s="19"/>
-      <c r="AP13" s="19"/>
-      <c r="AQ13" s="19"/>
-      <c r="AR13" s="19"/>
-      <c r="AS13" s="21" t="s">
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="7"/>
+      <c r="AA13" s="7"/>
+      <c r="AB13" s="7"/>
+      <c r="AC13" s="7"/>
+      <c r="AD13" s="7"/>
+      <c r="AE13" s="7"/>
+      <c r="AF13" s="7"/>
+      <c r="AG13" s="7"/>
+      <c r="AH13" s="7"/>
+      <c r="AI13" s="7"/>
+      <c r="AJ13" s="7"/>
+      <c r="AK13" s="7"/>
+      <c r="AL13" s="7"/>
+      <c r="AM13" s="7"/>
+      <c r="AN13" s="7"/>
+      <c r="AO13" s="7"/>
+      <c r="AP13" s="7"/>
+      <c r="AQ13" s="7"/>
+      <c r="AR13" s="7"/>
+      <c r="AS13" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="AT13" s="19">
-        <v>0</v>
-      </c>
-      <c r="AU13" s="19"/>
-      <c r="AV13" s="19"/>
-      <c r="AW13" s="19"/>
-      <c r="AX13" s="19"/>
+      <c r="AT13" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="7"/>
+      <c r="AV13" s="7"/>
+      <c r="AW13" s="7"/>
+      <c r="AX13" s="7"/>
     </row>
     <row r="14" spans="1:50" ht="85" x14ac:dyDescent="0.45">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19" t="s">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="7">
         <v>50</v>
       </c>
-      <c r="F14" s="19">
-        <v>0</v>
-      </c>
-      <c r="G14" s="19">
-        <v>0</v>
-      </c>
-      <c r="H14" s="23">
-        <v>0</v>
-      </c>
-      <c r="I14" s="23">
-        <v>0</v>
-      </c>
-      <c r="J14" s="23">
-        <v>0</v>
-      </c>
-      <c r="K14" s="19">
+      <c r="F14" s="7">
+        <v>0</v>
+      </c>
+      <c r="G14" s="7">
+        <v>0</v>
+      </c>
+      <c r="H14" s="11">
+        <v>0</v>
+      </c>
+      <c r="I14" s="11">
+        <v>0</v>
+      </c>
+      <c r="J14" s="11">
+        <v>0</v>
+      </c>
+      <c r="K14" s="7">
         <v>2</v>
       </c>
-      <c r="L14" s="19" t="s">
+      <c r="L14" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="19"/>
-      <c r="R14" s="19"/>
-      <c r="S14" s="19"/>
-      <c r="T14" s="19"/>
-      <c r="U14" s="19"/>
-      <c r="V14" s="19"/>
-      <c r="W14" s="19" t="s">
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="X14" s="19" t="s">
+      <c r="X14" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="Y14" s="19"/>
-      <c r="Z14" s="19"/>
-      <c r="AA14" s="19"/>
-      <c r="AB14" s="19"/>
-      <c r="AC14" s="19"/>
-      <c r="AD14" s="19"/>
-      <c r="AE14" s="19"/>
-      <c r="AF14" s="19"/>
-      <c r="AG14" s="19"/>
-      <c r="AH14" s="19"/>
-      <c r="AI14" s="19"/>
-      <c r="AJ14" s="19"/>
-      <c r="AK14" s="19"/>
-      <c r="AL14" s="19"/>
-      <c r="AM14" s="19"/>
-      <c r="AN14" s="19"/>
-      <c r="AO14" s="19"/>
-      <c r="AP14" s="19"/>
-      <c r="AQ14" s="19"/>
-      <c r="AR14" s="19"/>
-      <c r="AS14" s="21" t="s">
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7"/>
+      <c r="AA14" s="7"/>
+      <c r="AB14" s="7"/>
+      <c r="AC14" s="7"/>
+      <c r="AD14" s="7"/>
+      <c r="AE14" s="7"/>
+      <c r="AF14" s="7"/>
+      <c r="AG14" s="7"/>
+      <c r="AH14" s="7"/>
+      <c r="AI14" s="7"/>
+      <c r="AJ14" s="7"/>
+      <c r="AK14" s="7"/>
+      <c r="AL14" s="7"/>
+      <c r="AM14" s="7"/>
+      <c r="AN14" s="7"/>
+      <c r="AO14" s="7"/>
+      <c r="AP14" s="7"/>
+      <c r="AQ14" s="7"/>
+      <c r="AR14" s="7"/>
+      <c r="AS14" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="AT14" s="19">
-        <v>0</v>
-      </c>
-      <c r="AU14" s="19"/>
-      <c r="AV14" s="19"/>
-      <c r="AW14" s="19"/>
-      <c r="AX14" s="19"/>
+      <c r="AT14" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="7"/>
+      <c r="AV14" s="7"/>
+      <c r="AW14" s="7"/>
+      <c r="AX14" s="7"/>
     </row>
     <row r="15" spans="1:50" ht="85" x14ac:dyDescent="0.45">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19" t="s">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="7">
         <v>50</v>
       </c>
-      <c r="F15" s="19">
-        <v>0</v>
-      </c>
-      <c r="G15" s="19">
-        <v>0</v>
-      </c>
-      <c r="H15" s="23">
-        <v>0</v>
-      </c>
-      <c r="I15" s="23">
-        <v>0</v>
-      </c>
-      <c r="J15" s="23">
-        <v>0</v>
-      </c>
-      <c r="K15" s="19">
+      <c r="F15" s="7">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7">
+        <v>0</v>
+      </c>
+      <c r="H15" s="11">
+        <v>0</v>
+      </c>
+      <c r="I15" s="11">
+        <v>0</v>
+      </c>
+      <c r="J15" s="11">
+        <v>0</v>
+      </c>
+      <c r="K15" s="7">
         <v>1</v>
       </c>
-      <c r="L15" s="19" t="s">
+      <c r="L15" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="M15" s="19" t="s">
+      <c r="M15" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="P15" s="19"/>
-      <c r="Q15" s="19"/>
-      <c r="R15" s="19"/>
-      <c r="S15" s="19"/>
-      <c r="T15" s="19"/>
-      <c r="U15" s="19"/>
-      <c r="V15" s="19"/>
-      <c r="W15" s="19" t="s">
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="X15" s="19" t="s">
+      <c r="X15" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="Y15" s="19"/>
-      <c r="Z15" s="19"/>
-      <c r="AA15" s="19"/>
-      <c r="AB15" s="19"/>
-      <c r="AC15" s="19"/>
-      <c r="AD15" s="19"/>
-      <c r="AE15" s="19"/>
-      <c r="AF15" s="19"/>
-      <c r="AG15" s="19"/>
-      <c r="AH15" s="19"/>
-      <c r="AI15" s="19"/>
-      <c r="AJ15" s="19"/>
-      <c r="AK15" s="19"/>
-      <c r="AL15" s="19"/>
-      <c r="AM15" s="19"/>
-      <c r="AN15" s="19"/>
-      <c r="AO15" s="19"/>
-      <c r="AP15" s="19"/>
-      <c r="AQ15" s="19"/>
-      <c r="AR15" s="19"/>
-      <c r="AS15" s="21" t="s">
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="7"/>
+      <c r="AA15" s="7"/>
+      <c r="AB15" s="7"/>
+      <c r="AC15" s="7"/>
+      <c r="AD15" s="7"/>
+      <c r="AE15" s="7"/>
+      <c r="AF15" s="7"/>
+      <c r="AG15" s="7"/>
+      <c r="AH15" s="7"/>
+      <c r="AI15" s="7"/>
+      <c r="AJ15" s="7"/>
+      <c r="AK15" s="7"/>
+      <c r="AL15" s="7"/>
+      <c r="AM15" s="7"/>
+      <c r="AN15" s="7"/>
+      <c r="AO15" s="7"/>
+      <c r="AP15" s="7"/>
+      <c r="AQ15" s="7"/>
+      <c r="AR15" s="7"/>
+      <c r="AS15" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="AT15" s="19">
-        <v>0</v>
-      </c>
-      <c r="AU15" s="19"/>
-      <c r="AV15" s="19"/>
-      <c r="AW15" s="19"/>
-      <c r="AX15" s="19"/>
+      <c r="AT15" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU15" s="7"/>
+      <c r="AV15" s="7"/>
+      <c r="AW15" s="7"/>
+      <c r="AX15" s="7"/>
     </row>
     <row r="16" spans="1:50" ht="85" x14ac:dyDescent="0.45">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19" t="s">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="7">
         <v>50</v>
       </c>
-      <c r="F16" s="19">
-        <v>0</v>
-      </c>
-      <c r="G16" s="19">
-        <v>0</v>
-      </c>
-      <c r="H16" s="23">
-        <v>0</v>
-      </c>
-      <c r="I16" s="23">
-        <v>0</v>
-      </c>
-      <c r="J16" s="23">
-        <v>0</v>
-      </c>
-      <c r="K16" s="19">
+      <c r="F16" s="7">
+        <v>0</v>
+      </c>
+      <c r="G16" s="7">
+        <v>0</v>
+      </c>
+      <c r="H16" s="11">
+        <v>0</v>
+      </c>
+      <c r="I16" s="11">
+        <v>0</v>
+      </c>
+      <c r="J16" s="11">
+        <v>0</v>
+      </c>
+      <c r="K16" s="7">
         <v>3</v>
       </c>
-      <c r="L16" s="19" t="s">
+      <c r="L16" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="M16" s="19" t="s">
+      <c r="M16" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="19"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
-      <c r="U16" s="19"/>
-      <c r="V16" s="19"/>
-      <c r="W16" s="19" t="s">
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="X16" s="19" t="s">
+      <c r="X16" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="Y16" s="19"/>
-      <c r="Z16" s="19"/>
-      <c r="AA16" s="19"/>
-      <c r="AB16" s="19"/>
-      <c r="AC16" s="19"/>
-      <c r="AD16" s="19"/>
-      <c r="AE16" s="19"/>
-      <c r="AF16" s="19"/>
-      <c r="AG16" s="19"/>
-      <c r="AH16" s="19"/>
-      <c r="AI16" s="19"/>
-      <c r="AJ16" s="19"/>
-      <c r="AK16" s="19"/>
-      <c r="AL16" s="19"/>
-      <c r="AM16" s="19"/>
-      <c r="AN16" s="19"/>
-      <c r="AO16" s="19"/>
-      <c r="AP16" s="19"/>
-      <c r="AQ16" s="19"/>
-      <c r="AR16" s="19"/>
-      <c r="AS16" s="21" t="s">
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="7"/>
+      <c r="AA16" s="7"/>
+      <c r="AB16" s="7"/>
+      <c r="AC16" s="7"/>
+      <c r="AD16" s="7"/>
+      <c r="AE16" s="7"/>
+      <c r="AF16" s="7"/>
+      <c r="AG16" s="7"/>
+      <c r="AH16" s="7"/>
+      <c r="AI16" s="7"/>
+      <c r="AJ16" s="7"/>
+      <c r="AK16" s="7"/>
+      <c r="AL16" s="7"/>
+      <c r="AM16" s="7"/>
+      <c r="AN16" s="7"/>
+      <c r="AO16" s="7"/>
+      <c r="AP16" s="7"/>
+      <c r="AQ16" s="7"/>
+      <c r="AR16" s="7"/>
+      <c r="AS16" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="AT16" s="19">
-        <v>0</v>
-      </c>
-      <c r="AU16" s="19"/>
-      <c r="AV16" s="19"/>
-      <c r="AW16" s="19"/>
-      <c r="AX16" s="19"/>
+      <c r="AT16" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="7"/>
+      <c r="AV16" s="7"/>
+      <c r="AW16" s="7"/>
+      <c r="AX16" s="7"/>
     </row>
     <row r="17" spans="1:50" ht="85" x14ac:dyDescent="0.45">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19" t="s">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="7">
         <v>50</v>
       </c>
-      <c r="F17" s="19">
-        <v>0</v>
-      </c>
-      <c r="G17" s="19">
-        <v>0</v>
-      </c>
-      <c r="H17" s="23">
-        <v>0</v>
-      </c>
-      <c r="I17" s="23">
-        <v>0</v>
-      </c>
-      <c r="J17" s="23">
-        <v>0</v>
-      </c>
-      <c r="K17" s="19">
+      <c r="F17" s="7">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7">
+        <v>0</v>
+      </c>
+      <c r="H17" s="11">
+        <v>0</v>
+      </c>
+      <c r="I17" s="11">
+        <v>0</v>
+      </c>
+      <c r="J17" s="11">
+        <v>0</v>
+      </c>
+      <c r="K17" s="7">
         <v>2</v>
       </c>
-      <c r="L17" s="19" t="s">
+      <c r="L17" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="M17" s="19" t="s">
+      <c r="M17" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
-      <c r="S17" s="19"/>
-      <c r="T17" s="19"/>
-      <c r="U17" s="19"/>
-      <c r="V17" s="19"/>
-      <c r="W17" s="19" t="s">
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="X17" s="19" t="s">
+      <c r="X17" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="Y17" s="19"/>
-      <c r="Z17" s="19"/>
-      <c r="AA17" s="19"/>
-      <c r="AB17" s="19"/>
-      <c r="AC17" s="19"/>
-      <c r="AD17" s="19"/>
-      <c r="AE17" s="19"/>
-      <c r="AF17" s="19"/>
-      <c r="AG17" s="19"/>
-      <c r="AH17" s="19"/>
-      <c r="AI17" s="19"/>
-      <c r="AJ17" s="19"/>
-      <c r="AK17" s="19"/>
-      <c r="AL17" s="19"/>
-      <c r="AM17" s="19"/>
-      <c r="AN17" s="19"/>
-      <c r="AO17" s="19"/>
-      <c r="AP17" s="19"/>
-      <c r="AQ17" s="19"/>
-      <c r="AR17" s="19"/>
-      <c r="AS17" s="21" t="s">
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="7"/>
+      <c r="AA17" s="7"/>
+      <c r="AB17" s="7"/>
+      <c r="AC17" s="7"/>
+      <c r="AD17" s="7"/>
+      <c r="AE17" s="7"/>
+      <c r="AF17" s="7"/>
+      <c r="AG17" s="7"/>
+      <c r="AH17" s="7"/>
+      <c r="AI17" s="7"/>
+      <c r="AJ17" s="7"/>
+      <c r="AK17" s="7"/>
+      <c r="AL17" s="7"/>
+      <c r="AM17" s="7"/>
+      <c r="AN17" s="7"/>
+      <c r="AO17" s="7"/>
+      <c r="AP17" s="7"/>
+      <c r="AQ17" s="7"/>
+      <c r="AR17" s="7"/>
+      <c r="AS17" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="AT17" s="19">
-        <v>0</v>
-      </c>
-      <c r="AU17" s="19"/>
-      <c r="AV17" s="19"/>
-      <c r="AW17" s="19"/>
-      <c r="AX17" s="19"/>
+      <c r="AT17" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU17" s="7"/>
+      <c r="AV17" s="7"/>
+      <c r="AW17" s="7"/>
+      <c r="AX17" s="7"/>
     </row>
     <row r="18" spans="1:50" ht="85" x14ac:dyDescent="0.45">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19" t="s">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="7">
         <v>50</v>
       </c>
-      <c r="F18" s="19">
-        <v>0</v>
-      </c>
-      <c r="G18" s="19">
-        <v>0</v>
-      </c>
-      <c r="H18" s="23">
-        <v>0</v>
-      </c>
-      <c r="I18" s="23">
-        <v>0</v>
-      </c>
-      <c r="J18" s="23">
-        <v>0</v>
-      </c>
-      <c r="K18" s="19">
+      <c r="F18" s="7">
+        <v>0</v>
+      </c>
+      <c r="G18" s="7">
+        <v>0</v>
+      </c>
+      <c r="H18" s="11">
+        <v>0</v>
+      </c>
+      <c r="I18" s="11">
+        <v>0</v>
+      </c>
+      <c r="J18" s="11">
+        <v>0</v>
+      </c>
+      <c r="K18" s="7">
         <v>1</v>
       </c>
-      <c r="L18" s="19" t="s">
+      <c r="L18" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="M18" s="19" t="s">
+      <c r="M18" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-      <c r="U18" s="19"/>
-      <c r="V18" s="19"/>
-      <c r="W18" s="19" t="s">
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="X18" s="19" t="s">
+      <c r="X18" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="Y18" s="19"/>
-      <c r="Z18" s="19"/>
-      <c r="AA18" s="19"/>
-      <c r="AB18" s="19"/>
-      <c r="AC18" s="19"/>
-      <c r="AD18" s="19"/>
-      <c r="AE18" s="19"/>
-      <c r="AF18" s="19"/>
-      <c r="AG18" s="19"/>
-      <c r="AH18" s="19"/>
-      <c r="AI18" s="19"/>
-      <c r="AJ18" s="19"/>
-      <c r="AK18" s="19"/>
-      <c r="AL18" s="19"/>
-      <c r="AM18" s="19"/>
-      <c r="AN18" s="19"/>
-      <c r="AO18" s="19"/>
-      <c r="AP18" s="19"/>
-      <c r="AQ18" s="19"/>
-      <c r="AR18" s="19"/>
-      <c r="AS18" s="21" t="s">
+      <c r="Y18" s="7"/>
+      <c r="Z18" s="7"/>
+      <c r="AA18" s="7"/>
+      <c r="AB18" s="7"/>
+      <c r="AC18" s="7"/>
+      <c r="AD18" s="7"/>
+      <c r="AE18" s="7"/>
+      <c r="AF18" s="7"/>
+      <c r="AG18" s="7"/>
+      <c r="AH18" s="7"/>
+      <c r="AI18" s="7"/>
+      <c r="AJ18" s="7"/>
+      <c r="AK18" s="7"/>
+      <c r="AL18" s="7"/>
+      <c r="AM18" s="7"/>
+      <c r="AN18" s="7"/>
+      <c r="AO18" s="7"/>
+      <c r="AP18" s="7"/>
+      <c r="AQ18" s="7"/>
+      <c r="AR18" s="7"/>
+      <c r="AS18" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="AT18" s="19">
-        <v>0</v>
-      </c>
-      <c r="AU18" s="19"/>
-      <c r="AV18" s="19"/>
-      <c r="AW18" s="19"/>
-      <c r="AX18" s="19"/>
+      <c r="AT18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU18" s="7"/>
+      <c r="AV18" s="7"/>
+      <c r="AW18" s="7"/>
+      <c r="AX18" s="7"/>
     </row>
     <row r="19" spans="1:50" ht="85" x14ac:dyDescent="0.45">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19" t="s">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="7">
         <v>50</v>
       </c>
-      <c r="F19" s="19">
-        <v>0</v>
-      </c>
-      <c r="G19" s="19">
-        <v>0</v>
-      </c>
-      <c r="H19" s="23">
-        <v>0</v>
-      </c>
-      <c r="I19" s="23">
-        <v>0</v>
-      </c>
-      <c r="J19" s="23">
-        <v>0</v>
-      </c>
-      <c r="K19" s="19">
+      <c r="F19" s="7">
+        <v>0</v>
+      </c>
+      <c r="G19" s="7">
+        <v>0</v>
+      </c>
+      <c r="H19" s="11">
+        <v>0</v>
+      </c>
+      <c r="I19" s="11">
+        <v>0</v>
+      </c>
+      <c r="J19" s="11">
+        <v>0</v>
+      </c>
+      <c r="K19" s="7">
         <v>3</v>
       </c>
-      <c r="L19" s="19" t="s">
+      <c r="L19" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="M19" s="19" t="s">
+      <c r="M19" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="19"/>
-      <c r="S19" s="19"/>
-      <c r="T19" s="19"/>
-      <c r="U19" s="19"/>
-      <c r="V19" s="19"/>
-      <c r="W19" s="19" t="s">
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="X19" s="19" t="s">
+      <c r="X19" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="Y19" s="19"/>
-      <c r="Z19" s="19"/>
-      <c r="AA19" s="19"/>
-      <c r="AB19" s="19"/>
-      <c r="AC19" s="19"/>
-      <c r="AD19" s="19"/>
-      <c r="AE19" s="19"/>
-      <c r="AF19" s="19"/>
-      <c r="AG19" s="19"/>
-      <c r="AH19" s="19"/>
-      <c r="AI19" s="19"/>
-      <c r="AJ19" s="19"/>
-      <c r="AK19" s="19"/>
-      <c r="AL19" s="19"/>
-      <c r="AM19" s="19"/>
-      <c r="AN19" s="19"/>
-      <c r="AO19" s="19"/>
-      <c r="AP19" s="19"/>
-      <c r="AQ19" s="19"/>
-      <c r="AR19" s="19"/>
-      <c r="AS19" s="21" t="s">
+      <c r="Y19" s="7"/>
+      <c r="Z19" s="7"/>
+      <c r="AA19" s="7"/>
+      <c r="AB19" s="7"/>
+      <c r="AC19" s="7"/>
+      <c r="AD19" s="7"/>
+      <c r="AE19" s="7"/>
+      <c r="AF19" s="7"/>
+      <c r="AG19" s="7"/>
+      <c r="AH19" s="7"/>
+      <c r="AI19" s="7"/>
+      <c r="AJ19" s="7"/>
+      <c r="AK19" s="7"/>
+      <c r="AL19" s="7"/>
+      <c r="AM19" s="7"/>
+      <c r="AN19" s="7"/>
+      <c r="AO19" s="7"/>
+      <c r="AP19" s="7"/>
+      <c r="AQ19" s="7"/>
+      <c r="AR19" s="7"/>
+      <c r="AS19" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="AT19" s="19">
-        <v>0</v>
-      </c>
-      <c r="AU19" s="19"/>
-      <c r="AV19" s="19"/>
-      <c r="AW19" s="19"/>
-      <c r="AX19" s="19"/>
+      <c r="AT19" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU19" s="7"/>
+      <c r="AV19" s="7"/>
+      <c r="AW19" s="7"/>
+      <c r="AX19" s="7"/>
     </row>
     <row r="20" spans="1:50" ht="85" x14ac:dyDescent="0.45">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19" t="s">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="7">
         <v>50</v>
       </c>
-      <c r="F20" s="19">
-        <v>0</v>
-      </c>
-      <c r="G20" s="19">
-        <v>0</v>
-      </c>
-      <c r="H20" s="23">
-        <v>0</v>
-      </c>
-      <c r="I20" s="23">
-        <v>0</v>
-      </c>
-      <c r="J20" s="23">
-        <v>0</v>
-      </c>
-      <c r="K20" s="19">
+      <c r="F20" s="7">
+        <v>0</v>
+      </c>
+      <c r="G20" s="7">
+        <v>0</v>
+      </c>
+      <c r="H20" s="11">
+        <v>0</v>
+      </c>
+      <c r="I20" s="11">
+        <v>0</v>
+      </c>
+      <c r="J20" s="11">
+        <v>0</v>
+      </c>
+      <c r="K20" s="7">
         <v>2</v>
       </c>
-      <c r="L20" s="19" t="s">
+      <c r="L20" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="M20" s="19" t="s">
+      <c r="M20" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="19"/>
-      <c r="S20" s="19"/>
-      <c r="T20" s="19"/>
-      <c r="U20" s="19"/>
-      <c r="V20" s="19"/>
-      <c r="W20" s="19" t="s">
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="7"/>
+      <c r="W20" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="X20" s="19" t="s">
+      <c r="X20" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="Y20" s="19"/>
-      <c r="Z20" s="19"/>
-      <c r="AA20" s="19"/>
-      <c r="AB20" s="19"/>
-      <c r="AC20" s="19"/>
-      <c r="AD20" s="19"/>
-      <c r="AE20" s="19"/>
-      <c r="AF20" s="19"/>
-      <c r="AG20" s="19"/>
-      <c r="AH20" s="19"/>
-      <c r="AI20" s="19"/>
-      <c r="AJ20" s="19"/>
-      <c r="AK20" s="19"/>
-      <c r="AL20" s="19"/>
-      <c r="AM20" s="19"/>
-      <c r="AN20" s="19"/>
-      <c r="AO20" s="19"/>
-      <c r="AP20" s="19"/>
-      <c r="AQ20" s="19"/>
-      <c r="AR20" s="19"/>
-      <c r="AS20" s="21" t="s">
+      <c r="Y20" s="7"/>
+      <c r="Z20" s="7"/>
+      <c r="AA20" s="7"/>
+      <c r="AB20" s="7"/>
+      <c r="AC20" s="7"/>
+      <c r="AD20" s="7"/>
+      <c r="AE20" s="7"/>
+      <c r="AF20" s="7"/>
+      <c r="AG20" s="7"/>
+      <c r="AH20" s="7"/>
+      <c r="AI20" s="7"/>
+      <c r="AJ20" s="7"/>
+      <c r="AK20" s="7"/>
+      <c r="AL20" s="7"/>
+      <c r="AM20" s="7"/>
+      <c r="AN20" s="7"/>
+      <c r="AO20" s="7"/>
+      <c r="AP20" s="7"/>
+      <c r="AQ20" s="7"/>
+      <c r="AR20" s="7"/>
+      <c r="AS20" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="AT20" s="19">
-        <v>0</v>
-      </c>
-      <c r="AU20" s="19"/>
-      <c r="AV20" s="19"/>
-      <c r="AW20" s="19"/>
-      <c r="AX20" s="19"/>
+      <c r="AT20" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU20" s="7"/>
+      <c r="AV20" s="7"/>
+      <c r="AW20" s="7"/>
+      <c r="AX20" s="7"/>
     </row>
     <row r="21" spans="1:50" ht="85" x14ac:dyDescent="0.45">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19" t="s">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="7">
         <v>50</v>
       </c>
-      <c r="F21" s="19">
-        <v>0</v>
-      </c>
-      <c r="G21" s="19">
-        <v>0</v>
-      </c>
-      <c r="H21" s="23">
-        <v>0</v>
-      </c>
-      <c r="I21" s="23">
-        <v>0</v>
-      </c>
-      <c r="J21" s="23">
-        <v>0</v>
-      </c>
-      <c r="K21" s="19">
+      <c r="F21" s="7">
+        <v>0</v>
+      </c>
+      <c r="G21" s="7">
+        <v>0</v>
+      </c>
+      <c r="H21" s="11">
+        <v>0</v>
+      </c>
+      <c r="I21" s="11">
+        <v>0</v>
+      </c>
+      <c r="J21" s="11">
+        <v>0</v>
+      </c>
+      <c r="K21" s="7">
         <v>1</v>
       </c>
-      <c r="L21" s="19" t="s">
+      <c r="L21" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="M21" s="19" t="s">
+      <c r="M21" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
-      <c r="S21" s="19"/>
-      <c r="T21" s="19"/>
-      <c r="U21" s="19"/>
-      <c r="V21" s="19"/>
-      <c r="W21" s="19" t="s">
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="7"/>
+      <c r="U21" s="7"/>
+      <c r="V21" s="7"/>
+      <c r="W21" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="X21" s="19" t="s">
+      <c r="X21" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="Y21" s="19"/>
-      <c r="Z21" s="19"/>
-      <c r="AA21" s="19"/>
-      <c r="AB21" s="19"/>
-      <c r="AC21" s="19"/>
-      <c r="AD21" s="19"/>
-      <c r="AE21" s="19"/>
-      <c r="AF21" s="19"/>
-      <c r="AG21" s="19"/>
-      <c r="AH21" s="19"/>
-      <c r="AI21" s="19"/>
-      <c r="AJ21" s="19"/>
-      <c r="AK21" s="19"/>
-      <c r="AL21" s="19"/>
-      <c r="AM21" s="19"/>
-      <c r="AN21" s="19"/>
-      <c r="AO21" s="19"/>
-      <c r="AP21" s="19"/>
-      <c r="AQ21" s="19"/>
-      <c r="AR21" s="19"/>
-      <c r="AS21" s="21" t="s">
+      <c r="Y21" s="7"/>
+      <c r="Z21" s="7"/>
+      <c r="AA21" s="7"/>
+      <c r="AB21" s="7"/>
+      <c r="AC21" s="7"/>
+      <c r="AD21" s="7"/>
+      <c r="AE21" s="7"/>
+      <c r="AF21" s="7"/>
+      <c r="AG21" s="7"/>
+      <c r="AH21" s="7"/>
+      <c r="AI21" s="7"/>
+      <c r="AJ21" s="7"/>
+      <c r="AK21" s="7"/>
+      <c r="AL21" s="7"/>
+      <c r="AM21" s="7"/>
+      <c r="AN21" s="7"/>
+      <c r="AO21" s="7"/>
+      <c r="AP21" s="7"/>
+      <c r="AQ21" s="7"/>
+      <c r="AR21" s="7"/>
+      <c r="AS21" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="AT21" s="19">
-        <v>0</v>
-      </c>
-      <c r="AU21" s="19"/>
-      <c r="AV21" s="19"/>
-      <c r="AW21" s="19"/>
-      <c r="AX21" s="19"/>
+      <c r="AT21" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU21" s="7"/>
+      <c r="AV21" s="7"/>
+      <c r="AW21" s="7"/>
+      <c r="AX21" s="7"/>
     </row>
     <row r="22" spans="1:50" ht="204" x14ac:dyDescent="0.45">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19" t="s">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22" s="7">
         <v>200</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="20">
+        <v>12</v>
+      </c>
+      <c r="G22" s="20">
         <v>18</v>
       </c>
-      <c r="G22" s="32">
-        <v>25</v>
-      </c>
-      <c r="H22" s="24">
+      <c r="H22" s="12">
         <v>0.25</v>
       </c>
-      <c r="I22" s="24">
+      <c r="I22" s="12">
         <v>0.1</v>
       </c>
-      <c r="J22" s="24">
+      <c r="J22" s="12">
         <v>0.2</v>
       </c>
-      <c r="K22" s="19">
-        <v>0</v>
-      </c>
-      <c r="L22" s="19" t="s">
+      <c r="K22" s="7">
+        <v>0</v>
+      </c>
+      <c r="L22" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="M22" s="19" t="s">
+      <c r="M22" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="N22" s="19">
-        <v>0</v>
-      </c>
-      <c r="O22" s="19">
+      <c r="N22" s="7">
+        <v>0</v>
+      </c>
+      <c r="O22" s="7">
         <v>1</v>
       </c>
-      <c r="P22" s="19">
+      <c r="P22" s="7">
         <v>1</v>
       </c>
-      <c r="Q22" s="19">
+      <c r="Q22" s="7">
         <v>1</v>
       </c>
-      <c r="R22" s="19">
+      <c r="R22" s="7">
         <v>9</v>
       </c>
-      <c r="S22" s="19">
-        <v>0</v>
-      </c>
-      <c r="T22" s="19"/>
-      <c r="U22" s="22">
+      <c r="S22" s="7">
+        <v>0</v>
+      </c>
+      <c r="T22" s="7"/>
+      <c r="U22" s="10">
         <v>1.20000004768372</v>
       </c>
-      <c r="V22" s="22">
+      <c r="V22" s="10">
         <v>1.2</v>
       </c>
-      <c r="W22" s="19" t="s">
+      <c r="W22" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="X22" s="19" t="s">
+      <c r="X22" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="Y22" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="19">
+      <c r="Y22" s="7">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="7">
         <v>1</v>
       </c>
-      <c r="AA22" s="19">
+      <c r="AA22" s="7">
         <v>1</v>
       </c>
-      <c r="AB22" s="19">
+      <c r="AB22" s="7">
         <v>1</v>
       </c>
-      <c r="AC22" s="19">
+      <c r="AC22" s="7">
         <v>2</v>
       </c>
-      <c r="AD22" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="19" t="s">
+      <c r="AD22" s="7">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="AF22" s="22">
+      <c r="AF22" s="10">
         <v>1.8</v>
       </c>
-      <c r="AG22" s="22">
+      <c r="AG22" s="10">
         <v>1.8</v>
       </c>
-      <c r="AH22" s="19" t="s">
+      <c r="AH22" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="AI22" s="21" t="s">
+      <c r="AI22" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="AJ22" s="19"/>
-      <c r="AK22" s="19"/>
-      <c r="AL22" s="19"/>
-      <c r="AM22" s="19"/>
-      <c r="AN22" s="19"/>
-      <c r="AO22" s="19"/>
-      <c r="AP22" s="19"/>
-      <c r="AQ22" s="25">
+      <c r="AJ22" s="7"/>
+      <c r="AK22" s="7"/>
+      <c r="AL22" s="7"/>
+      <c r="AM22" s="7"/>
+      <c r="AN22" s="7"/>
+      <c r="AO22" s="7"/>
+      <c r="AP22" s="7"/>
+      <c r="AQ22" s="13">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AR22" s="25">
+      <c r="AR22" s="13">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AS22" s="21" t="s">
+      <c r="AS22" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="AT22" s="19"/>
-      <c r="AU22" s="19"/>
-      <c r="AV22" s="19"/>
-      <c r="AW22" s="19"/>
-      <c r="AX22" s="19"/>
+      <c r="AT22" s="7"/>
+      <c r="AU22" s="7"/>
+      <c r="AV22" s="7"/>
+      <c r="AW22" s="7"/>
+      <c r="AX22" s="7"/>
     </row>
     <row r="23" spans="1:50" ht="357" x14ac:dyDescent="0.45">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19" t="s">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="E23" s="32">
+      <c r="E23" s="7">
         <v>80</v>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="20">
+        <v>10</v>
+      </c>
+      <c r="G23" s="20">
         <v>15</v>
       </c>
-      <c r="G23" s="19">
-        <v>20</v>
-      </c>
-      <c r="H23" s="24">
+      <c r="H23" s="12">
         <v>0.2</v>
       </c>
-      <c r="I23" s="24">
-        <v>0</v>
-      </c>
-      <c r="J23" s="24">
-        <v>0</v>
-      </c>
-      <c r="K23" s="19">
+      <c r="I23" s="12">
+        <v>0</v>
+      </c>
+      <c r="J23" s="12">
+        <v>0</v>
+      </c>
+      <c r="K23" s="7">
         <v>3</v>
       </c>
-      <c r="L23" s="19" t="s">
+      <c r="L23" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="M23" s="19" t="s">
+      <c r="M23" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="19"/>
-      <c r="S23" s="19"/>
-      <c r="T23" s="19"/>
-      <c r="U23" s="22"/>
-      <c r="V23" s="22"/>
-      <c r="W23" s="19" t="s">
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="10"/>
+      <c r="V23" s="10"/>
+      <c r="W23" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="X23" s="19" t="s">
+      <c r="X23" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="Y23" s="19"/>
-      <c r="Z23" s="19"/>
-      <c r="AA23" s="19"/>
-      <c r="AB23" s="19"/>
-      <c r="AC23" s="19"/>
-      <c r="AD23" s="19"/>
-      <c r="AE23" s="19"/>
-      <c r="AF23" s="22"/>
-      <c r="AG23" s="22"/>
-      <c r="AH23" s="19" t="s">
+      <c r="Y23" s="7"/>
+      <c r="Z23" s="7"/>
+      <c r="AA23" s="7"/>
+      <c r="AB23" s="7"/>
+      <c r="AC23" s="7"/>
+      <c r="AD23" s="7"/>
+      <c r="AE23" s="7"/>
+      <c r="AF23" s="10"/>
+      <c r="AG23" s="10"/>
+      <c r="AH23" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="AI23" s="19" t="s">
+      <c r="AI23" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="AJ23" s="19">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="19">
+      <c r="AJ23" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="7">
         <v>1</v>
       </c>
-      <c r="AL23" s="19">
+      <c r="AL23" s="7">
         <v>1</v>
       </c>
-      <c r="AM23" s="19">
+      <c r="AM23" s="7">
         <v>1</v>
       </c>
-      <c r="AN23" s="19">
+      <c r="AN23" s="7">
         <v>9</v>
       </c>
-      <c r="AO23" s="19">
-        <v>0</v>
-      </c>
-      <c r="AP23" s="19"/>
-      <c r="AQ23" s="22">
+      <c r="AO23" s="7">
+        <v>0</v>
+      </c>
+      <c r="AP23" s="7"/>
+      <c r="AQ23" s="10">
         <v>1.20000004768372</v>
       </c>
-      <c r="AR23" s="22">
+      <c r="AR23" s="10">
         <v>1.2</v>
       </c>
-      <c r="AS23" s="21" t="s">
+      <c r="AS23" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="AT23" s="19"/>
-      <c r="AU23" s="19"/>
-      <c r="AV23" s="19"/>
-      <c r="AW23" s="19"/>
-      <c r="AX23" s="19"/>
+      <c r="AT23" s="7"/>
+      <c r="AU23" s="7"/>
+      <c r="AV23" s="7"/>
+      <c r="AW23" s="7"/>
+      <c r="AX23" s="7"/>
     </row>
     <row r="24" spans="1:50" ht="374" x14ac:dyDescent="0.45">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19" t="s">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="E24" s="32">
+      <c r="E24" s="7">
         <v>80</v>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="20">
+        <v>10</v>
+      </c>
+      <c r="G24" s="20">
         <v>15</v>
       </c>
-      <c r="G24" s="19">
-        <v>20</v>
-      </c>
-      <c r="H24" s="24">
+      <c r="H24" s="12">
         <v>0.2</v>
       </c>
-      <c r="I24" s="24">
-        <v>0</v>
-      </c>
-      <c r="J24" s="24">
-        <v>0</v>
-      </c>
-      <c r="K24" s="19">
+      <c r="I24" s="12">
+        <v>0</v>
+      </c>
+      <c r="J24" s="12">
+        <v>0</v>
+      </c>
+      <c r="K24" s="7">
         <v>2</v>
       </c>
-      <c r="L24" s="19" t="s">
+      <c r="L24" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
-      <c r="S24" s="19"/>
-      <c r="T24" s="19"/>
-      <c r="U24" s="22"/>
-      <c r="V24" s="22"/>
-      <c r="W24" s="19" t="s">
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
+      <c r="U24" s="10"/>
+      <c r="V24" s="10"/>
+      <c r="W24" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="X24" s="19" t="s">
+      <c r="X24" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="Y24" s="19"/>
-      <c r="Z24" s="19"/>
-      <c r="AA24" s="19"/>
-      <c r="AB24" s="19"/>
-      <c r="AC24" s="19"/>
-      <c r="AD24" s="19"/>
-      <c r="AE24" s="19"/>
-      <c r="AF24" s="22"/>
-      <c r="AG24" s="22"/>
-      <c r="AH24" s="19" t="s">
+      <c r="Y24" s="7"/>
+      <c r="Z24" s="7"/>
+      <c r="AA24" s="7"/>
+      <c r="AB24" s="7"/>
+      <c r="AC24" s="7"/>
+      <c r="AD24" s="7"/>
+      <c r="AE24" s="7"/>
+      <c r="AF24" s="10"/>
+      <c r="AG24" s="10"/>
+      <c r="AH24" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="AI24" s="19" t="s">
+      <c r="AI24" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="AJ24" s="19">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="19">
+      <c r="AJ24" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="7">
         <v>1</v>
       </c>
-      <c r="AL24" s="19">
+      <c r="AL24" s="7">
         <v>1</v>
       </c>
-      <c r="AM24" s="19">
+      <c r="AM24" s="7">
         <v>1</v>
       </c>
-      <c r="AN24" s="19">
+      <c r="AN24" s="7">
         <v>2</v>
       </c>
-      <c r="AO24" s="19">
-        <v>0</v>
-      </c>
-      <c r="AP24" s="19" t="s">
+      <c r="AO24" s="7">
+        <v>0</v>
+      </c>
+      <c r="AP24" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="AQ24" s="22">
+      <c r="AQ24" s="10">
         <v>1.8</v>
       </c>
-      <c r="AR24" s="22">
+      <c r="AR24" s="10">
         <v>1.8</v>
       </c>
-      <c r="AS24" s="21" t="s">
+      <c r="AS24" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="AT24" s="19"/>
-      <c r="AU24" s="19"/>
-      <c r="AV24" s="19"/>
-      <c r="AW24" s="19"/>
-      <c r="AX24" s="19"/>
+      <c r="AT24" s="7"/>
+      <c r="AU24" s="7"/>
+      <c r="AV24" s="7"/>
+      <c r="AW24" s="7"/>
+      <c r="AX24" s="7"/>
     </row>
     <row r="25" spans="1:50" ht="170" x14ac:dyDescent="0.45">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19" t="s">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="E25" s="32">
+      <c r="E25" s="7">
         <v>200</v>
       </c>
-      <c r="F25" s="19">
-        <v>15</v>
-      </c>
-      <c r="G25" s="32">
-        <v>25</v>
-      </c>
-      <c r="H25" s="24">
+      <c r="F25" s="20">
+        <v>10</v>
+      </c>
+      <c r="G25" s="20">
+        <v>18</v>
+      </c>
+      <c r="H25" s="12">
         <v>0.25</v>
       </c>
-      <c r="I25" s="24">
+      <c r="I25" s="12">
         <v>0.1</v>
       </c>
-      <c r="J25" s="24">
+      <c r="J25" s="12">
         <v>0.2</v>
       </c>
-      <c r="K25" s="19">
-        <v>0</v>
-      </c>
-      <c r="L25" s="19" t="s">
+      <c r="K25" s="7">
+        <v>0</v>
+      </c>
+      <c r="L25" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="M25" s="19" t="s">
+      <c r="M25" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="19"/>
-      <c r="S25" s="19"/>
-      <c r="T25" s="19"/>
-      <c r="U25" s="22">
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="7"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="V25" s="22">
+      <c r="V25" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="W25" s="19"/>
-      <c r="X25" s="19"/>
-      <c r="Y25" s="19"/>
-      <c r="Z25" s="19"/>
-      <c r="AA25" s="19"/>
-      <c r="AB25" s="19"/>
-      <c r="AC25" s="19"/>
-      <c r="AD25" s="19"/>
-      <c r="AE25" s="19"/>
-      <c r="AF25" s="22"/>
-      <c r="AG25" s="22"/>
-      <c r="AH25" s="19"/>
-      <c r="AI25" s="21"/>
-      <c r="AJ25" s="19"/>
-      <c r="AK25" s="19"/>
-      <c r="AL25" s="19"/>
-      <c r="AM25" s="19"/>
-      <c r="AN25" s="19"/>
-      <c r="AO25" s="19"/>
-      <c r="AP25" s="19"/>
-      <c r="AQ25" s="25"/>
-      <c r="AR25" s="25"/>
-      <c r="AS25" s="21" t="s">
+      <c r="W25" s="7"/>
+      <c r="X25" s="7"/>
+      <c r="Y25" s="7"/>
+      <c r="Z25" s="7"/>
+      <c r="AA25" s="7"/>
+      <c r="AB25" s="7"/>
+      <c r="AC25" s="7"/>
+      <c r="AD25" s="7"/>
+      <c r="AE25" s="7"/>
+      <c r="AF25" s="10"/>
+      <c r="AG25" s="10"/>
+      <c r="AH25" s="7"/>
+      <c r="AI25" s="9"/>
+      <c r="AJ25" s="7"/>
+      <c r="AK25" s="7"/>
+      <c r="AL25" s="7"/>
+      <c r="AM25" s="7"/>
+      <c r="AN25" s="7"/>
+      <c r="AO25" s="7"/>
+      <c r="AP25" s="7"/>
+      <c r="AQ25" s="13"/>
+      <c r="AR25" s="13"/>
+      <c r="AS25" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="AT25" s="19"/>
-      <c r="AU25" s="19"/>
-      <c r="AV25" s="19"/>
-      <c r="AW25" s="19"/>
-      <c r="AX25" s="19"/>
+      <c r="AT25" s="7"/>
+      <c r="AU25" s="7"/>
+      <c r="AV25" s="7"/>
+      <c r="AW25" s="7"/>
+      <c r="AX25" s="7"/>
     </row>
     <row r="26" spans="1:50" ht="170" x14ac:dyDescent="0.45">
-      <c r="A26" s="19"/>
-      <c r="B26" s="26" t="s">
+      <c r="A26" s="7"/>
+      <c r="B26" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="C26" s="26" t="s">
+      <c r="C26" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="D26" s="26" t="s">
+      <c r="D26" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="14">
         <v>30</v>
       </c>
-      <c r="F26" s="33">
-        <v>18</v>
-      </c>
-      <c r="G26" s="26">
+      <c r="F26" s="21">
+        <v>12</v>
+      </c>
+      <c r="G26" s="21">
         <v>10</v>
       </c>
-      <c r="H26" s="27">
-        <v>0</v>
-      </c>
-      <c r="I26" s="27">
-        <v>0</v>
-      </c>
-      <c r="J26" s="27">
-        <v>0</v>
-      </c>
-      <c r="K26" s="19">
+      <c r="H26" s="15">
+        <v>0</v>
+      </c>
+      <c r="I26" s="15">
+        <v>0</v>
+      </c>
+      <c r="J26" s="15">
+        <v>0</v>
+      </c>
+      <c r="K26" s="7">
         <v>1</v>
       </c>
-      <c r="L26" s="26" t="s">
+      <c r="L26" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="M26" s="26" t="s">
+      <c r="M26" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="N26" s="26">
-        <v>0</v>
-      </c>
-      <c r="O26" s="26">
+      <c r="N26" s="14">
+        <v>0</v>
+      </c>
+      <c r="O26" s="14">
         <v>1</v>
       </c>
-      <c r="P26" s="26">
+      <c r="P26" s="14">
         <v>1</v>
       </c>
-      <c r="Q26" s="26">
+      <c r="Q26" s="14">
         <v>1</v>
       </c>
-      <c r="R26" s="26">
+      <c r="R26" s="14">
         <v>2</v>
       </c>
-      <c r="S26" s="26">
-        <v>0</v>
-      </c>
-      <c r="T26" s="28" t="s">
+      <c r="S26" s="14">
+        <v>0</v>
+      </c>
+      <c r="T26" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="U26" s="29">
+      <c r="U26" s="17">
         <v>2.2999999999999998</v>
       </c>
-      <c r="V26" s="29">
+      <c r="V26" s="17">
         <v>2.2999999999999998</v>
       </c>
-      <c r="W26" s="26"/>
-      <c r="X26" s="26"/>
-      <c r="Y26" s="26"/>
-      <c r="Z26" s="26"/>
-      <c r="AA26" s="26"/>
-      <c r="AB26" s="26"/>
-      <c r="AC26" s="26"/>
-      <c r="AD26" s="26"/>
-      <c r="AE26" s="26"/>
-      <c r="AF26" s="29"/>
-      <c r="AG26" s="29"/>
-      <c r="AH26" s="26"/>
-      <c r="AI26" s="30"/>
-      <c r="AJ26" s="28"/>
-      <c r="AK26" s="28"/>
-      <c r="AL26" s="28"/>
-      <c r="AM26" s="28"/>
-      <c r="AN26" s="28"/>
-      <c r="AO26" s="28"/>
-      <c r="AP26" s="28"/>
-      <c r="AQ26" s="31"/>
-      <c r="AR26" s="31"/>
-      <c r="AS26" s="30" t="s">
+      <c r="W26" s="14"/>
+      <c r="X26" s="14"/>
+      <c r="Y26" s="14"/>
+      <c r="Z26" s="14"/>
+      <c r="AA26" s="14"/>
+      <c r="AB26" s="14"/>
+      <c r="AC26" s="14"/>
+      <c r="AD26" s="14"/>
+      <c r="AE26" s="14"/>
+      <c r="AF26" s="17"/>
+      <c r="AG26" s="17"/>
+      <c r="AH26" s="14"/>
+      <c r="AI26" s="18"/>
+      <c r="AJ26" s="16"/>
+      <c r="AK26" s="16"/>
+      <c r="AL26" s="16"/>
+      <c r="AM26" s="16"/>
+      <c r="AN26" s="16"/>
+      <c r="AO26" s="16"/>
+      <c r="AP26" s="16"/>
+      <c r="AQ26" s="19"/>
+      <c r="AR26" s="19"/>
+      <c r="AS26" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="AT26" s="28"/>
-      <c r="AU26" s="28"/>
-      <c r="AV26" s="28"/>
-      <c r="AW26" s="28"/>
-      <c r="AX26" s="28"/>
+      <c r="AT26" s="16"/>
+      <c r="AU26" s="16"/>
+      <c r="AV26" s="16"/>
+      <c r="AW26" s="16"/>
+      <c r="AX26" s="16"/>
     </row>
     <row r="27" spans="1:50" ht="102" x14ac:dyDescent="0.45">
-      <c r="A27" s="19" t="s">
+      <c r="A27" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="E27" s="19" t="s">
+      <c r="E27" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="F27" s="19" t="s">
+      <c r="F27" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="G27" s="19" t="s">
+      <c r="G27" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="H27" s="19" t="s">
+      <c r="H27" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="I27" s="19" t="s">
+      <c r="I27" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="J27" s="19" t="s">
+      <c r="J27" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="K27" s="19" t="s">
+      <c r="K27" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="L27" s="19" t="s">
+      <c r="L27" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="M27" s="19" t="s">
+      <c r="M27" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="N27" s="21" t="s">
+      <c r="N27" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="O27" s="19" t="s">
+      <c r="O27" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="P27" s="19" t="s">
+      <c r="P27" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="Q27" s="19" t="s">
+      <c r="Q27" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="R27" s="19" t="s">
+      <c r="R27" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="S27" s="19" t="s">
+      <c r="S27" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="T27" s="19" t="s">
+      <c r="T27" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="U27" s="19" t="s">
+      <c r="U27" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="V27" s="19" t="s">
+      <c r="V27" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="W27" s="19" t="s">
+      <c r="W27" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="X27" s="19" t="s">
+      <c r="X27" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="Y27" s="19" t="s">
+      <c r="Y27" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="Z27" s="19" t="s">
+      <c r="Z27" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="AA27" s="19" t="s">
+      <c r="AA27" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="AB27" s="19" t="s">
+      <c r="AB27" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="AC27" s="19" t="s">
+      <c r="AC27" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="AD27" s="19" t="s">
+      <c r="AD27" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="AE27" s="19" t="s">
+      <c r="AE27" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="AF27" s="19" t="s">
+      <c r="AF27" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AG27" s="19" t="s">
+      <c r="AG27" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="AH27" s="19" t="s">
+      <c r="AH27" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="AI27" s="21" t="s">
+      <c r="AI27" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="AJ27" s="21" t="s">
+      <c r="AJ27" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="AK27" s="21" t="s">
+      <c r="AK27" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="AL27" s="21" t="s">
+      <c r="AL27" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="AM27" s="21" t="s">
+      <c r="AM27" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="AN27" s="21" t="s">
+      <c r="AN27" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="AO27" s="21" t="s">
+      <c r="AO27" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="AP27" s="21" t="s">
+      <c r="AP27" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="AQ27" s="19" t="s">
+      <c r="AQ27" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="AR27" s="19" t="s">
+      <c r="AR27" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="AS27" s="19" t="s">
+      <c r="AS27" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="AT27" s="19" t="s">
+      <c r="AT27" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="AU27" s="19" t="s">
+      <c r="AU27" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="AV27" s="19" t="s">
+      <c r="AV27" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="AW27" s="19" t="s">
+      <c r="AW27" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="AX27" s="19" t="s">
+      <c r="AX27" s="7" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:50" x14ac:dyDescent="0.45">
-      <c r="A28" s="19" t="s">
+      <c r="A28" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="19"/>
-      <c r="T28" s="19"/>
-      <c r="U28" s="19"/>
-      <c r="V28" s="19"/>
-      <c r="W28" s="19"/>
-      <c r="X28" s="19"/>
-      <c r="Y28" s="19"/>
-      <c r="Z28" s="19"/>
-      <c r="AA28" s="19"/>
-      <c r="AB28" s="19"/>
-      <c r="AC28" s="19"/>
-      <c r="AD28" s="19"/>
-      <c r="AE28" s="19"/>
-      <c r="AF28" s="19"/>
-      <c r="AG28" s="19"/>
-      <c r="AH28" s="19"/>
-      <c r="AI28" s="19"/>
-      <c r="AJ28" s="19"/>
-      <c r="AK28" s="19"/>
-      <c r="AL28" s="19"/>
-      <c r="AM28" s="19"/>
-      <c r="AN28" s="19"/>
-      <c r="AO28" s="19"/>
-      <c r="AP28" s="19"/>
-      <c r="AQ28" s="19"/>
-      <c r="AR28" s="19"/>
-      <c r="AS28" s="19"/>
-      <c r="AT28" s="19"/>
-      <c r="AU28" s="19"/>
-      <c r="AV28" s="19"/>
-      <c r="AW28" s="19"/>
-      <c r="AX28" s="19"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
+      <c r="U28" s="7"/>
+      <c r="V28" s="7"/>
+      <c r="W28" s="7"/>
+      <c r="X28" s="7"/>
+      <c r="Y28" s="7"/>
+      <c r="Z28" s="7"/>
+      <c r="AA28" s="7"/>
+      <c r="AB28" s="7"/>
+      <c r="AC28" s="7"/>
+      <c r="AD28" s="7"/>
+      <c r="AE28" s="7"/>
+      <c r="AF28" s="7"/>
+      <c r="AG28" s="7"/>
+      <c r="AH28" s="7"/>
+      <c r="AI28" s="7"/>
+      <c r="AJ28" s="7"/>
+      <c r="AK28" s="7"/>
+      <c r="AL28" s="7"/>
+      <c r="AM28" s="7"/>
+      <c r="AN28" s="7"/>
+      <c r="AO28" s="7"/>
+      <c r="AP28" s="7"/>
+      <c r="AQ28" s="7"/>
+      <c r="AR28" s="7"/>
+      <c r="AS28" s="7"/>
+      <c r="AT28" s="7"/>
+      <c r="AU28" s="7"/>
+      <c r="AV28" s="7"/>
+      <c r="AW28" s="7"/>
+      <c r="AX28" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5108,763 +5145,813 @@
   <dimension ref="A1:Q26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.5" style="12" customWidth="1"/>
-    <col min="2" max="2" width="17.08203125" style="12" customWidth="1"/>
-    <col min="3" max="3" width="47.25" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" style="12" customWidth="1"/>
-    <col min="5" max="5" width="10.75" style="12" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" style="12" customWidth="1"/>
-    <col min="7" max="9" width="10.75" style="12" customWidth="1"/>
-    <col min="10" max="10" width="8.83203125" style="12" customWidth="1"/>
-    <col min="11" max="11" width="10.75" style="12" customWidth="1"/>
-    <col min="12" max="12" width="8.83203125" style="12" customWidth="1"/>
-    <col min="13" max="13" width="10.75" style="12" customWidth="1"/>
-    <col min="14" max="14" width="8.83203125" style="12" customWidth="1"/>
-    <col min="15" max="15" width="10.75" style="12" customWidth="1"/>
-    <col min="16" max="38" width="15.58203125" style="12" customWidth="1"/>
-    <col min="39" max="16384" width="9" style="12"/>
+    <col min="1" max="1" width="10.5" style="23" customWidth="1"/>
+    <col min="2" max="2" width="17.08203125" style="23" customWidth="1"/>
+    <col min="3" max="3" width="47.25" style="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" style="23" customWidth="1"/>
+    <col min="5" max="5" width="10.75" style="23" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" style="23" customWidth="1"/>
+    <col min="7" max="9" width="10.75" style="23" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" style="23" customWidth="1"/>
+    <col min="11" max="11" width="10.75" style="23" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" style="23" customWidth="1"/>
+    <col min="13" max="13" width="10.75" style="23" customWidth="1"/>
+    <col min="14" max="14" width="8.83203125" style="23" customWidth="1"/>
+    <col min="15" max="15" width="10.75" style="23" customWidth="1"/>
+    <col min="16" max="38" width="15.58203125" style="23" customWidth="1"/>
+    <col min="39" max="16384" width="9" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="23" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="O4" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="Q4" s="25" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="23" t="s">
         <v>224</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="23" t="s">
         <v>226</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="23" t="s">
         <v>227</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="23" t="s">
         <v>228</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="L5" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="23" t="s">
         <v>234</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="25" t="s">
         <v>235</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="Q5" s="25" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="25" t="s">
         <v>257</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="25" t="s">
         <v>272</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="23">
         <v>2</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9">
+      <c r="F6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="P6" s="23">
         <v>4</v>
       </c>
-      <c r="Q6" s="9">
+      <c r="Q6" s="23">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="25" t="s">
         <v>240</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="25" t="s">
         <v>258</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="23">
         <v>4</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="23">
         <v>6</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="23">
         <v>1</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="23">
         <v>2</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="L7" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="23">
         <v>3</v>
       </c>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9">
+      <c r="P7" s="23">
         <v>3</v>
       </c>
-      <c r="Q7" s="9">
+      <c r="Q7" s="23">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="25" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="25" t="s">
         <v>259</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="23">
         <v>1</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="23">
         <v>3</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="23">
         <v>4</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="23">
         <v>6</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="L8" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="M8" s="9">
+      <c r="M8" s="23">
         <v>2</v>
       </c>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9">
+      <c r="P8" s="23">
         <v>3</v>
       </c>
-      <c r="Q8" s="9">
+      <c r="Q8" s="23">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="25" t="s">
         <v>242</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="25" t="s">
         <v>260</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="23">
         <v>1</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="23">
         <v>3</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="23">
         <v>4</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="23">
         <v>6</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="L9" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="M9" s="9">
+      <c r="M9" s="23">
         <v>2</v>
       </c>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9">
+      <c r="P9" s="23">
         <v>3</v>
       </c>
-      <c r="Q9" s="9">
+      <c r="Q9" s="23">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="25" t="s">
         <v>261</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="25" t="s">
         <v>269</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="23">
         <v>2</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="23">
         <v>5</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="25" t="s">
         <v>270</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="23">
         <v>4</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="J10" s="25" t="s">
         <v>270</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="23">
         <v>6</v>
       </c>
-      <c r="L10" s="15" t="s">
+      <c r="L10" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="M10" s="16">
+      <c r="M10" s="23">
         <v>1</v>
       </c>
-      <c r="N10" s="15" t="s">
+      <c r="N10" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="O10" s="16">
+      <c r="O10" s="23">
         <v>3</v>
       </c>
-      <c r="P10" s="16">
+      <c r="P10" s="23">
         <v>4</v>
       </c>
-      <c r="Q10" s="16">
+      <c r="Q10" s="23">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="25" t="s">
         <v>244</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="25" t="s">
         <v>262</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="31" t="s">
         <v>270</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="23">
         <v>6</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="23">
         <v>4</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="25" t="s">
         <v>272</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="23">
         <v>2</v>
       </c>
-      <c r="J11" s="8"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9">
+      <c r="J11" s="25"/>
+      <c r="P11" s="23">
         <v>4</v>
       </c>
-      <c r="Q11" s="9">
+      <c r="Q11" s="23">
         <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="25" t="s">
         <v>245</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="25" t="s">
         <v>246</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="23">
         <v>4</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="23">
         <v>6</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="23">
         <v>1</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="J12" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="23">
         <v>3</v>
       </c>
-      <c r="L12"/>
-      <c r="N12"/>
-      <c r="P12" s="12">
+      <c r="L12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="P12" s="23">
         <v>3</v>
       </c>
-      <c r="Q12" s="12">
+      <c r="Q12" s="23">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="25" t="s">
         <v>247</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="25" t="s">
         <v>248</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="23">
         <v>1</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="23">
         <v>2</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="23">
         <v>3</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="J13" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="23">
         <v>5</v>
       </c>
-      <c r="L13" s="8" t="s">
+      <c r="L13" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="M13" s="9">
+      <c r="M13" s="6">
+        <v>4</v>
+      </c>
+      <c r="N13" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="O13" s="6">
+        <v>6</v>
+      </c>
+      <c r="P13" s="23">
+        <v>4</v>
+      </c>
+      <c r="Q13" s="23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="B14" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="E14" s="23">
+        <v>5</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G14" s="23">
+        <v>4</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="I14" s="23">
+        <v>6</v>
+      </c>
+      <c r="J14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="P14" s="23">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A15" s="7"/>
+      <c r="B15" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="E15" s="33">
+        <v>5</v>
+      </c>
+      <c r="F15" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="G15" s="33">
+        <v>4</v>
+      </c>
+      <c r="H15" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="I15" s="33">
+        <v>6</v>
+      </c>
+      <c r="J15" s="33"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="33"/>
+      <c r="N15" s="33"/>
+      <c r="O15" s="33"/>
+      <c r="P15" s="6">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A16" s="7"/>
+      <c r="B16" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>269</v>
+      </c>
+      <c r="E16" s="33">
+        <v>2</v>
+      </c>
+      <c r="F16" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="G16" s="33">
         <v>1</v>
       </c>
-      <c r="N13" s="8" t="s">
+      <c r="H16" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="I16" s="33">
+        <v>3</v>
+      </c>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="6">
+        <v>4</v>
+      </c>
+      <c r="Q16" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="B17" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="E17" s="6">
+        <v>2</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" s="6">
+        <v>5</v>
+      </c>
+      <c r="H17" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="I17" s="6">
+        <v>6</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="K17" s="6">
+        <v>4</v>
+      </c>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="6">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="B18" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="E18" s="6">
+        <v>6</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="G18" s="6">
+        <v>4</v>
+      </c>
+      <c r="H18" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="I18" s="6">
+        <v>2</v>
+      </c>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="6">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="B20" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="H20" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="I20" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="J20" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="K20" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="L20" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="M20" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="N20" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="O20" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="P20" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q20" s="25" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A21" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A22" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="E22" s="28">
+        <v>1</v>
+      </c>
+      <c r="F22" s="29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="B23" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="E23" s="28">
+        <v>2</v>
+      </c>
+      <c r="F23" s="29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="B24" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="O13" s="9">
+      <c r="C24" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="28">
         <v>3</v>
       </c>
-      <c r="P13" s="12">
-        <v>4</v>
-      </c>
-      <c r="Q13" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B14" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="D14" t="s">
-        <v>141</v>
-      </c>
-      <c r="E14" s="12">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>152</v>
-      </c>
-      <c r="G14" s="12">
-        <v>4</v>
-      </c>
-      <c r="H14" t="s">
-        <v>160</v>
-      </c>
-      <c r="I14" s="12">
+      <c r="F24" s="29">
         <v>6</v>
       </c>
-      <c r="J14"/>
-      <c r="L14"/>
-      <c r="N14"/>
-      <c r="P14" s="12">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A15"/>
-      <c r="B15" t="s">
-        <v>263</v>
-      </c>
-      <c r="C15" t="s">
-        <v>264</v>
-      </c>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15"/>
-      <c r="H15"/>
-      <c r="I15"/>
-      <c r="J15"/>
-      <c r="K15"/>
-      <c r="L15"/>
-      <c r="M15"/>
-      <c r="N15"/>
-      <c r="O15"/>
-      <c r="P15"/>
-      <c r="Q15"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A16"/>
-      <c r="B16" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B17" t="s">
-        <v>267</v>
-      </c>
-      <c r="C17" t="s">
-        <v>268</v>
-      </c>
-      <c r="D17"/>
-      <c r="E17"/>
-      <c r="F17"/>
-      <c r="G17"/>
-      <c r="H17"/>
-      <c r="I17"/>
-      <c r="J17"/>
-      <c r="K17"/>
-      <c r="L17"/>
-      <c r="M17"/>
-      <c r="N17"/>
-      <c r="O17"/>
-      <c r="P17"/>
-      <c r="Q17"/>
-    </row>
-    <row r="18" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="18"/>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="18"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B19"/>
-      <c r="C19"/>
-      <c r="D19"/>
-      <c r="E19"/>
-      <c r="F19"/>
-      <c r="G19"/>
-      <c r="H19"/>
-      <c r="I19"/>
-      <c r="J19"/>
-      <c r="K19"/>
-      <c r="L19"/>
-      <c r="M19"/>
-      <c r="N19"/>
-      <c r="O19"/>
-      <c r="P19"/>
-      <c r="Q19"/>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B20" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="N20" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="P20" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="Q20" s="6" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A21" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="B21"/>
-      <c r="C21"/>
-      <c r="D21"/>
-      <c r="E21"/>
-      <c r="F21"/>
-      <c r="G21"/>
-      <c r="H21"/>
-      <c r="I21"/>
-      <c r="J21"/>
-      <c r="K21"/>
-      <c r="L21"/>
-      <c r="M21"/>
-      <c r="N21"/>
-      <c r="O21"/>
-      <c r="P21"/>
-      <c r="Q21"/>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A22" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1</v>
-      </c>
-      <c r="F22" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B23" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="E23" s="3">
-        <v>2</v>
-      </c>
-      <c r="F23" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B24" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" s="3">
-        <v>3</v>
-      </c>
-      <c r="F24" s="4">
-        <v>6</v>
-      </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="2"/>
+      <c r="E25" s="30"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="7" t="s">
         <v>253</v>
       </c>
     </row>

--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/2구역 전투 테이블 V1.3.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/2구역 전투 테이블 V1.3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\개인\게임인재원 7기\Hero Influence\기획서\Hero Influence_강현재\밸런스\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HeroInfluencetmp\Assets\_ProtoType_Merge\ASB\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14546355-506E-48ED-9D28-345DDBDFBD24}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355A9002-06BC-414D-8CEA-68B3F2B6B46D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14300" yWindow="0" windowWidth="14610" windowHeight="15590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14300" yWindow="0" windowWidth="14610" windowHeight="15590" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수정 내역" sheetId="41" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="297">
   <si>
     <t>2구역 메인/서브 이벤트 전투 테이블</t>
   </si>
@@ -1124,6 +1124,14 @@
   </si>
   <si>
     <t>보스 스테이터스 밸런스</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{7,3}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{7,3}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1361,12 +1369,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1391,6 +1393,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="5" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2483,23 +2491,23 @@
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.45">
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
     </row>
     <row r="4" spans="1:50" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="s">
@@ -4498,8 +4506,8 @@
       <c r="AB22" s="7">
         <v>1</v>
       </c>
-      <c r="AC22" s="7">
-        <v>2</v>
+      <c r="AC22" s="14" t="s">
+        <v>296</v>
       </c>
       <c r="AD22" s="7">
         <v>0</v>
@@ -4723,8 +4731,8 @@
       <c r="AM24" s="7">
         <v>1</v>
       </c>
-      <c r="AN24" s="7">
-        <v>2</v>
+      <c r="AN24" s="14" t="s">
+        <v>296</v>
       </c>
       <c r="AO24" s="7">
         <v>0</v>
@@ -4879,8 +4887,8 @@
       <c r="Q26" s="14">
         <v>1</v>
       </c>
-      <c r="R26" s="14">
-        <v>2</v>
+      <c r="R26" s="14" t="s">
+        <v>295</v>
       </c>
       <c r="S26" s="14">
         <v>0</v>
@@ -5137,6 +5145,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5145,504 +5154,504 @@
   <dimension ref="A1:Q26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.5" style="23" customWidth="1"/>
-    <col min="2" max="2" width="17.08203125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="47.25" style="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" style="23" customWidth="1"/>
-    <col min="5" max="5" width="10.75" style="23" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" style="23" customWidth="1"/>
-    <col min="7" max="9" width="10.75" style="23" customWidth="1"/>
-    <col min="10" max="10" width="8.83203125" style="23" customWidth="1"/>
-    <col min="11" max="11" width="10.75" style="23" customWidth="1"/>
-    <col min="12" max="12" width="8.83203125" style="23" customWidth="1"/>
-    <col min="13" max="13" width="10.75" style="23" customWidth="1"/>
-    <col min="14" max="14" width="8.83203125" style="23" customWidth="1"/>
-    <col min="15" max="15" width="10.75" style="23" customWidth="1"/>
-    <col min="16" max="38" width="15.58203125" style="23" customWidth="1"/>
-    <col min="39" max="16384" width="9" style="23"/>
+    <col min="1" max="1" width="10.5" style="22" customWidth="1"/>
+    <col min="2" max="2" width="17.08203125" style="22" customWidth="1"/>
+    <col min="3" max="3" width="47.25" style="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" style="22" customWidth="1"/>
+    <col min="5" max="5" width="10.75" style="22" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" style="22" customWidth="1"/>
+    <col min="7" max="9" width="10.75" style="22" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" style="22" customWidth="1"/>
+    <col min="11" max="11" width="10.75" style="22" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" style="22" customWidth="1"/>
+    <col min="13" max="13" width="10.75" style="22" customWidth="1"/>
+    <col min="14" max="14" width="8.83203125" style="22" customWidth="1"/>
+    <col min="15" max="15" width="10.75" style="22" customWidth="1"/>
+    <col min="16" max="38" width="15.58203125" style="22" customWidth="1"/>
+    <col min="39" max="16384" width="9" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="33" t="s">
         <v>223</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="25" t="s">
+      <c r="H4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="23" t="s">
+      <c r="K4" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="25" t="s">
+      <c r="L4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="23" t="s">
+      <c r="M4" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="25" t="s">
+      <c r="N4" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="23" t="s">
+      <c r="O4" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="P4" s="25" t="s">
+      <c r="P4" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="25" t="s">
+      <c r="Q4" s="23" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="23" t="s">
         <v>225</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="22" t="s">
         <v>227</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="22" t="s">
         <v>230</v>
       </c>
-      <c r="J5" s="23" t="s">
+      <c r="J5" s="22" t="s">
         <v>231</v>
       </c>
-      <c r="K5" s="23" t="s">
+      <c r="K5" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="L5" s="23" t="s">
+      <c r="L5" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="M5" s="23" t="s">
+      <c r="M5" s="22" t="s">
         <v>234</v>
       </c>
-      <c r="N5" s="25" t="s">
+      <c r="N5" s="23" t="s">
         <v>235</v>
       </c>
-      <c r="O5" s="25" t="s">
+      <c r="O5" s="23" t="s">
         <v>236</v>
       </c>
-      <c r="P5" s="25" t="s">
+      <c r="P5" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="Q5" s="25" t="s">
+      <c r="Q5" s="23" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="23" t="s">
         <v>239</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="23" t="s">
         <v>257</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="23" t="s">
         <v>272</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="22">
         <v>2</v>
       </c>
-      <c r="F6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="P6" s="23">
+      <c r="F6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="P6" s="22">
         <v>4</v>
       </c>
-      <c r="Q6" s="23">
+      <c r="Q6" s="22">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="23" t="s">
         <v>240</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="23" t="s">
         <v>258</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="22">
         <v>4</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="22">
         <v>6</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="H7" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="22">
         <v>1</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="K7" s="23">
+      <c r="K7" s="22">
         <v>2</v>
       </c>
-      <c r="L7" s="25" t="s">
+      <c r="L7" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="M7" s="23">
+      <c r="M7" s="22">
         <v>3</v>
       </c>
-      <c r="P7" s="23">
+      <c r="P7" s="22">
         <v>3</v>
       </c>
-      <c r="Q7" s="23">
+      <c r="Q7" s="22">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="23" t="s">
         <v>259</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="22">
         <v>1</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="F8" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="22">
         <v>3</v>
       </c>
-      <c r="H8" s="25" t="s">
+      <c r="H8" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="22">
         <v>4</v>
       </c>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="K8" s="23">
+      <c r="K8" s="22">
         <v>6</v>
       </c>
-      <c r="L8" s="25" t="s">
+      <c r="L8" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="M8" s="23">
+      <c r="M8" s="22">
         <v>2</v>
       </c>
-      <c r="P8" s="23">
+      <c r="P8" s="22">
         <v>3</v>
       </c>
-      <c r="Q8" s="23">
+      <c r="Q8" s="22">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="23" t="s">
         <v>260</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="22">
         <v>1</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="22">
         <v>3</v>
       </c>
-      <c r="H9" s="25" t="s">
+      <c r="H9" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="22">
         <v>4</v>
       </c>
-      <c r="J9" s="25" t="s">
+      <c r="J9" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="K9" s="23">
+      <c r="K9" s="22">
         <v>6</v>
       </c>
-      <c r="L9" s="25" t="s">
+      <c r="L9" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="M9" s="23">
+      <c r="M9" s="22">
         <v>2</v>
       </c>
-      <c r="P9" s="23">
+      <c r="P9" s="22">
         <v>3</v>
       </c>
-      <c r="Q9" s="23">
+      <c r="Q9" s="22">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="23" t="s">
         <v>243</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="23" t="s">
         <v>261</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="23" t="s">
         <v>269</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="22">
         <v>2</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="22">
         <v>5</v>
       </c>
-      <c r="H10" s="25" t="s">
+      <c r="H10" s="23" t="s">
         <v>270</v>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="22">
         <v>4</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="23" t="s">
         <v>270</v>
       </c>
-      <c r="K10" s="23">
+      <c r="K10" s="22">
         <v>6</v>
       </c>
-      <c r="L10" s="25" t="s">
+      <c r="L10" s="23" t="s">
         <v>271</v>
       </c>
-      <c r="M10" s="23">
+      <c r="M10" s="22">
         <v>1</v>
       </c>
-      <c r="N10" s="25" t="s">
+      <c r="N10" s="23" t="s">
         <v>271</v>
       </c>
-      <c r="O10" s="23">
+      <c r="O10" s="22">
         <v>3</v>
       </c>
-      <c r="P10" s="23">
+      <c r="P10" s="22">
         <v>4</v>
       </c>
-      <c r="Q10" s="23">
+      <c r="Q10" s="22">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="23" t="s">
         <v>244</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="23" t="s">
         <v>262</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="D11" s="29" t="s">
         <v>270</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="22">
         <v>6</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="23" t="s">
         <v>271</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="22">
         <v>4</v>
       </c>
-      <c r="H11" s="25" t="s">
+      <c r="H11" s="23" t="s">
         <v>272</v>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="22">
         <v>2</v>
       </c>
-      <c r="J11" s="25"/>
-      <c r="P11" s="23">
+      <c r="J11" s="23"/>
+      <c r="P11" s="22">
         <v>4</v>
       </c>
-      <c r="Q11" s="23">
+      <c r="Q11" s="22">
         <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="23" t="s">
         <v>245</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="23" t="s">
         <v>246</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D12" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="22">
         <v>4</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="F12" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="22">
         <v>6</v>
       </c>
-      <c r="H12" s="25" t="s">
+      <c r="H12" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="22">
         <v>1</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="K12" s="23">
+      <c r="K12" s="22">
         <v>3</v>
       </c>
       <c r="L12" s="7"/>
       <c r="N12" s="7"/>
-      <c r="P12" s="23">
+      <c r="P12" s="22">
         <v>3</v>
       </c>
-      <c r="Q12" s="23">
+      <c r="Q12" s="22">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="23" t="s">
         <v>247</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="22">
         <v>1</v>
       </c>
-      <c r="F13" s="25" t="s">
+      <c r="F13" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="22">
         <v>2</v>
       </c>
-      <c r="H13" s="25" t="s">
+      <c r="H13" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="I13" s="23">
+      <c r="I13" s="22">
         <v>3</v>
       </c>
-      <c r="J13" s="25" t="s">
+      <c r="J13" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="K13" s="23">
+      <c r="K13" s="22">
         <v>5</v>
       </c>
-      <c r="L13" s="25" t="s">
+      <c r="L13" s="23" t="s">
         <v>77</v>
       </c>
       <c r="M13" s="6">
         <v>4</v>
       </c>
-      <c r="N13" s="25" t="s">
+      <c r="N13" s="23" t="s">
         <v>77</v>
       </c>
       <c r="O13" s="6">
         <v>6</v>
       </c>
-      <c r="P13" s="23">
+      <c r="P13" s="22">
         <v>4</v>
       </c>
-      <c r="Q13" s="23">
+      <c r="Q13" s="22">
         <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="23" t="s">
         <v>249</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="23" t="s">
         <v>250</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="22">
         <v>5</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="22">
         <v>4</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="22">
         <v>6</v>
       </c>
       <c r="J14" s="7"/>
       <c r="L14" s="7"/>
       <c r="N14" s="7"/>
-      <c r="P14" s="23">
+      <c r="P14" s="22">
         <v>5</v>
       </c>
-      <c r="Q14" s="23">
+      <c r="Q14" s="22">
         <v>7</v>
       </c>
     </row>
@@ -5654,30 +5663,30 @@
       <c r="C15" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="D15" s="33" t="s">
+      <c r="D15" s="31" t="s">
         <v>292</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="31">
         <v>5</v>
       </c>
-      <c r="F15" s="33" t="s">
+      <c r="F15" s="31" t="s">
         <v>270</v>
       </c>
-      <c r="G15" s="33">
+      <c r="G15" s="31">
         <v>4</v>
       </c>
-      <c r="H15" s="33" t="s">
+      <c r="H15" s="31" t="s">
         <v>270</v>
       </c>
-      <c r="I15" s="33">
+      <c r="I15" s="31">
         <v>6</v>
       </c>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="33"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="31"/>
       <c r="P15" s="6">
         <v>4</v>
       </c>
@@ -5693,30 +5702,30 @@
       <c r="C16" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="31" t="s">
         <v>269</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="31">
         <v>2</v>
       </c>
-      <c r="F16" s="33" t="s">
+      <c r="F16" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="G16" s="33">
+      <c r="G16" s="31">
         <v>1</v>
       </c>
-      <c r="H16" s="33" t="s">
+      <c r="H16" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="I16" s="33">
+      <c r="I16" s="31">
         <v>3</v>
       </c>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="31"/>
       <c r="P16" s="6">
         <v>4</v>
       </c>
@@ -5743,7 +5752,7 @@
       <c r="G17" s="6">
         <v>5</v>
       </c>
-      <c r="H17" s="32" t="s">
+      <c r="H17" s="30" t="s">
         <v>270</v>
       </c>
       <c r="I17" s="6">
@@ -5773,7 +5782,7 @@
       <c r="C18" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="30" t="s">
         <v>270</v>
       </c>
       <c r="E18" s="6">
@@ -5785,7 +5794,7 @@
       <c r="G18" s="6">
         <v>4</v>
       </c>
-      <c r="H18" s="32" t="s">
+      <c r="H18" s="30" t="s">
         <v>272</v>
       </c>
       <c r="I18" s="6">
@@ -5823,57 +5832,57 @@
       <c r="Q19" s="7"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="22" t="s">
         <v>274</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="23" t="s">
         <v>275</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="24" t="s">
         <v>276</v>
       </c>
-      <c r="E20" s="27" t="s">
+      <c r="E20" s="25" t="s">
         <v>277</v>
       </c>
-      <c r="F20" s="26" t="s">
+      <c r="F20" s="24" t="s">
         <v>276</v>
       </c>
-      <c r="G20" s="27" t="s">
+      <c r="G20" s="25" t="s">
         <v>277</v>
       </c>
-      <c r="H20" s="26" t="s">
+      <c r="H20" s="24" t="s">
         <v>276</v>
       </c>
-      <c r="I20" s="27" t="s">
+      <c r="I20" s="25" t="s">
         <v>277</v>
       </c>
-      <c r="J20" s="26" t="s">
+      <c r="J20" s="24" t="s">
         <v>276</v>
       </c>
-      <c r="K20" s="27" t="s">
+      <c r="K20" s="25" t="s">
         <v>277</v>
       </c>
-      <c r="L20" s="26" t="s">
+      <c r="L20" s="24" t="s">
         <v>276</v>
       </c>
-      <c r="M20" s="27" t="s">
+      <c r="M20" s="25" t="s">
         <v>277</v>
       </c>
-      <c r="N20" s="26" t="s">
+      <c r="N20" s="24" t="s">
         <v>276</v>
       </c>
-      <c r="O20" s="27" t="s">
+      <c r="O20" s="25" t="s">
         <v>277</v>
       </c>
-      <c r="P20" s="25" t="s">
+      <c r="P20" s="23" t="s">
         <v>278</v>
       </c>
-      <c r="Q20" s="25" t="s">
+      <c r="Q20" s="23" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="22" t="s">
         <v>176</v>
       </c>
       <c r="B21" s="7"/>
@@ -5894,7 +5903,7 @@
       <c r="Q21" s="7"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="22" t="s">
         <v>273</v>
       </c>
       <c r="B22" s="7" t="s">
@@ -5903,10 +5912,10 @@
       <c r="C22" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="26">
         <v>1</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="27">
         <v>4</v>
       </c>
     </row>
@@ -5917,10 +5926,10 @@
       <c r="C23" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="26">
         <v>2</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="27">
         <v>5</v>
       </c>
     </row>
@@ -5931,10 +5940,10 @@
       <c r="C24" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="26">
         <v>3</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="27">
         <v>6</v>
       </c>
     </row>
@@ -5945,7 +5954,7 @@
       <c r="C25" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="30"/>
+      <c r="E25" s="28"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B26" s="7" t="s">

--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/2구역 전투 테이블 V1.3.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/2구역 전투 테이블 V1.3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HeroInfluencetmp\Assets\_ProtoType_Merge\ASB\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355A9002-06BC-414D-8CEA-68B3F2B6B46D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B38FB2F-EE05-4DE4-AC98-E682B9E740AF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14300" yWindow="0" windowWidth="14610" windowHeight="15590" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14300" yWindow="0" windowWidth="14610" windowHeight="15590" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수정 내역" sheetId="41" r:id="rId1"/>
@@ -5814,6 +5814,9 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A19" s="22" t="s">
+        <v>176</v>
+      </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
@@ -5882,9 +5885,6 @@
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A21" s="22" t="s">
-        <v>176</v>
-      </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
